--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP66" headerRowCount="1">
-  <autoFilter ref="A1:EP66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP67" headerRowCount="1">
+  <autoFilter ref="A1:EP67"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP66"/>
+  <dimension ref="A1:EP67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1.57</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         <v>2.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE10" t="n">
         <v>1.17</v>
@@ -9530,7 +9530,7 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE18" t="n">
         <v>1</v>
@@ -11995,7 +11995,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -13866,7 +13866,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE27" t="n">
         <v>0.83</v>
@@ -15309,7 +15309,7 @@
         <v>1</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -18597,7 +18597,7 @@
         <v>1.71</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -21922,7 +21922,7 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE44" t="n">
         <v>0.63</v>
@@ -23826,7 +23826,7 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE48" t="n">
         <v>0.86</v>
@@ -28573,7 +28573,7 @@
         <v>2</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -29034,7 +29034,7 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE59" t="n">
         <v>2.17</v>
@@ -30485,7 +30485,7 @@
         <v>1</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -32546,6 +32546,454 @@
           <t>1.58</t>
         </is>
       </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>14</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>45982.70833333334</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>6</v>
+      </c>
+      <c r="R67" t="n">
+        <v>3</v>
+      </c>
+      <c r="S67" t="n">
+        <v>7</v>
+      </c>
+      <c r="T67" t="n">
+        <v>7</v>
+      </c>
+      <c r="U67" t="n">
+        <v>13</v>
+      </c>
+      <c r="V67" t="n">
+        <v>10</v>
+      </c>
+      <c r="W67" t="n">
+        <v>7</v>
+      </c>
+      <c r="X67" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>1861</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>37</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX67" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY67" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ67" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA67" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB67" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC67" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD67" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE67" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DF67" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH67" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI67" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DJ67" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK67" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL67" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM67" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN67" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DO67" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU67" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV67" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW67" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DX67" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="DY67" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="DZ67" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA67" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EB67" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EC67" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="ED67" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EE67" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EF67" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EG67" t="inlineStr"/>
+      <c r="EH67" t="inlineStr"/>
+      <c r="EI67" t="inlineStr"/>
+      <c r="EJ67" t="inlineStr"/>
+      <c r="EK67" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EL67" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr"/>
+      <c r="EN67" t="inlineStr"/>
+      <c r="EO67" t="inlineStr"/>
+      <c r="EP67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP67" headerRowCount="1">
-  <autoFilter ref="A1:EP67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP71" headerRowCount="1">
+  <autoFilter ref="A1:EP71"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP67"/>
+  <dimension ref="A1:EP71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE4" t="n">
         <v>1</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3253,7 +3253,7 @@
         <v>2.29</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4218,7 +4218,7 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE7" t="n">
         <v>0.29</v>
@@ -4251,7 +4251,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5219,7 +5219,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>2</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6629,7 +6629,7 @@
         <v>1.29</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7147,7 +7147,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE14" t="n">
         <v>1.43</v>
@@ -7635,7 +7635,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8115,7 +8115,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9091,7 +9091,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10018,10 +10018,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -10051,7 +10051,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10501,7 +10501,7 @@
         <v>1</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10531,7 +10531,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10986,10 +10986,10 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -11019,7 +11019,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11507,7 +11507,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12931,7 +12931,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13869,7 +13869,7 @@
         <v>2</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13899,7 +13899,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14349,7 +14349,7 @@
         <v>1.71</v>
       </c>
       <c r="DE28" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -14379,7 +14379,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14834,7 +14834,7 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE29" t="n">
         <v>1</v>
@@ -14867,7 +14867,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15339,7 +15339,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15778,7 +15778,7 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE31" t="n">
         <v>1.33</v>
@@ -15811,7 +15811,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16275,7 +16275,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16733,7 +16733,7 @@
         <v>1.57</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF33" t="n">
         <v>1.33</v>
@@ -16763,7 +16763,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17202,7 +17202,7 @@
         <v>17</v>
       </c>
       <c r="DD34" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -17235,7 +17235,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17723,7 +17723,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18179,7 +18179,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18627,7 +18627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19058,10 +19058,10 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -19091,7 +19091,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -19563,7 +19563,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20002,7 +20002,7 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE40" t="n">
         <v>0.63</v>
@@ -20035,7 +20035,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20474,7 +20474,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE41" t="n">
         <v>1</v>
@@ -20507,7 +20507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20957,7 +20957,7 @@
         <v>2</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF42" t="n">
         <v>2.33</v>
@@ -20987,7 +20987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21445,7 +21445,7 @@
         <v>1.29</v>
       </c>
       <c r="DE43" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -21475,7 +21475,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21955,7 +21955,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22410,7 +22410,7 @@
         <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE45" t="n">
         <v>0.86</v>
@@ -22443,7 +22443,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22931,7 +22931,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23395,7 +23395,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23859,7 +23859,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24298,7 +24298,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE49" t="n">
         <v>0.63</v>
@@ -24331,7 +24331,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24781,7 +24781,7 @@
         <v>2</v>
       </c>
       <c r="DE50" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -24811,7 +24811,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25250,10 +25250,10 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF51" t="n">
         <v>1</v>
@@ -25283,7 +25283,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25722,10 +25722,10 @@
         <v>88</v>
       </c>
       <c r="DD52" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE52" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -25755,7 +25755,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26213,7 +26213,7 @@
         <v>1.57</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -26243,7 +26243,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26707,7 +26707,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27130,7 +27130,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="DE55" t="n">
         <v>0.63</v>
@@ -27163,7 +27163,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27651,7 +27651,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28098,7 +28098,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DE57" t="n">
         <v>0.86</v>
@@ -28131,7 +28131,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28603,7 +28603,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29037,7 +29037,7 @@
         <v>2</v>
       </c>
       <c r="DE59" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -29067,7 +29067,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29525,7 +29525,7 @@
         <v>1</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DF60" t="n">
         <v>1</v>
@@ -29555,7 +29555,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30010,7 +30010,7 @@
         <v>90</v>
       </c>
       <c r="DD61" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE61" t="n">
         <v>1</v>
@@ -30043,7 +30043,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30482,7 +30482,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE62" t="n">
         <v>0.29</v>
@@ -30515,7 +30515,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31003,7 +31003,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31491,7 +31491,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31979,7 +31979,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32427,7 +32427,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32994,6 +32994,1942 @@
       <c r="EN67" t="inlineStr"/>
       <c r="EO67" t="inlineStr"/>
       <c r="EP67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>14</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>45983.58333333334</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>7</v>
+      </c>
+      <c r="L68" t="n">
+        <v>12</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>6</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2</v>
+      </c>
+      <c r="S68" t="n">
+        <v>7</v>
+      </c>
+      <c r="T68" t="n">
+        <v>7</v>
+      </c>
+      <c r="U68" t="n">
+        <v>13</v>
+      </c>
+      <c r="V68" t="n">
+        <v>9</v>
+      </c>
+      <c r="W68" t="n">
+        <v>11</v>
+      </c>
+      <c r="X68" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU68" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX68" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY68" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ68" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH68" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DI68" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DJ68" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK68" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL68" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DM68" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN68" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DO68" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT68" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU68" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV68" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW68" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="DX68" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="DY68" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="DZ68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA68" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EB68" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="EC68" t="inlineStr">
+        <is>
+          <t>9.16</t>
+        </is>
+      </c>
+      <c r="ED68" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EE68" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EF68" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EG68" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EH68" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EI68" t="inlineStr"/>
+      <c r="EJ68" t="inlineStr"/>
+      <c r="EK68" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EL68" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM68" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EN68" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EO68" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EP68" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>14</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>45983.70833333334</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3</v>
+      </c>
+      <c r="K69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L69" t="n">
+        <v>11</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>3</v>
+      </c>
+      <c r="S69" t="n">
+        <v>8</v>
+      </c>
+      <c r="T69" t="n">
+        <v>6</v>
+      </c>
+      <c r="U69" t="n">
+        <v>13</v>
+      </c>
+      <c r="V69" t="n">
+        <v>9</v>
+      </c>
+      <c r="W69" t="n">
+        <v>19</v>
+      </c>
+      <c r="X69" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY69" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ69" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB69" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DI69" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK69" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL69" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DM69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN69" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="DO69" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT69" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU69" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV69" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW69" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DX69" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="DY69" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="DZ69" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA69" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EB69" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EC69" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="ED69" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EE69" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="EF69" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EG69" t="inlineStr"/>
+      <c r="EH69" t="inlineStr"/>
+      <c r="EI69" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EJ69" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EK69" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EL69" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EM69" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EN69" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EO69" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EP69" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>14</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>45984.625</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>6</v>
+      </c>
+      <c r="L70" t="n">
+        <v>9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>3</v>
+      </c>
+      <c r="R70" t="n">
+        <v>8</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="n">
+        <v>16</v>
+      </c>
+      <c r="U70" t="n">
+        <v>8</v>
+      </c>
+      <c r="V70" t="n">
+        <v>24</v>
+      </c>
+      <c r="W70" t="n">
+        <v>12</v>
+      </c>
+      <c r="X70" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>102</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>158</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY70" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>35</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH70" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DI70" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ70" t="n">
+        <v>65</v>
+      </c>
+      <c r="DK70" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL70" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM70" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DN70" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="DO70" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP70" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ70" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU70" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV70" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW70" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DX70" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="DY70" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="DZ70" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="EA70" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EB70" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC70" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="ED70" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EE70" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EF70" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG70" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH70" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EI70" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ70" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EK70" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EL70" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EM70" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EN70" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EO70" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EP70" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>14</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>45984.71875</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" t="n">
+        <v>4</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>6</v>
+      </c>
+      <c r="R71" t="n">
+        <v>5</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="n">
+        <v>9</v>
+      </c>
+      <c r="U71" t="n">
+        <v>12</v>
+      </c>
+      <c r="V71" t="n">
+        <v>14</v>
+      </c>
+      <c r="W71" t="n">
+        <v>8</v>
+      </c>
+      <c r="X71" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>ŠRC Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>, Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AC71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>1875</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>77</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY71" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA71" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB71" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR71" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS71" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU71" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV71" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW71" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX71" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY71" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ71" t="n">
+        <v>69</v>
+      </c>
+      <c r="DA71" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB71" t="n">
+        <v>47</v>
+      </c>
+      <c r="DC71" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD71" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE71" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG71" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH71" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI71" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DJ71" t="n">
+        <v>31</v>
+      </c>
+      <c r="DK71" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM71" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DN71" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DO71" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP71" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV71" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW71" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DX71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DY71" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="DZ71" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA71" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EB71" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC71" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="ED71" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EE71" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EF71" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG71" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EH71" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EI71" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EJ71" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EK71" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL71" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EM71" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EN71" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EO71" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EP71" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -34519,7 +34519,7 @@
         <v>14</v>
       </c>
       <c r="W71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X71" t="n">
         <v>13</v>
@@ -34742,10 +34742,10 @@
         <v>1</v>
       </c>
       <c r="CR71" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS71" t="n">
         <v>21</v>
-      </c>
-      <c r="CS71" t="n">
-        <v>22</v>
       </c>
       <c r="CT71" t="n">
         <v>1</v>
@@ -34754,7 +34754,7 @@
         <v>13</v>
       </c>
       <c r="CV71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CW71" t="n">
         <v>1</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP71" headerRowCount="1">
-  <autoFilter ref="A1:EP71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP72" headerRowCount="1">
+  <autoFilter ref="A1:EP72"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP71"/>
+  <dimension ref="A1:EP72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -6626,7 +6626,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE12" t="n">
         <v>0.71</v>
@@ -8085,7 +8085,7 @@
         <v>1.71</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -9058,7 +9058,7 @@
         <v>84</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE17" t="n">
         <v>1.33</v>
@@ -11962,7 +11962,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE23" t="n">
         <v>1</v>
@@ -12901,7 +12901,7 @@
         <v>1.57</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -15339,7 +15339,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -17693,7 +17693,7 @@
         <v>2</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -18146,7 +18146,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE36" t="n">
         <v>0.86</v>
@@ -20005,7 +20005,7 @@
         <v>1.25</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -21442,7 +21442,7 @@
         <v>100</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE43" t="n">
         <v>1.86</v>
@@ -21925,7 +21925,7 @@
         <v>2</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -23362,7 +23362,7 @@
         <v>90</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE47" t="n">
         <v>1</v>
@@ -24301,7 +24301,7 @@
         <v>2.57</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF49" t="n">
         <v>2.25</v>
@@ -27133,7 +27133,7 @@
         <v>1.57</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -27618,7 +27618,7 @@
         <v>74</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DE56" t="n">
         <v>1.43</v>
@@ -31461,7 +31461,7 @@
         <v>2.29</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="DF64" t="n">
         <v>2.17</v>
@@ -34928,6 +34928,494 @@
       <c r="EP71" t="inlineStr">
         <is>
           <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>15</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>45989.70833333334</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" t="n">
+        <v>14</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>3</v>
+      </c>
+      <c r="R72" t="n">
+        <v>9</v>
+      </c>
+      <c r="S72" t="n">
+        <v>9</v>
+      </c>
+      <c r="T72" t="n">
+        <v>9</v>
+      </c>
+      <c r="U72" t="n">
+        <v>12</v>
+      </c>
+      <c r="V72" t="n">
+        <v>18</v>
+      </c>
+      <c r="W72" t="n">
+        <v>9</v>
+      </c>
+      <c r="X72" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Stadion Cibalia</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Hansa Dietricha Genschera 10b, Vinkovci</t>
+        </is>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ72" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK72" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>77</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>77</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>131</v>
+      </c>
+      <c r="BY72" t="n">
+        <v>127</v>
+      </c>
+      <c r="BZ72" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA72" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CB72" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="CC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN72" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR72" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS72" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU72" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV72" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW72" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX72" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY72" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ72" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA72" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB72" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC72" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD72" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE72" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF72" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG72" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DH72" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI72" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DJ72" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK72" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL72" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM72" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN72" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DO72" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT72" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU72" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV72" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW72" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DX72" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="DY72" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="DZ72" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA72" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EB72" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EC72" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="ED72" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EE72" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EF72" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EG72" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EH72" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EI72" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EJ72" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EK72" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL72" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EM72" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EN72" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EO72" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP72" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP72" headerRowCount="1">
-  <autoFilter ref="A1:EP72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP75" headerRowCount="1">
+  <autoFilter ref="A1:EP75"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP72"/>
+  <dimension ref="A1:EP75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
         <v>0.29</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE5" t="n">
         <v>0.71</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DE8" t="n">
         <v>1</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5189,7 +5189,7 @@
         <v>1</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6138,7 +6138,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE11" t="n">
         <v>1.33</v>
@@ -6659,7 +6659,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7114,7 +7114,7 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE13" t="n">
         <v>1.33</v>
@@ -8115,7 +8115,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8570,7 +8570,7 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE16" t="n">
         <v>1</v>
@@ -8603,7 +8603,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11019,7 +11019,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11474,7 +11474,7 @@
         <v>88</v>
       </c>
       <c r="DD22" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DE22" t="n">
         <v>1.33</v>
@@ -11995,7 +11995,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE25" t="n">
         <v>0.67</v>
@@ -12931,7 +12931,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13386,10 +13386,10 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13419,7 +13419,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13899,7 +13899,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14379,7 +14379,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14867,7 +14867,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -16242,7 +16242,7 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE32" t="n">
         <v>1.43</v>
@@ -16730,7 +16730,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE33" t="n">
         <v>1</v>
@@ -16763,7 +16763,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17690,7 +17690,7 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DE35" t="n">
         <v>0.67</v>
@@ -17723,7 +17723,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18149,7 +18149,7 @@
         <v>1.25</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF36" t="n">
         <v>0.67</v>
@@ -18179,7 +18179,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18627,7 +18627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19091,7 +19091,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE39" t="n">
         <v>1</v>
@@ -19563,7 +19563,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20954,7 +20954,7 @@
         <v>67</v>
       </c>
       <c r="DD42" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DE42" t="n">
         <v>1</v>
@@ -20987,7 +20987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21475,7 +21475,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21955,7 +21955,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22413,7 +22413,7 @@
         <v>1.25</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -22898,7 +22898,7 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE46" t="n">
         <v>1.43</v>
@@ -23395,7 +23395,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23829,7 +23829,7 @@
         <v>2</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF48" t="n">
         <v>2.25</v>
@@ -23859,7 +23859,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24778,7 +24778,7 @@
         <v>59</v>
       </c>
       <c r="DD50" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DE50" t="n">
         <v>1.86</v>
@@ -24811,7 +24811,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26210,7 +26210,7 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE53" t="n">
         <v>0.71</v>
@@ -26243,7 +26243,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26707,7 +26707,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27163,7 +27163,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -28101,7 +28101,7 @@
         <v>2.57</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF57" t="n">
         <v>2.4</v>
@@ -28570,7 +28570,7 @@
         <v>80</v>
       </c>
       <c r="DD58" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DE58" t="n">
         <v>0.29</v>
@@ -28603,7 +28603,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29067,7 +29067,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29555,7 +29555,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30970,7 +30970,7 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -31003,7 +31003,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31458,7 +31458,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="DE64" t="n">
         <v>0.67</v>
@@ -31491,7 +31491,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31946,7 +31946,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DE65" t="n">
         <v>1.43</v>
@@ -32397,7 +32397,7 @@
         <v>1.71</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -32427,7 +32427,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32907,7 +32907,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33843,7 +33843,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34323,7 +34323,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35416,6 +35416,1470 @@
       <c r="EP72" t="inlineStr">
         <is>
           <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>15</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>45990.60416666666</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>7</v>
+      </c>
+      <c r="K73" t="n">
+        <v>4</v>
+      </c>
+      <c r="L73" t="n">
+        <v>11</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3</v>
+      </c>
+      <c r="N73" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>4</v>
+      </c>
+      <c r="R73" t="n">
+        <v>2</v>
+      </c>
+      <c r="S73" t="n">
+        <v>8</v>
+      </c>
+      <c r="T73" t="n">
+        <v>8</v>
+      </c>
+      <c r="U73" t="n">
+        <v>12</v>
+      </c>
+      <c r="V73" t="n">
+        <v>10</v>
+      </c>
+      <c r="W73" t="n">
+        <v>15</v>
+      </c>
+      <c r="X73" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK73" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ73" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV73" t="n">
+        <v>91</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ73" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA73" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB73" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR73" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS73" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU73" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV73" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW73" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX73" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY73" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ73" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA73" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB73" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC73" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD73" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF73" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH73" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DI73" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ73" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK73" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL73" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DM73" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN73" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DO73" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU73" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV73" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW73" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="DX73" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="DY73" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="DZ73" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="EA73" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EB73" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EC73" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="ED73" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE73" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EF73" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG73" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EH73" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EI73" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ73" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EK73" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EL73" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EM73" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EN73" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EO73" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EP73" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>15</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>45990.71875</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" t="n">
+        <v>2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>3</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2</v>
+      </c>
+      <c r="S74" t="n">
+        <v>7</v>
+      </c>
+      <c r="T74" t="n">
+        <v>15</v>
+      </c>
+      <c r="U74" t="n">
+        <v>10</v>
+      </c>
+      <c r="V74" t="n">
+        <v>17</v>
+      </c>
+      <c r="W74" t="n">
+        <v>9</v>
+      </c>
+      <c r="X74" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Stadion Aldo Drosina</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Marsovo polje, Pula</t>
+        </is>
+      </c>
+      <c r="AC74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>120</v>
+      </c>
+      <c r="BZ74" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA74" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CB74" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR74" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS74" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU74" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV74" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX74" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY74" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ74" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA74" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB74" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC74" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD74" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF74" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH74" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ74" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK74" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL74" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DM74" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DN74" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DO74" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW74" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="DX74" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DY74" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="DZ74" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="EA74" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EB74" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EC74" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="ED74" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EE74" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EF74" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG74" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EH74" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EI74" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EJ74" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EK74" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EL74" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EM74" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EN74" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EO74" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EP74" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>15</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>45991.58333333334</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>4</v>
+      </c>
+      <c r="R75" t="n">
+        <v>4</v>
+      </c>
+      <c r="S75" t="n">
+        <v>9</v>
+      </c>
+      <c r="T75" t="n">
+        <v>6</v>
+      </c>
+      <c r="U75" t="n">
+        <v>13</v>
+      </c>
+      <c r="V75" t="n">
+        <v>10</v>
+      </c>
+      <c r="W75" t="n">
+        <v>15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>118</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX75" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY75" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>22</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK75" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL75" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DM75" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DN75" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="DO75" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW75" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="DX75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DY75" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ75" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA75" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EB75" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EC75" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED75" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EF75" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG75" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH75" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EI75" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EJ75" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EM75" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EN75" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EO75" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EP75" t="inlineStr">
+        <is>
+          <t>1.82</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP75" headerRowCount="1">
-  <autoFilter ref="A1:EP75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP76" headerRowCount="1">
+  <autoFilter ref="A1:EP76"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP75"/>
+  <dimension ref="A1:EP76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4251,7 +4251,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7147,7 +7147,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7605,7 +7605,7 @@
         <v>1.57</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7635,7 +7635,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -9091,7 +9091,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11507,7 +11507,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12429,7 +12429,7 @@
         <v>1.71</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -15811,7 +15811,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16245,7 +16245,7 @@
         <v>2.13</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF32" t="n">
         <v>2.5</v>
@@ -16275,7 +16275,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -17202,7 +17202,7 @@
         <v>17</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -17235,7 +17235,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -20002,7 +20002,7 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE40" t="n">
         <v>0.67</v>
@@ -20035,7 +20035,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20507,7 +20507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -22410,7 +22410,7 @@
         <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE45" t="n">
         <v>0.88</v>
@@ -22443,7 +22443,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22901,7 +22901,7 @@
         <v>1.5</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF46" t="n">
         <v>1.75</v>
@@ -22931,7 +22931,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -24331,7 +24331,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25250,7 +25250,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE51" t="n">
         <v>1</v>
@@ -25283,7 +25283,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25722,7 +25722,7 @@
         <v>88</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE52" t="n">
         <v>1.86</v>
@@ -25755,7 +25755,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -27621,7 +27621,7 @@
         <v>1.25</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -27651,7 +27651,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28131,7 +28131,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -30010,7 +30010,7 @@
         <v>90</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE61" t="n">
         <v>1</v>
@@ -30043,7 +30043,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30482,7 +30482,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE62" t="n">
         <v>0.29</v>
@@ -30515,7 +30515,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31949,7 +31949,7 @@
         <v>1.88</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DF65" t="n">
         <v>1.83</v>
@@ -31979,7 +31979,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -33363,7 +33363,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34778,7 +34778,7 @@
         <v>85</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DE71" t="n">
         <v>0.71</v>
@@ -34811,7 +34811,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -36477,10 +36477,10 @@
         <v>16</v>
       </c>
       <c r="Y75" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z75" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -36880,6 +36880,478 @@
       <c r="EP75" t="inlineStr">
         <is>
           <t>1.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>15</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>45992.70833333334</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K76" t="n">
+        <v>4</v>
+      </c>
+      <c r="L76" t="n">
+        <v>7</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="n">
+        <v>10</v>
+      </c>
+      <c r="U76" t="n">
+        <v>7</v>
+      </c>
+      <c r="V76" t="n">
+        <v>12</v>
+      </c>
+      <c r="W76" t="n">
+        <v>11</v>
+      </c>
+      <c r="X76" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>ŠRC Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>, Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>72</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK76" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL76" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM76" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DN76" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DO76" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW76" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="DX76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DY76" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA76" t="inlineStr">
+        <is>
+          <t>6.26</t>
+        </is>
+      </c>
+      <c r="EB76" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="EC76" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="ED76" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EF76" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EG76" t="inlineStr"/>
+      <c r="EH76" t="inlineStr"/>
+      <c r="EI76" t="inlineStr"/>
+      <c r="EJ76" t="inlineStr"/>
+      <c r="EK76" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EM76" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EN76" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EO76" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EP76" t="inlineStr">
+        <is>
+          <t>1.87</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP76" headerRowCount="1">
-  <autoFilter ref="A1:EP76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP77" headerRowCount="1">
+  <autoFilter ref="A1:EP77"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP76"/>
+  <dimension ref="A1:EP77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -3733,7 +3733,7 @@
         <v>1.71</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE10" t="n">
         <v>1</v>
@@ -6141,7 +6141,7 @@
         <v>2.13</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -7117,7 +7117,7 @@
         <v>1.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -9061,7 +9061,7 @@
         <v>1.25</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -9530,7 +9530,7 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE18" t="n">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         <v>1.88</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF22" t="n">
         <v>1</v>
@@ -13866,7 +13866,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE27" t="n">
         <v>0.71</v>
@@ -15781,7 +15781,7 @@
         <v>2.57</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -17235,7 +17235,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -21922,7 +21922,7 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE44" t="n">
         <v>0.67</v>
@@ -23826,7 +23826,7 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE48" t="n">
         <v>0.88</v>
@@ -29034,7 +29034,7 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE59" t="n">
         <v>1.86</v>
@@ -32874,7 +32874,7 @@
         <v>83</v>
       </c>
       <c r="DD67" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DE67" t="n">
         <v>0.29</v>
@@ -37352,6 +37352,486 @@
       <c r="EP76" t="inlineStr">
         <is>
           <t>1.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>16</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>45996.70833333334</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>4</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>7</v>
+      </c>
+      <c r="R77" t="n">
+        <v>4</v>
+      </c>
+      <c r="S77" t="n">
+        <v>6</v>
+      </c>
+      <c r="T77" t="n">
+        <v>9</v>
+      </c>
+      <c r="U77" t="n">
+        <v>13</v>
+      </c>
+      <c r="V77" t="n">
+        <v>13</v>
+      </c>
+      <c r="W77" t="n">
+        <v>17</v>
+      </c>
+      <c r="X77" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>1861</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>77</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>154</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY77" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DE77" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF77" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK77" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL77" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM77" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DN77" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DO77" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV77" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW77" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="DX77" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="DY77" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="DZ77" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA77" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EB77" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EC77" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="ED77" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EE77" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EF77" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG77" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH77" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EI77" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EJ77" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EK77" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EL77" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EN77" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EO77" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EP77" t="inlineStr">
+        <is>
+          <t>1.52</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP77" headerRowCount="1">
-  <autoFilter ref="A1:EP77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP81" headerRowCount="1">
+  <autoFilter ref="A1:EP81"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP77"/>
+  <dimension ref="A1:EP81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE3" t="n">
         <v>1.63</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE4" t="n">
         <v>1</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3253,7 +3253,7 @@
         <v>2.13</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE6" t="n">
         <v>1.14</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4218,10 +4218,10 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>1.88</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE9" t="n">
         <v>0.88</v>
@@ -5219,7 +5219,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6629,7 +6629,7 @@
         <v>1.25</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7147,7 +7147,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE14" t="n">
         <v>1.63</v>
@@ -7635,7 +7635,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8082,7 +8082,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE15" t="n">
         <v>0.67</v>
@@ -8115,7 +8115,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9091,7 +9091,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9533,7 +9533,7 @@
         <v>2.13</v>
       </c>
       <c r="DE18" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9563,7 +9563,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10018,10 +10018,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -10051,7 +10051,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10498,10 +10498,10 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10531,7 +10531,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE21" t="n">
         <v>1</v>
@@ -11019,7 +11019,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11507,7 +11507,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11995,7 +11995,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12426,7 +12426,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE24" t="n">
         <v>1.63</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12931,7 +12931,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13419,7 +13419,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13869,7 +13869,7 @@
         <v>2.13</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13899,7 +13899,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14346,10 +14346,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -14379,7 +14379,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14834,10 +14834,10 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE29" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF29" t="n">
         <v>1</v>
@@ -14867,7 +14867,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15306,10 +15306,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -15339,7 +15339,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15778,7 +15778,7 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DE31" t="n">
         <v>1.14</v>
@@ -15811,7 +15811,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16275,7 +16275,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16763,7 +16763,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17723,7 +17723,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18179,7 +18179,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18594,10 +18594,10 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18627,7 +18627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19058,10 +19058,10 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -19091,7 +19091,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -19533,7 +19533,7 @@
         <v>2.13</v>
       </c>
       <c r="DE39" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -19563,7 +19563,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20035,7 +20035,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20474,7 +20474,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DE41" t="n">
         <v>1</v>
@@ -20507,7 +20507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20987,7 +20987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21445,7 +21445,7 @@
         <v>1.25</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -21475,7 +21475,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21955,7 +21955,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22443,7 +22443,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22931,7 +22931,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23365,7 +23365,7 @@
         <v>1.25</v>
       </c>
       <c r="DE47" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -23395,7 +23395,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23859,7 +23859,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24298,7 +24298,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DE49" t="n">
         <v>0.67</v>
@@ -24331,7 +24331,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24781,7 +24781,7 @@
         <v>1.88</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -24811,7 +24811,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25283,7 +25283,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25725,7 +25725,7 @@
         <v>1.11</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -25755,7 +25755,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26213,7 +26213,7 @@
         <v>1.5</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -26243,7 +26243,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26674,7 +26674,7 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE54" t="n">
         <v>1</v>
@@ -26707,7 +26707,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27130,7 +27130,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE55" t="n">
         <v>0.67</v>
@@ -27163,7 +27163,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27651,7 +27651,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28098,7 +28098,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DE57" t="n">
         <v>0.88</v>
@@ -28131,7 +28131,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28573,7 +28573,7 @@
         <v>1.88</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -28603,7 +28603,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29037,7 +29037,7 @@
         <v>2.13</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -29067,7 +29067,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29522,7 +29522,7 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE60" t="n">
         <v>1</v>
@@ -29555,7 +29555,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30013,7 +30013,7 @@
         <v>1.11</v>
       </c>
       <c r="DE61" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF61" t="n">
         <v>0.6</v>
@@ -30043,7 +30043,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30485,7 +30485,7 @@
         <v>1.11</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -30515,7 +30515,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31003,7 +31003,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31491,7 +31491,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31979,7 +31979,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32394,7 +32394,7 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE66" t="n">
         <v>0.88</v>
@@ -32427,7 +32427,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32877,7 +32877,7 @@
         <v>2.13</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -32907,7 +32907,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33330,7 +33330,7 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="DE68" t="n">
         <v>1</v>
@@ -33363,7 +33363,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33810,10 +33810,10 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF69" t="n">
         <v>1.33</v>
@@ -33843,7 +33843,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34290,10 +34290,10 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE70" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF70" t="n">
         <v>1</v>
@@ -34323,7 +34323,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34781,7 +34781,7 @@
         <v>1.11</v>
       </c>
       <c r="DE71" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -34811,7 +34811,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35299,7 +35299,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35787,7 +35787,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36275,7 +36275,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36763,7 +36763,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37251,7 +37251,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37832,6 +37832,1934 @@
       <c r="EP77" t="inlineStr">
         <is>
           <t>1.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>16</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>45997.58333333334</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" t="n">
+        <v>10</v>
+      </c>
+      <c r="M78" t="n">
+        <v>6</v>
+      </c>
+      <c r="N78" t="n">
+        <v>10</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>8</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>13</v>
+      </c>
+      <c r="V78" t="n">
+        <v>4</v>
+      </c>
+      <c r="W78" t="n">
+        <v>12</v>
+      </c>
+      <c r="X78" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC78" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>7</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>97</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>155</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>27</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="DO78" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW78" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="DX78" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DY78" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="DZ78" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA78" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EB78" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EC78" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG78" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL78" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EM78" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN78" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EO78" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP78" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>16</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>45997.70833333334</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>4</v>
+      </c>
+      <c r="J79" t="n">
+        <v>12</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3</v>
+      </c>
+      <c r="L79" t="n">
+        <v>15</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>7</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>20</v>
+      </c>
+      <c r="V79" t="n">
+        <v>5</v>
+      </c>
+      <c r="W79" t="n">
+        <v>8</v>
+      </c>
+      <c r="X79" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>87</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>148</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK79" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL79" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DM79" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DN79" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="DO79" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW79" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="DX79" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="DY79" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DZ79" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="EA79" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>5.96</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>11.67</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr"/>
+      <c r="EN79" t="inlineStr"/>
+      <c r="EO79" t="inlineStr"/>
+      <c r="EP79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>16</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>45998.58333333334</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" t="n">
+        <v>6</v>
+      </c>
+      <c r="J80" t="n">
+        <v>4</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>4</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>10</v>
+      </c>
+      <c r="V80" t="n">
+        <v>7</v>
+      </c>
+      <c r="W80" t="n">
+        <v>16</v>
+      </c>
+      <c r="X80" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>1881</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="DO80" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW80" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="DX80" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="DZ80" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA80" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EN80" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EO80" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EP80" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>16</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>45998.6875</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6</v>
+      </c>
+      <c r="J81" t="n">
+        <v>6</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" t="n">
+        <v>9</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>9</v>
+      </c>
+      <c r="T81" t="n">
+        <v>6</v>
+      </c>
+      <c r="U81" t="n">
+        <v>13</v>
+      </c>
+      <c r="V81" t="n">
+        <v>12</v>
+      </c>
+      <c r="W81" t="n">
+        <v>16</v>
+      </c>
+      <c r="X81" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>1857</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>37</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>83</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>83</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>131</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY81" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ81" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA81" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB81" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC81" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD81" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF81" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG81" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH81" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ81" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK81" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL81" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DM81" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DN81" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DO81" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW81" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="DX81" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DY81" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ81" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EC81" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="ED81" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EE81" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="EF81" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EG81" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EH81" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EI81" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EN81" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EO81" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EP81" t="inlineStr">
+        <is>
+          <t>1.76</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -37917,10 +37917,10 @@
         <v>27</v>
       </c>
       <c r="Y78" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Z78" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -38877,10 +38877,10 @@
         <v>14</v>
       </c>
       <c r="Y80" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Z80" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
@@ -39107,7 +39107,7 @@
         <v>1</v>
       </c>
       <c r="CY80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ80" t="n">
         <v>43</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP81" headerRowCount="1">
-  <autoFilter ref="A1:EP81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP85" headerRowCount="1">
+  <autoFilter ref="A1:EP85"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP81"/>
+  <dimension ref="A1:EP85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE2" t="n">
         <v>0.25</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3733,7 +3733,7 @@
         <v>1.88</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4251,7 +4251,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE9" t="n">
         <v>0.88</v>
@@ -5666,10 +5666,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6141,7 +6141,7 @@
         <v>2.13</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6171,7 +6171,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6626,7 +6626,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE12" t="n">
         <v>1</v>
@@ -7114,10 +7114,10 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -7147,7 +7147,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7605,7 +7605,7 @@
         <v>1.75</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -8115,7 +8115,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9058,10 +9058,10 @@
         <v>84</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -9091,7 +9091,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9530,7 +9530,7 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE18" t="n">
         <v>0.88</v>
@@ -9563,7 +9563,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10498,10 +10498,10 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10531,7 +10531,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10989,7 +10989,7 @@
         <v>1.75</v>
       </c>
       <c r="DE21" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -11477,7 +11477,7 @@
         <v>1.88</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF22" t="n">
         <v>1</v>
@@ -11962,7 +11962,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE23" t="n">
         <v>1</v>
@@ -11995,7 +11995,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12429,7 +12429,7 @@
         <v>1.88</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE25" t="n">
         <v>0.67</v>
@@ -12931,7 +12931,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13866,7 +13866,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE27" t="n">
         <v>1</v>
@@ -14349,7 +14349,7 @@
         <v>1.88</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -14379,7 +14379,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15306,7 +15306,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE30" t="n">
         <v>0.25</v>
@@ -15339,7 +15339,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15781,7 +15781,7 @@
         <v>2.38</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15811,7 +15811,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16245,7 +16245,7 @@
         <v>2.13</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF32" t="n">
         <v>2.5</v>
@@ -16275,7 +16275,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16730,10 +16730,10 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF33" t="n">
         <v>1.33</v>
@@ -16763,7 +16763,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17235,7 +17235,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18146,7 +18146,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE36" t="n">
         <v>0.88</v>
@@ -18627,7 +18627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19563,7 +19563,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20035,7 +20035,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20507,7 +20507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20957,7 +20957,7 @@
         <v>1.88</v>
       </c>
       <c r="DE42" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF42" t="n">
         <v>2.33</v>
@@ -21442,10 +21442,10 @@
         <v>100</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -21475,7 +21475,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21922,7 +21922,7 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE44" t="n">
         <v>0.67</v>
@@ -21955,7 +21955,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22898,10 +22898,10 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF46" t="n">
         <v>1.75</v>
@@ -22931,7 +22931,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23362,7 +23362,7 @@
         <v>90</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE47" t="n">
         <v>0.88</v>
@@ -23395,7 +23395,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23826,7 +23826,7 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE48" t="n">
         <v>0.88</v>
@@ -24331,7 +24331,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24781,7 +24781,7 @@
         <v>1.88</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -25253,7 +25253,7 @@
         <v>1.11</v>
       </c>
       <c r="DE51" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF51" t="n">
         <v>1</v>
@@ -25283,7 +25283,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25725,7 +25725,7 @@
         <v>1.11</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -25755,7 +25755,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26210,7 +26210,7 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE53" t="n">
         <v>1</v>
@@ -26707,7 +26707,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27618,10 +27618,10 @@
         <v>74</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -27651,7 +27651,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -29034,10 +29034,10 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -29067,7 +29067,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29522,10 +29522,10 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE60" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF60" t="n">
         <v>1</v>
@@ -29555,7 +29555,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30043,7 +30043,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30515,7 +30515,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30970,7 +30970,7 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -31003,7 +31003,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31491,7 +31491,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31949,7 +31949,7 @@
         <v>1.88</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF65" t="n">
         <v>1.83</v>
@@ -32874,7 +32874,7 @@
         <v>83</v>
       </c>
       <c r="DD67" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE67" t="n">
         <v>0.25</v>
@@ -32907,7 +32907,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33333,7 +33333,7 @@
         <v>2.38</v>
       </c>
       <c r="DE68" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF68" t="n">
         <v>2.5</v>
@@ -33363,7 +33363,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33813,7 +33813,7 @@
         <v>1.75</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF69" t="n">
         <v>1.33</v>
@@ -34290,7 +34290,7 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE70" t="n">
         <v>0.88</v>
@@ -34323,7 +34323,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35266,7 +35266,7 @@
         <v>73</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE72" t="n">
         <v>0.67</v>
@@ -35299,7 +35299,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35757,7 +35757,7 @@
         <v>2.13</v>
       </c>
       <c r="DE73" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF73" t="n">
         <v>2.29</v>
@@ -35787,7 +35787,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36730,7 +36730,7 @@
         <v>86</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE75" t="n">
         <v>0.88</v>
@@ -37221,7 +37221,7 @@
         <v>1.11</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DF76" t="n">
         <v>1.25</v>
@@ -37251,7 +37251,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37682,10 +37682,10 @@
         <v>77</v>
       </c>
       <c r="DD77" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF77" t="n">
         <v>2</v>
@@ -37715,7 +37715,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38173,7 +38173,7 @@
         <v>2.38</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DF78" t="n">
         <v>2.57</v>
@@ -38203,7 +38203,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -39155,7 +39155,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39610,7 +39610,7 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE81" t="n">
         <v>1</v>
@@ -39760,6 +39760,1938 @@
       <c r="EP81" t="inlineStr">
         <is>
           <t>1.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>17</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46003.70833333334</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="n">
+        <v>4</v>
+      </c>
+      <c r="L82" t="n">
+        <v>8</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>6</v>
+      </c>
+      <c r="R82" t="n">
+        <v>3</v>
+      </c>
+      <c r="S82" t="n">
+        <v>7</v>
+      </c>
+      <c r="T82" t="n">
+        <v>5</v>
+      </c>
+      <c r="U82" t="n">
+        <v>13</v>
+      </c>
+      <c r="V82" t="n">
+        <v>8</v>
+      </c>
+      <c r="W82" t="n">
+        <v>16</v>
+      </c>
+      <c r="X82" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Stadion Cibalia</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Hansa Dietricha Genschera 10b, Vinkovci</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>19790</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC82" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE82" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI82" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ82" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK82" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL82" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM82" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN82" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO82" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW82" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="DX82" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DY82" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="DZ82" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EC82" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="ED82" t="inlineStr"/>
+      <c r="EE82" t="inlineStr"/>
+      <c r="EF82" t="inlineStr"/>
+      <c r="EG82" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EH82" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EI82" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EN82" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EO82" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EP82" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>17</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46004.58333333334</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" t="n">
+        <v>7</v>
+      </c>
+      <c r="K83" t="n">
+        <v>3</v>
+      </c>
+      <c r="L83" t="n">
+        <v>10</v>
+      </c>
+      <c r="M83" t="n">
+        <v>3</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2</v>
+      </c>
+      <c r="S83" t="n">
+        <v>11</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>16</v>
+      </c>
+      <c r="V83" t="n">
+        <v>4</v>
+      </c>
+      <c r="W83" t="n">
+        <v>18</v>
+      </c>
+      <c r="X83" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC83" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>127</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>168</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB83" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR83" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS83" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU83" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV83" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX83" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY83" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ83" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA83" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB83" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC83" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD83" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DE83" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF83" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DG83" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI83" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ83" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK83" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL83" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DM83" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN83" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="DO83" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV83" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW83" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="DX83" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DY83" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ83" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA83" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EB83" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EE83" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EG83" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EH83" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EI83" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ83" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EK83" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EL83" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM83" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EN83" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EO83" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EP83" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>17</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46004.69791666666</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>5</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6</v>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6</v>
+      </c>
+      <c r="S84" t="n">
+        <v>4</v>
+      </c>
+      <c r="T84" t="n">
+        <v>13</v>
+      </c>
+      <c r="U84" t="n">
+        <v>6</v>
+      </c>
+      <c r="V84" t="n">
+        <v>19</v>
+      </c>
+      <c r="W84" t="n">
+        <v>15</v>
+      </c>
+      <c r="X84" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY84" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ84" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA84" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB84" t="n">
+        <v>26</v>
+      </c>
+      <c r="DC84" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD84" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE84" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DF84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH84" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DI84" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DJ84" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK84" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL84" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DM84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN84" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DO84" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW84" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="DX84" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DY84" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="DZ84" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE84" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="EF84" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG84" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EH84" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EI84" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ84" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EL84" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM84" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EN84" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EO84" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP84" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>17</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46005.58333333334</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>5</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" t="n">
+        <v>3</v>
+      </c>
+      <c r="L85" t="n">
+        <v>6</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>6</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6</v>
+      </c>
+      <c r="S85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T85" t="n">
+        <v>9</v>
+      </c>
+      <c r="U85" t="n">
+        <v>10</v>
+      </c>
+      <c r="V85" t="n">
+        <v>15</v>
+      </c>
+      <c r="W85" t="n">
+        <v>15</v>
+      </c>
+      <c r="X85" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY85" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ85" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB85" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC85" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD85" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE85" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DF85" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DG85" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DH85" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI85" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ85" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK85" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL85" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DM85" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DN85" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="DO85" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW85" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="DX85" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DY85" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="DZ85" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EG85" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EO85" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EP85" t="inlineStr">
+        <is>
+          <t>1.63</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -40538,7 +40538,7 @@
         <v>1</v>
       </c>
       <c r="CR83" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CS83" t="n">
         <v>17</v>
@@ -41509,7 +41509,7 @@
         <v>22</v>
       </c>
       <c r="CS85" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CT85" t="n">
         <v>1</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -41294,7 +41294,7 @@
         <v>15</v>
       </c>
       <c r="X85" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y85" t="n">
         <v>47</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP85" headerRowCount="1">
-  <autoFilter ref="A1:EP85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP88" headerRowCount="1">
+  <autoFilter ref="A1:EP88"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP85"/>
+  <dimension ref="A1:EP88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE3" t="n">
         <v>1.78</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3253,7 +3253,7 @@
         <v>2.13</v>
       </c>
       <c r="DE5" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE6" t="n">
         <v>1.13</v>
@@ -4218,7 +4218,7 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE7" t="n">
         <v>0.25</v>
@@ -4701,7 +4701,7 @@
         <v>1.88</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE9" t="n">
         <v>0.88</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6629,7 +6629,7 @@
         <v>1.44</v>
       </c>
       <c r="DE12" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -8082,7 +8082,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE15" t="n">
         <v>0.67</v>
@@ -8115,7 +8115,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>1.89</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9563,7 +9563,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10018,10 +10018,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE19" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -10051,7 +10051,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE20" t="n">
         <v>1.89</v>
@@ -11507,7 +11507,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12426,7 +12426,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE24" t="n">
         <v>1.78</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12931,7 +12931,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13869,7 +13869,7 @@
         <v>1.89</v>
       </c>
       <c r="DE27" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13899,7 +13899,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14346,7 +14346,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE28" t="n">
         <v>1.89</v>
@@ -14837,7 +14837,7 @@
         <v>1.75</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF29" t="n">
         <v>1</v>
@@ -15306,7 +15306,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE30" t="n">
         <v>0.25</v>
@@ -15778,7 +15778,7 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE31" t="n">
         <v>1.13</v>
@@ -16763,7 +16763,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17723,7 +17723,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18594,7 +18594,7 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE37" t="n">
         <v>0.25</v>
@@ -19061,7 +19061,7 @@
         <v>1.75</v>
       </c>
       <c r="DE38" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -19533,7 +19533,7 @@
         <v>2.13</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -20474,7 +20474,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE41" t="n">
         <v>1</v>
@@ -20507,7 +20507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20987,7 +20987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21955,7 +21955,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22931,7 +22931,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23365,7 +23365,7 @@
         <v>1.44</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -24298,7 +24298,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE49" t="n">
         <v>0.67</v>
@@ -24331,7 +24331,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24811,7 +24811,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26213,7 +26213,7 @@
         <v>1.33</v>
       </c>
       <c r="DE53" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -26243,7 +26243,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26674,7 +26674,7 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE54" t="n">
         <v>1</v>
@@ -26707,7 +26707,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -28098,7 +28098,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE57" t="n">
         <v>0.88</v>
@@ -28603,7 +28603,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29522,7 +29522,7 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE60" t="n">
         <v>0.89</v>
@@ -29555,7 +29555,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30013,7 +30013,7 @@
         <v>1.11</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF61" t="n">
         <v>0.6</v>
@@ -31003,7 +31003,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31979,7 +31979,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32394,7 +32394,7 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE66" t="n">
         <v>0.88</v>
@@ -33330,7 +33330,7 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE68" t="n">
         <v>0.89</v>
@@ -33363,7 +33363,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34290,10 +34290,10 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF70" t="n">
         <v>1</v>
@@ -34323,7 +34323,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34781,7 +34781,7 @@
         <v>1.11</v>
       </c>
       <c r="DE71" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -34811,7 +34811,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -36275,7 +36275,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -38170,7 +38170,7 @@
         <v>86</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="DE78" t="n">
         <v>1.89</v>
@@ -39122,10 +39122,10 @@
         <v>86</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF80" t="n">
         <v>1.71</v>
@@ -39155,7 +39155,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39610,10 +39610,10 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE81" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -39643,7 +39643,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40574,7 +40574,7 @@
         <v>64</v>
       </c>
       <c r="DD83" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE83" t="n">
         <v>1.13</v>
@@ -41575,7 +41575,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41692,6 +41692,1434 @@
       <c r="EP85" t="inlineStr">
         <is>
           <t>1.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>18</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>46010.625</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3</v>
+      </c>
+      <c r="I86" t="n">
+        <v>4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>9</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>14</v>
+      </c>
+      <c r="M86" t="n">
+        <v>3</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>9</v>
+      </c>
+      <c r="R86" t="n">
+        <v>4</v>
+      </c>
+      <c r="S86" t="n">
+        <v>12</v>
+      </c>
+      <c r="T86" t="n">
+        <v>10</v>
+      </c>
+      <c r="U86" t="n">
+        <v>21</v>
+      </c>
+      <c r="V86" t="n">
+        <v>14</v>
+      </c>
+      <c r="W86" t="n">
+        <v>15</v>
+      </c>
+      <c r="X86" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>1857</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV86" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>134</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CB86" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="CC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR86" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX86" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY86" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ86" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA86" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB86" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC86" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD86" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE86" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF86" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DG86" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH86" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI86" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ86" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK86" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL86" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM86" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN86" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DO86" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW86" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="DX86" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="DY86" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="DZ86" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="EA86" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EB86" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EC86" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="ED86" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EG86" t="inlineStr"/>
+      <c r="EH86" t="inlineStr"/>
+      <c r="EI86" t="inlineStr"/>
+      <c r="EJ86" t="inlineStr"/>
+      <c r="EK86" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EL86" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM86" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EN86" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EO86" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EP86" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>18</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>46011.58333333334</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>3</v>
+      </c>
+      <c r="S87" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" t="n">
+        <v>4</v>
+      </c>
+      <c r="U87" t="n">
+        <v>12</v>
+      </c>
+      <c r="V87" t="n">
+        <v>7</v>
+      </c>
+      <c r="W87" t="n">
+        <v>14</v>
+      </c>
+      <c r="X87" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>106</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>153</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY87" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC87" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD87" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DJ87" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK87" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL87" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DM87" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN87" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO87" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW87" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="DX87" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DY87" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="DZ87" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="EA87" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EH87" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EL87" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EO87" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EP87" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>18</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>46011.69791666666</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2</v>
+      </c>
+      <c r="S88" t="n">
+        <v>7</v>
+      </c>
+      <c r="T88" t="n">
+        <v>4</v>
+      </c>
+      <c r="U88" t="n">
+        <v>12</v>
+      </c>
+      <c r="V88" t="n">
+        <v>6</v>
+      </c>
+      <c r="W88" t="n">
+        <v>9</v>
+      </c>
+      <c r="X88" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>82</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>77</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>147</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>120</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>69</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC88" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD88" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DE88" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF88" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DI88" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DJ88" t="n">
+        <v>32</v>
+      </c>
+      <c r="DK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL88" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM88" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN88" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="DO88" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW88" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="DX88" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DY88" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ88" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA88" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EB88" t="inlineStr">
+        <is>
+          <t>5.51</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="ED88" t="inlineStr"/>
+      <c r="EE88" t="inlineStr"/>
+      <c r="EF88" t="inlineStr"/>
+      <c r="EG88" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL88" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EO88" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EP88" t="inlineStr">
+        <is>
+          <t>1.97</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP88" headerRowCount="1">
-  <autoFilter ref="A1:EP88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP90" headerRowCount="1">
+  <autoFilter ref="A1:EP90"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP88"/>
+  <dimension ref="A1:EP90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1.33</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE4" t="n">
         <v>1</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE5" t="n">
         <v>1.22</v>
@@ -3733,7 +3733,7 @@
         <v>1.67</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4221,7 +4221,7 @@
         <v>2.44</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5219,7 +5219,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -6138,10 +6138,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6171,7 +6171,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7117,7 +7117,7 @@
         <v>1.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -7147,7 +7147,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE14" t="n">
         <v>1.78</v>
@@ -7635,7 +7635,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8570,7 +8570,7 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE16" t="n">
         <v>1</v>
@@ -8603,7 +8603,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9061,7 +9061,7 @@
         <v>1.44</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -9091,7 +9091,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE21" t="n">
         <v>0.89</v>
@@ -11019,7 +11019,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11477,7 +11477,7 @@
         <v>1.88</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF22" t="n">
         <v>1</v>
@@ -11995,7 +11995,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -13386,7 +13386,7 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE26" t="n">
         <v>0.88</v>
@@ -13419,7 +13419,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14379,7 +14379,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14834,7 +14834,7 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE29" t="n">
         <v>0.78</v>
@@ -14867,7 +14867,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15309,7 +15309,7 @@
         <v>0.89</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -15339,7 +15339,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15781,7 +15781,7 @@
         <v>2.44</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15811,7 +15811,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16242,7 +16242,7 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE32" t="n">
         <v>1.78</v>
@@ -16275,7 +16275,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -17235,7 +17235,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18179,7 +18179,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18597,7 +18597,7 @@
         <v>1.67</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18627,7 +18627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19058,7 +19058,7 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE38" t="n">
         <v>1.22</v>
@@ -19091,7 +19091,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE39" t="n">
         <v>0.78</v>
@@ -19563,7 +19563,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20035,7 +20035,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -21475,7 +21475,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22443,7 +22443,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23395,7 +23395,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23859,7 +23859,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -25283,7 +25283,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25755,7 +25755,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -27130,7 +27130,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE55" t="n">
         <v>0.67</v>
@@ -27163,7 +27163,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27651,7 +27651,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28131,7 +28131,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28573,7 +28573,7 @@
         <v>1.88</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -29067,7 +29067,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -30043,7 +30043,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30485,7 +30485,7 @@
         <v>1.11</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -30515,7 +30515,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31458,7 +31458,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE64" t="n">
         <v>0.67</v>
@@ -31491,7 +31491,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32427,7 +32427,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32877,7 +32877,7 @@
         <v>1.89</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -32907,7 +32907,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33810,7 +33810,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE69" t="n">
         <v>1.89</v>
@@ -33843,7 +33843,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -35299,7 +35299,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35754,7 +35754,7 @@
         <v>64</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="DE73" t="n">
         <v>0.89</v>
@@ -35787,7 +35787,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36763,7 +36763,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37251,7 +37251,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37685,7 +37685,7 @@
         <v>1.89</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF77" t="n">
         <v>2</v>
@@ -37715,7 +37715,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38203,7 +38203,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38658,10 +38658,10 @@
         <v>79</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF79" t="n">
         <v>1.57</v>
@@ -38691,7 +38691,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -40131,7 +40131,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40577,7 +40577,7 @@
         <v>0.89</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF83" t="n">
         <v>0.86</v>
@@ -40607,7 +40607,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41095,7 +41095,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41771,7 +41771,7 @@
         <v>14</v>
       </c>
       <c r="W86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X86" t="n">
         <v>8</v>
@@ -42723,10 +42723,10 @@
         <v>6</v>
       </c>
       <c r="W88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X88" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y88" t="n">
         <v>48</v>
@@ -43120,6 +43120,966 @@
       <c r="EP88" t="inlineStr">
         <is>
           <t>1.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>18</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46012.58333333334</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3</v>
+      </c>
+      <c r="L89" t="n">
+        <v>5</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3</v>
+      </c>
+      <c r="N89" t="n">
+        <v>5</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>8</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>8</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>16</v>
+      </c>
+      <c r="V89" t="n">
+        <v>3</v>
+      </c>
+      <c r="W89" t="n">
+        <v>12</v>
+      </c>
+      <c r="X89" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX89" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY89" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ89" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CA89" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR89" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS89" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU89" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV89" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX89" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY89" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ89" t="n">
+        <v>51</v>
+      </c>
+      <c r="DA89" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB89" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC89" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD89" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DE89" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DF89" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DG89" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH89" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI89" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DJ89" t="n">
+        <v>51</v>
+      </c>
+      <c r="DK89" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL89" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM89" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN89" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="DO89" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW89" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="DX89" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="DY89" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="DZ89" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA89" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EB89" t="inlineStr">
+        <is>
+          <t>5.42</t>
+        </is>
+      </c>
+      <c r="EC89" t="inlineStr">
+        <is>
+          <t>10.72</t>
+        </is>
+      </c>
+      <c r="ED89" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EE89" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EF89" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EG89" t="inlineStr"/>
+      <c r="EH89" t="inlineStr"/>
+      <c r="EI89" t="inlineStr"/>
+      <c r="EJ89" t="inlineStr"/>
+      <c r="EK89" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EL89" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM89" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EN89" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EO89" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EP89" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>18</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>46012.69791666666</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>10</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4</v>
+      </c>
+      <c r="L90" t="n">
+        <v>14</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>4</v>
+      </c>
+      <c r="R90" t="n">
+        <v>2</v>
+      </c>
+      <c r="S90" t="n">
+        <v>11</v>
+      </c>
+      <c r="T90" t="n">
+        <v>5</v>
+      </c>
+      <c r="U90" t="n">
+        <v>15</v>
+      </c>
+      <c r="V90" t="n">
+        <v>7</v>
+      </c>
+      <c r="W90" t="n">
+        <v>12</v>
+      </c>
+      <c r="X90" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>101</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX90" t="n">
+        <v>150</v>
+      </c>
+      <c r="BY90" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ90" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CA90" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CB90" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM90" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR90" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS90" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU90" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV90" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX90" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY90" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA90" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB90" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC90" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD90" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE90" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF90" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG90" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH90" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI90" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DJ90" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK90" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL90" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DM90" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN90" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="DO90" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW90" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="DX90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="EA90" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="EC90" t="inlineStr">
+        <is>
+          <t>6.89</t>
+        </is>
+      </c>
+      <c r="ED90" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EE90" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EF90" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EG90" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EH90" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EI90" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EJ90" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EK90" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL90" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM90" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EN90" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EO90" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EP90" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45872.82291666666</v>
+        <v>45872.79166666666</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -27809,7 +27809,7 @@
         <v>11</v>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
         <v>5</v>
@@ -27861,7 +27861,7 @@
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD57" t="n">
         <v>5</v>
@@ -27975,7 +27975,7 @@
         <v>7</v>
       </c>
       <c r="BO57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP57" t="n">
         <v>1</v>
@@ -27987,7 +27987,7 @@
         <v>4</v>
       </c>
       <c r="BS57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT57" t="n">
         <v>7</v>
@@ -30196,7 +30196,7 @@
         <v>2</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -30248,7 +30248,7 @@
         <v>2</v>
       </c>
       <c r="AD62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE62" t="n">
         <v>1.7</v>
@@ -30368,13 +30368,13 @@
         <v>1</v>
       </c>
       <c r="BR62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS62" t="n">
         <v>3</v>
       </c>
       <c r="BT62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU62" t="n">
         <v>1</v>
@@ -31657,7 +31657,7 @@
         <v>23</v>
       </c>
       <c r="M65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N65" t="n">
         <v>3</v>
@@ -31709,7 +31709,7 @@
         </is>
       </c>
       <c r="AC65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD65" t="n">
         <v>3</v>
@@ -31823,7 +31823,7 @@
         <v>13</v>
       </c>
       <c r="BO65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP65" t="n">
         <v>0</v>
@@ -31835,7 +31835,7 @@
         <v>3</v>
       </c>
       <c r="BS65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT65" t="n">
         <v>8</v>
@@ -41515,7 +41515,7 @@
         <v>1</v>
       </c>
       <c r="CU85" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV85" t="n">
         <v>15</v>
@@ -42723,10 +42723,10 @@
         <v>6</v>
       </c>
       <c r="W88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y88" t="n">
         <v>48</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP90" headerRowCount="1">
-  <autoFilter ref="A1:EP90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP91" headerRowCount="1">
+  <autoFilter ref="A1:EP91"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP90"/>
+  <dimension ref="A1:EP91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE8" t="n">
         <v>0.78</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5189,7 +5189,7 @@
         <v>0.89</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7635,7 +7635,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11019,7 +11019,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11474,7 +11474,7 @@
         <v>88</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE22" t="n">
         <v>1</v>
@@ -11507,7 +11507,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -13389,7 +13389,7 @@
         <v>2.22</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13419,7 +13419,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13899,7 +13899,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14867,7 +14867,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -17690,7 +17690,7 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE35" t="n">
         <v>0.67</v>
@@ -17723,7 +17723,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18149,7 +18149,7 @@
         <v>1.44</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF36" t="n">
         <v>0.67</v>
@@ -18179,7 +18179,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -19091,7 +19091,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -20954,7 +20954,7 @@
         <v>67</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE42" t="n">
         <v>0.89</v>
@@ -20987,7 +20987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -22413,7 +22413,7 @@
         <v>1.11</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -22443,7 +22443,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23829,7 +23829,7 @@
         <v>1.89</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF48" t="n">
         <v>2.25</v>
@@ -23859,7 +23859,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24778,7 +24778,7 @@
         <v>59</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE50" t="n">
         <v>1.89</v>
@@ -24811,7 +24811,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26243,7 +26243,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -27163,7 +27163,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -28101,7 +28101,7 @@
         <v>2.44</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF57" t="n">
         <v>2.4</v>
@@ -28131,7 +28131,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28570,7 +28570,7 @@
         <v>80</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE58" t="n">
         <v>0.22</v>
@@ -28603,7 +28603,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -31946,7 +31946,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE65" t="n">
         <v>1.78</v>
@@ -31979,7 +31979,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32397,7 +32397,7 @@
         <v>1.67</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -32427,7 +32427,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33843,7 +33843,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34811,7 +34811,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -36242,7 +36242,7 @@
         <v>71</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE74" t="n">
         <v>1</v>
@@ -36275,7 +36275,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36733,7 +36733,7 @@
         <v>1.33</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="DF75" t="n">
         <v>1.57</v>
@@ -36763,7 +36763,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -38691,7 +38691,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39643,7 +39643,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -42055,7 +42055,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -43963,7 +43963,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44080,6 +44080,494 @@
       <c r="EP90" t="inlineStr">
         <is>
           <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>17</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>46042.625</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4</v>
+      </c>
+      <c r="L91" t="n">
+        <v>7</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>4</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2</v>
+      </c>
+      <c r="S91" t="n">
+        <v>7</v>
+      </c>
+      <c r="T91" t="n">
+        <v>8</v>
+      </c>
+      <c r="U91" t="n">
+        <v>11</v>
+      </c>
+      <c r="V91" t="n">
+        <v>10</v>
+      </c>
+      <c r="W91" t="n">
+        <v>16</v>
+      </c>
+      <c r="X91" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Stadion Aldo Drosina</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>Marsovo polje, Pula</t>
+        </is>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>3386</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX91" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY91" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ91" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CA91" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB91" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR91" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS91" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU91" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV91" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX91" t="n">
+        <v>16</v>
+      </c>
+      <c r="CY91" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ91" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA91" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB91" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC91" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD91" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE91" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF91" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DG91" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH91" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DI91" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DJ91" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK91" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL91" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM91" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DN91" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DO91" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW91" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="DX91" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DY91" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ91" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA91" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EB91" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC91" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="ED91" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EE91" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EF91" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EG91" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EH91" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EI91" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EJ91" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EK91" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EL91" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EM91" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EN91" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EO91" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EP91" t="inlineStr">
+        <is>
+          <t>1.61</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -44385,7 +44385,7 @@
         <v>24</v>
       </c>
       <c r="CS91" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT91" t="n">
         <v>1</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP91" headerRowCount="1">
-  <autoFilter ref="A1:EP91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP95" headerRowCount="1">
+  <autoFilter ref="A1:EP95"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP91"/>
+  <dimension ref="A1:EP95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="26.4" customWidth="1" min="27" max="27"/>
+    <col width="27.6" customWidth="1" min="27" max="27"/>
     <col width="49.2" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
@@ -1802,10 +1802,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE4" t="n">
         <v>1</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3250,10 +3250,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4221,7 +4221,7 @@
         <v>2.44</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE9" t="n">
         <v>1.11</v>
@@ -5219,7 +5219,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -6138,7 +6138,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE11" t="n">
         <v>1</v>
@@ -6629,7 +6629,7 @@
         <v>1.44</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7114,7 +7114,7 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -7602,10 +7602,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7635,7 +7635,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8570,7 +8570,7 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE16" t="n">
         <v>1</v>
@@ -8603,7 +8603,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10021,7 +10021,7 @@
         <v>2.44</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -10051,7 +10051,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE20" t="n">
         <v>1.89</v>
@@ -10531,7 +10531,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE21" t="n">
         <v>0.89</v>
@@ -11995,7 +11995,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12429,7 +12429,7 @@
         <v>1.67</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE25" t="n">
         <v>0.67</v>
@@ -12931,7 +12931,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13386,7 +13386,7 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE26" t="n">
         <v>1.11</v>
@@ -13419,7 +13419,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13869,7 +13869,7 @@
         <v>1.89</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13899,7 +13899,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14834,7 +14834,7 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE29" t="n">
         <v>0.78</v>
@@ -14867,7 +14867,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15306,10 +15306,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -15339,7 +15339,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -16242,10 +16242,10 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF32" t="n">
         <v>2.5</v>
@@ -16275,7 +16275,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16730,7 +16730,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE33" t="n">
         <v>0.89</v>
@@ -17723,7 +17723,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18179,7 +18179,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18597,7 +18597,7 @@
         <v>1.67</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -19058,10 +19058,10 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -19091,7 +19091,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE39" t="n">
         <v>0.78</v>
@@ -19563,7 +19563,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20507,7 +20507,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21475,7 +21475,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21955,7 +21955,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22898,10 +22898,10 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF46" t="n">
         <v>1.75</v>
@@ -22931,7 +22931,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23395,7 +23395,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23859,7 +23859,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24331,7 +24331,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24811,7 +24811,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26210,10 +26210,10 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -26243,7 +26243,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -27130,7 +27130,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE55" t="n">
         <v>0.67</v>
@@ -27163,7 +27163,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27621,7 +27621,7 @@
         <v>1.44</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -27651,7 +27651,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28131,7 +28131,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28573,7 +28573,7 @@
         <v>1.67</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -28603,7 +28603,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29067,7 +29067,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29522,7 +29522,7 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE60" t="n">
         <v>0.89</v>
@@ -30485,7 +30485,7 @@
         <v>1.11</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -30970,7 +30970,7 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE63" t="n">
         <v>1</v>
@@ -31003,7 +31003,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31458,7 +31458,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE64" t="n">
         <v>0.67</v>
@@ -31491,7 +31491,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31949,7 +31949,7 @@
         <v>1.67</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF65" t="n">
         <v>1.83</v>
@@ -31979,7 +31979,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32877,7 +32877,7 @@
         <v>1.89</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -32907,7 +32907,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33810,7 +33810,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE69" t="n">
         <v>1.89</v>
@@ -33843,7 +33843,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34290,7 +34290,7 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE70" t="n">
         <v>0.78</v>
@@ -34323,7 +34323,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34781,7 +34781,7 @@
         <v>1.11</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -35299,7 +35299,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35754,7 +35754,7 @@
         <v>64</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE73" t="n">
         <v>0.89</v>
@@ -36275,7 +36275,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36730,7 +36730,7 @@
         <v>86</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE75" t="n">
         <v>1.11</v>
@@ -36763,7 +36763,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -37221,7 +37221,7 @@
         <v>1.11</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF76" t="n">
         <v>1.25</v>
@@ -38203,7 +38203,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38658,10 +38658,10 @@
         <v>79</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF79" t="n">
         <v>1.57</v>
@@ -38691,7 +38691,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39610,10 +39610,10 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -39643,7 +39643,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40574,7 +40574,7 @@
         <v>64</v>
       </c>
       <c r="DD83" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE83" t="n">
         <v>1</v>
@@ -41062,7 +41062,7 @@
         <v>76</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DE84" t="n">
         <v>1.89</v>
@@ -41095,7 +41095,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41545,7 +41545,7 @@
         <v>1.89</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DF85" t="n">
         <v>2.13</v>
@@ -41575,7 +41575,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -42025,7 +42025,7 @@
         <v>1.67</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DF86" t="n">
         <v>1.88</v>
@@ -42494,7 +42494,7 @@
         <v>69</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE87" t="n">
         <v>1</v>
@@ -42527,7 +42527,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -43015,7 +43015,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43458,10 +43458,10 @@
         <v>82</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF89" t="n">
         <v>2.13</v>
@@ -43491,7 +43491,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43930,7 +43930,7 @@
         <v>75</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DE90" t="n">
         <v>1</v>
@@ -44451,7 +44451,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44568,6 +44568,1942 @@
       <c r="EP91" t="inlineStr">
         <is>
           <t>1.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>19</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46046.58333333334</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" t="n">
+        <v>8</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2</v>
+      </c>
+      <c r="S92" t="n">
+        <v>6</v>
+      </c>
+      <c r="T92" t="n">
+        <v>6</v>
+      </c>
+      <c r="U92" t="n">
+        <v>8</v>
+      </c>
+      <c r="V92" t="n">
+        <v>8</v>
+      </c>
+      <c r="W92" t="n">
+        <v>8</v>
+      </c>
+      <c r="X92" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Stadion Kranjčevićeva</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>Kranjčevićeva 4, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>1859</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>73</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>200</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>34</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX92" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY92" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB92" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC92" t="n">
+        <v>89</v>
+      </c>
+      <c r="DD92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF92" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG92" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DH92" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI92" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DJ92" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK92" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL92" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM92" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN92" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DO92" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW92" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="DX92" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DY92" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="DZ92" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA92" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EB92" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EC92" t="inlineStr">
+        <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="ED92" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EE92" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EF92" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EG92" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EH92" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EI92" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EJ92" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EK92" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EL92" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EM92" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EN92" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EO92" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EP92" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>19</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46046.67708333334</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>4</v>
+      </c>
+      <c r="J93" t="n">
+        <v>4</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" t="n">
+        <v>7</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>4</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6</v>
+      </c>
+      <c r="S93" t="n">
+        <v>11</v>
+      </c>
+      <c r="T93" t="n">
+        <v>12</v>
+      </c>
+      <c r="U93" t="n">
+        <v>15</v>
+      </c>
+      <c r="V93" t="n">
+        <v>18</v>
+      </c>
+      <c r="W93" t="n">
+        <v>18</v>
+      </c>
+      <c r="X93" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>3808</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="DO93" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW93" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="DX93" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="DY93" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="DZ93" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA93" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EB93" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EC93" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="ED93" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EF93" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG93" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EH93" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EI93" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EJ93" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EK93" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL93" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EM93" t="inlineStr"/>
+      <c r="EN93" t="inlineStr"/>
+      <c r="EO93" t="inlineStr"/>
+      <c r="EP93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>19</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46047.58333333334</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" t="n">
+        <v>6</v>
+      </c>
+      <c r="K94" t="n">
+        <v>6</v>
+      </c>
+      <c r="L94" t="n">
+        <v>12</v>
+      </c>
+      <c r="M94" t="n">
+        <v>4</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>7</v>
+      </c>
+      <c r="R94" t="n">
+        <v>4</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="n">
+        <v>6</v>
+      </c>
+      <c r="U94" t="n">
+        <v>22</v>
+      </c>
+      <c r="V94" t="n">
+        <v>10</v>
+      </c>
+      <c r="W94" t="n">
+        <v>8</v>
+      </c>
+      <c r="X94" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>1857</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY94" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE94" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF94" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH94" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DI94" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DJ94" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK94" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL94" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DM94" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN94" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DO94" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="DX94" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="DY94" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="DZ94" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA94" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EB94" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="ED94" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EE94" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EF94" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EG94" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EH94" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EI94" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EJ94" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EK94" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EL94" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM94" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EN94" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EO94" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EP94" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>19</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46047.69791666666</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2</v>
+      </c>
+      <c r="L95" t="n">
+        <v>6</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6</v>
+      </c>
+      <c r="S95" t="n">
+        <v>7</v>
+      </c>
+      <c r="T95" t="n">
+        <v>11</v>
+      </c>
+      <c r="U95" t="n">
+        <v>8</v>
+      </c>
+      <c r="V95" t="n">
+        <v>17</v>
+      </c>
+      <c r="W95" t="n">
+        <v>14</v>
+      </c>
+      <c r="X95" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>39</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>65</v>
+      </c>
+      <c r="BX95" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY95" t="n">
+        <v>115</v>
+      </c>
+      <c r="BZ95" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA95" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CB95" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM95" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR95" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS95" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU95" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV95" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX95" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY95" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ95" t="n">
+        <v>33</v>
+      </c>
+      <c r="DA95" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB95" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC95" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD95" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DF95" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DG95" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DH95" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DI95" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DJ95" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK95" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL95" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DM95" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DN95" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="DO95" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW95" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="DX95" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="DY95" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="DZ95" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA95" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="EB95" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="EC95" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="ED95" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EE95" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EF95" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EG95" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EH95" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI95" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EJ95" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EK95" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EL95" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EM95" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EN95" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EO95" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EP95" t="inlineStr">
+        <is>
+          <t>1.71</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP95" headerRowCount="1">
-  <autoFilter ref="A1:EP95"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP96" headerRowCount="1">
+  <autoFilter ref="A1:EP96"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP95"/>
+  <dimension ref="A1:EP96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -5669,7 +5669,7 @@
         <v>1.89</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7147,7 +7147,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -8115,7 +8115,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -9091,7 +9091,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10989,7 +10989,7 @@
         <v>1.8</v>
       </c>
       <c r="DE21" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -11019,7 +11019,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11507,7 +11507,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12459,7 +12459,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -14379,7 +14379,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15811,7 +15811,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16733,7 +16733,7 @@
         <v>1.5</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF33" t="n">
         <v>1.33</v>
@@ -16763,7 +16763,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17202,7 +17202,7 @@
         <v>17</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -17235,7 +17235,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18627,7 +18627,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -20002,7 +20002,7 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE40" t="n">
         <v>0.67</v>
@@ -20035,7 +20035,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20957,7 +20957,7 @@
         <v>1.67</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF42" t="n">
         <v>2.33</v>
@@ -20987,7 +20987,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -22410,7 +22410,7 @@
         <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE45" t="n">
         <v>1.11</v>
@@ -22443,7 +22443,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -25250,10 +25250,10 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE51" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF51" t="n">
         <v>1</v>
@@ -25283,7 +25283,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25722,7 +25722,7 @@
         <v>88</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE52" t="n">
         <v>1.89</v>
@@ -25755,7 +25755,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26707,7 +26707,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -29525,7 +29525,7 @@
         <v>0.8</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF60" t="n">
         <v>1</v>
@@ -29555,7 +29555,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30010,7 +30010,7 @@
         <v>90</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE61" t="n">
         <v>0.78</v>
@@ -30043,7 +30043,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30482,7 +30482,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE62" t="n">
         <v>0.2</v>
@@ -30515,7 +30515,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -32427,7 +32427,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33333,7 +33333,7 @@
         <v>2.44</v>
       </c>
       <c r="DE68" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF68" t="n">
         <v>2.5</v>
@@ -33363,7 +33363,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34778,7 +34778,7 @@
         <v>85</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE71" t="n">
         <v>1.4</v>
@@ -34811,7 +34811,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35757,7 +35757,7 @@
         <v>2</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF73" t="n">
         <v>2.29</v>
@@ -35787,7 +35787,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -37218,7 +37218,7 @@
         <v>80</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DE76" t="n">
         <v>1.9</v>
@@ -37251,7 +37251,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37715,7 +37715,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -39155,7 +39155,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -40101,7 +40101,7 @@
         <v>1.44</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="DF82" t="n">
         <v>1.25</v>
@@ -40131,7 +40131,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40607,7 +40607,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -42055,7 +42055,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -43963,7 +43963,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -45716,7 +45716,7 @@
         <v>0</v>
       </c>
       <c r="BF94" t="n">
-        <v>-1</v>
+        <v>11925</v>
       </c>
       <c r="BG94" t="n">
         <v>2</v>
@@ -46204,7 +46204,7 @@
         <v>0</v>
       </c>
       <c r="BF95" t="n">
-        <v>-1</v>
+        <v>8723</v>
       </c>
       <c r="BG95" t="n">
         <v>2</v>
@@ -46504,6 +46504,478 @@
       <c r="EP95" t="inlineStr">
         <is>
           <t>1.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>19</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46048.625</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3</v>
+      </c>
+      <c r="L96" t="n">
+        <v>10</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>2</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5</v>
+      </c>
+      <c r="R96" t="n">
+        <v>4</v>
+      </c>
+      <c r="S96" t="n">
+        <v>8</v>
+      </c>
+      <c r="T96" t="n">
+        <v>8</v>
+      </c>
+      <c r="U96" t="n">
+        <v>13</v>
+      </c>
+      <c r="V96" t="n">
+        <v>12</v>
+      </c>
+      <c r="W96" t="n">
+        <v>8</v>
+      </c>
+      <c r="X96" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>ŠRC Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>, Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>1881</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>318</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY96" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE96" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DF96" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI96" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK96" t="n">
+        <v>28</v>
+      </c>
+      <c r="DL96" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM96" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN96" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO96" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW96" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="DX96" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DY96" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="DZ96" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA96" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EB96" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr"/>
+      <c r="EH96" t="inlineStr"/>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EO96" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EP96" t="inlineStr">
+        <is>
+          <t>1.60</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL97" headerRowCount="1">
-  <autoFilter ref="A1:EL97"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL100" headerRowCount="1">
+  <autoFilter ref="A1:EL100"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL97"/>
+  <dimension ref="A1:EL100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE3" t="n">
         <v>1.9</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -5046,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5510,10 +5510,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9246,7 +9246,7 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE18" t="n">
         <v>0.8</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10182,10 +10182,10 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10657,7 +10657,7 @@
         <v>1.8</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12977,7 +12977,7 @@
         <v>2</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13438,7 +13438,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE27" t="n">
         <v>1.4</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13905,7 +13905,7 @@
         <v>1.67</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14830,7 +14830,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE30" t="n">
         <v>0.2</v>
@@ -16209,7 +16209,7 @@
         <v>1.5</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF33" t="n">
         <v>1.33</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16662,7 +16662,7 @@
         <v>17</v>
       </c>
       <c r="DD34" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17577,7 +17577,7 @@
         <v>1.44</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF36" t="n">
         <v>0.67</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19366,7 +19366,7 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE40" t="n">
         <v>0.67</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20289,7 +20289,7 @@
         <v>1.6</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF42" t="n">
         <v>2.33</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20761,7 +20761,7 @@
         <v>1.44</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -21222,7 +21222,7 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE44" t="n">
         <v>0.67</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21694,10 +21694,10 @@
         <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23062,10 +23062,10 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF48" t="n">
         <v>2.25</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23985,7 +23985,7 @@
         <v>1.6</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24438,10 +24438,10 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF51" t="n">
         <v>1</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24894,10 +24894,10 @@
         <v>88</v>
       </c>
       <c r="DD52" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27193,7 +27193,7 @@
         <v>2.44</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF57" t="n">
         <v>2.4</v>
@@ -28094,10 +28094,10 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28566,10 +28566,10 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF60" t="n">
         <v>1</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -29038,7 +29038,7 @@
         <v>90</v>
       </c>
       <c r="DD61" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE61" t="n">
         <v>0.8</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29494,7 +29494,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE62" t="n">
         <v>0.2</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31345,7 +31345,7 @@
         <v>1.67</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31806,7 +31806,7 @@
         <v>83</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE67" t="n">
         <v>0.2</v>
@@ -32249,7 +32249,7 @@
         <v>2.44</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF68" t="n">
         <v>2.5</v>
@@ -32713,7 +32713,7 @@
         <v>1.8</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF69" t="n">
         <v>1.33</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33174,7 +33174,7 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE70" t="n">
         <v>0.8</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33646,7 +33646,7 @@
         <v>85</v>
       </c>
       <c r="DD71" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE71" t="n">
         <v>1.4</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34593,7 +34593,7 @@
         <v>2</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF73" t="n">
         <v>2.29</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35537,7 +35537,7 @@
         <v>1.5</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF75" t="n">
         <v>1.57</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36006,7 +36006,7 @@
         <v>80</v>
       </c>
       <c r="DD76" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE76" t="n">
         <v>1.9</v>
@@ -36454,7 +36454,7 @@
         <v>77</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE77" t="n">
         <v>1</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36929,7 +36929,7 @@
         <v>2.44</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF78" t="n">
         <v>2.57</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38318,7 +38318,7 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE81" t="n">
         <v>1.4</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38793,7 +38793,7 @@
         <v>1.44</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF82" t="n">
         <v>1.25</v>
@@ -39250,7 +39250,7 @@
         <v>64</v>
       </c>
       <c r="DD83" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE83" t="n">
         <v>1</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39725,7 +39725,7 @@
         <v>1.5</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DF84" t="n">
         <v>1.5</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40186,7 +40186,7 @@
         <v>82</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DE85" t="n">
         <v>1.9</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41106,7 +41106,7 @@
         <v>69</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE87" t="n">
         <v>1</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42969,7 +42969,7 @@
         <v>1.6</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DF91" t="n">
         <v>1.88</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44838,7 +44838,7 @@
         <v>67</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DE95" t="n">
         <v>1.9</v>
@@ -45310,10 +45310,10 @@
         <v>73</v>
       </c>
       <c r="DD96" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DF96" t="n">
         <v>1.11</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45616,7 +45616,7 @@
         <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>-1</v>
+        <v>1757</v>
       </c>
       <c r="BG97" t="n">
         <v>2</v>
@@ -45900,6 +45900,1398 @@
       <c r="EL97" t="inlineStr">
         <is>
           <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>20</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46053.58333333334</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>9</v>
+      </c>
+      <c r="L98" t="n">
+        <v>10</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>2</v>
+      </c>
+      <c r="R98" t="n">
+        <v>5</v>
+      </c>
+      <c r="S98" t="n">
+        <v>4</v>
+      </c>
+      <c r="T98" t="n">
+        <v>16</v>
+      </c>
+      <c r="U98" t="n">
+        <v>6</v>
+      </c>
+      <c r="V98" t="n">
+        <v>21</v>
+      </c>
+      <c r="W98" t="n">
+        <v>18</v>
+      </c>
+      <c r="X98" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>74</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>ŠRC Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>, Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AC98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>1875</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>3889</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX98" t="n">
+        <v>76</v>
+      </c>
+      <c r="BY98" t="n">
+        <v>136</v>
+      </c>
+      <c r="BZ98" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CA98" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR98" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS98" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU98" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV98" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX98" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY98" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ98" t="n">
+        <v>52</v>
+      </c>
+      <c r="DA98" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB98" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC98" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD98" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DE98" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI98" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DJ98" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK98" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL98" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM98" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN98" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DO98" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW98" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="DX98" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="DY98" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DZ98" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EA98" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="ED98" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EE98" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EG98" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH98" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr"/>
+      <c r="EJ98" t="inlineStr"/>
+      <c r="EK98" t="inlineStr"/>
+      <c r="EL98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>20</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46053.69791666666</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" t="n">
+        <v>2</v>
+      </c>
+      <c r="J99" t="n">
+        <v>11</v>
+      </c>
+      <c r="K99" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" t="n">
+        <v>16</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>5</v>
+      </c>
+      <c r="R99" t="n">
+        <v>5</v>
+      </c>
+      <c r="S99" t="n">
+        <v>20</v>
+      </c>
+      <c r="T99" t="n">
+        <v>3</v>
+      </c>
+      <c r="U99" t="n">
+        <v>25</v>
+      </c>
+      <c r="V99" t="n">
+        <v>8</v>
+      </c>
+      <c r="W99" t="n">
+        <v>17</v>
+      </c>
+      <c r="X99" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>1881</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>875</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>97</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>53</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD99" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DE99" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK99" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL99" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DM99" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN99" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO99" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW99" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="DX99" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>20</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46054.58333333334</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" t="n">
+        <v>7</v>
+      </c>
+      <c r="L100" t="n">
+        <v>10</v>
+      </c>
+      <c r="M100" t="n">
+        <v>4</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>3</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2</v>
+      </c>
+      <c r="S100" t="n">
+        <v>6</v>
+      </c>
+      <c r="T100" t="n">
+        <v>13</v>
+      </c>
+      <c r="U100" t="n">
+        <v>9</v>
+      </c>
+      <c r="V100" t="n">
+        <v>15</v>
+      </c>
+      <c r="W100" t="n">
+        <v>15</v>
+      </c>
+      <c r="X100" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>68</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>1864</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>77</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK100" t="n">
+        <v>26</v>
+      </c>
+      <c r="DL100" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DM100" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DN100" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="DO100" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW100" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="DX100" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="DZ100" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EL100" t="inlineStr">
+        <is>
+          <t>1.86</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL100" headerRowCount="1">
-  <autoFilter ref="A1:EL100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL101" headerRowCount="1">
+  <autoFilter ref="A1:EL101"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL100"/>
+  <dimension ref="A1:EL101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -4110,10 +4110,10 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9718,7 +9718,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE19" t="n">
         <v>1.4</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -14833,7 +14833,7 @@
         <v>1</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15286,7 +15286,7 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE31" t="n">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18009,7 +18009,7 @@
         <v>1.67</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19822,7 +19822,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE41" t="n">
         <v>1</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23518,7 +23518,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE49" t="n">
         <v>0.67</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27190,7 +27190,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE57" t="n">
         <v>1</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27649,7 +27649,7 @@
         <v>1.6</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29497,7 +29497,7 @@
         <v>1.18</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31809,7 +31809,7 @@
         <v>1.7</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32246,7 +32246,7 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE68" t="n">
         <v>1.27</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36926,7 +36926,7 @@
         <v>86</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE78" t="n">
         <v>1.7</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37401,7 +37401,7 @@
         <v>1.8</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF79" t="n">
         <v>1.57</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41578,7 +41578,7 @@
         <v>88</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DE88" t="n">
         <v>0.8</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42041,7 +42041,7 @@
         <v>2</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF89" t="n">
         <v>2.13</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43441,7 +43441,7 @@
         <v>1.5</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF92" t="n">
         <v>1.33</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45513,10 +45513,10 @@
         <v>16</v>
       </c>
       <c r="Y97" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z97" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
@@ -45964,13 +45964,13 @@
         <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
       </c>
       <c r="T98" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U98" t="n">
         <v>6</v>
@@ -46151,10 +46151,10 @@
         <v>0.72</v>
       </c>
       <c r="CA98" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="CB98" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="CC98" t="n">
         <v>0</v>
@@ -46441,10 +46441,10 @@
         <v>12</v>
       </c>
       <c r="Y99" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z99" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -47008,7 +47008,7 @@
         <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>-1</v>
+        <v>3262</v>
       </c>
       <c r="BG100" t="n">
         <v>2</v>
@@ -47292,6 +47292,470 @@
       <c r="EL100" t="inlineStr">
         <is>
           <t>1.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>20</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46055.70833333334</v>
+      </c>
+      <c r="G101" t="n">
+        <v>3</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>4</v>
+      </c>
+      <c r="J101" t="n">
+        <v>8</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>9</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>10</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2</v>
+      </c>
+      <c r="S101" t="n">
+        <v>17</v>
+      </c>
+      <c r="T101" t="n">
+        <v>4</v>
+      </c>
+      <c r="U101" t="n">
+        <v>27</v>
+      </c>
+      <c r="V101" t="n">
+        <v>6</v>
+      </c>
+      <c r="W101" t="n">
+        <v>9</v>
+      </c>
+      <c r="X101" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>4750</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>84</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>128</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>3</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>74</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>95</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>26</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL101" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DM101" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN101" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="DO101" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW101" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="DX101" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>14.28</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="ED101" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EE101" t="inlineStr"/>
+      <c r="EF101" t="inlineStr"/>
+      <c r="EG101" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EJ101" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EK101" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EL101" t="inlineStr">
+        <is>
+          <t>1.97</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL101" headerRowCount="1">
-  <autoFilter ref="A1:EL101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL104" headerRowCount="1">
+  <autoFilter ref="A1:EL104"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL101"/>
+  <dimension ref="A1:EL104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE2" t="n">
         <v>0.18</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2705,7 +2705,7 @@
         <v>1.8</v>
       </c>
       <c r="DE4" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3174,10 +3174,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3641,7 +3641,7 @@
         <v>1.67</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5966,10 +5966,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6438,10 +6438,10 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6910,10 +6910,10 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -8318,10 +8318,10 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE16" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8790,10 +8790,10 @@
         <v>84</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         <v>2.5</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -11129,7 +11129,7 @@
         <v>1.6</v>
       </c>
       <c r="DE22" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF22" t="n">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11598,10 +11598,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE23" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF23" t="n">
         <v>1</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12502,7 +12502,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE25" t="n">
         <v>0.67</v>
@@ -12974,7 +12974,7 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE26" t="n">
         <v>1</v>
@@ -13441,7 +13441,7 @@
         <v>1.7</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -15289,7 +15289,7 @@
         <v>2.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15734,7 +15734,7 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE32" t="n">
         <v>1.9</v>
@@ -16206,7 +16206,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE33" t="n">
         <v>1.27</v>
@@ -16665,7 +16665,7 @@
         <v>1.18</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17574,7 +17574,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE36" t="n">
         <v>1</v>
@@ -18457,7 +18457,7 @@
         <v>1.8</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18910,7 +18910,7 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE39" t="n">
         <v>0.8</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19825,7 +19825,7 @@
         <v>2.5</v>
       </c>
       <c r="DE41" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -20758,7 +20758,7 @@
         <v>100</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE43" t="n">
         <v>1.7</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22166,7 +22166,7 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE46" t="n">
         <v>1.9</v>
@@ -22614,7 +22614,7 @@
         <v>90</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE47" t="n">
         <v>0.8</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25366,10 +25366,10 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25817,7 +25817,7 @@
         <v>1.67</v>
       </c>
       <c r="DE54" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF54" t="n">
         <v>1.8</v>
@@ -26726,7 +26726,7 @@
         <v>74</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE56" t="n">
         <v>1.9</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29966,10 +29966,10 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF63" t="n">
         <v>1.67</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30438,7 +30438,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE64" t="n">
         <v>0.67</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33649,7 +33649,7 @@
         <v>1.18</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34118,7 +34118,7 @@
         <v>73</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE72" t="n">
         <v>0.67</v>
@@ -34590,7 +34590,7 @@
         <v>64</v>
       </c>
       <c r="DD73" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE73" t="n">
         <v>1.27</v>
@@ -35065,7 +35065,7 @@
         <v>1.6</v>
       </c>
       <c r="DE74" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF74" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35534,7 +35534,7 @@
         <v>86</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE75" t="n">
         <v>1</v>
@@ -36457,7 +36457,7 @@
         <v>1.7</v>
       </c>
       <c r="DE77" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF77" t="n">
         <v>2</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38321,7 +38321,7 @@
         <v>1</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -38790,7 +38790,7 @@
         <v>63</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE82" t="n">
         <v>1.27</v>
@@ -39253,7 +39253,7 @@
         <v>1</v>
       </c>
       <c r="DE83" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF83" t="n">
         <v>0.86</v>
@@ -39722,7 +39722,7 @@
         <v>76</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE84" t="n">
         <v>1.7</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40653,7 +40653,7 @@
         <v>1.67</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF86" t="n">
         <v>1.88</v>
@@ -41109,7 +41109,7 @@
         <v>1</v>
       </c>
       <c r="DE87" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF87" t="n">
         <v>0.88</v>
@@ -42038,7 +42038,7 @@
         <v>82</v>
       </c>
       <c r="DD89" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE89" t="n">
         <v>0.18</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42497,7 +42497,7 @@
         <v>1.8</v>
       </c>
       <c r="DE90" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DF90" t="n">
         <v>1.75</v>
@@ -43438,7 +43438,7 @@
         <v>89</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="DE92" t="n">
         <v>0.18</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43913,7 +43913,7 @@
         <v>1.8</v>
       </c>
       <c r="DE93" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF93" t="n">
         <v>1.89</v>
@@ -44366,10 +44366,10 @@
         <v>84</v>
       </c>
       <c r="DD94" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF94" t="n">
         <v>2.22</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47756,6 +47756,1390 @@
       <c r="EL101" t="inlineStr">
         <is>
           <t>1.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>21</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46059.70833333334</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>2</v>
+      </c>
+      <c r="K102" t="n">
+        <v>9</v>
+      </c>
+      <c r="L102" t="n">
+        <v>11</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>7</v>
+      </c>
+      <c r="R102" t="n">
+        <v>4</v>
+      </c>
+      <c r="S102" t="n">
+        <v>3</v>
+      </c>
+      <c r="T102" t="n">
+        <v>16</v>
+      </c>
+      <c r="U102" t="n">
+        <v>10</v>
+      </c>
+      <c r="V102" t="n">
+        <v>20</v>
+      </c>
+      <c r="W102" t="n">
+        <v>14</v>
+      </c>
+      <c r="X102" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>1859</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>74</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV102" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX102" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY102" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ102" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR102" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS102" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU102" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV102" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX102" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY102" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ102" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>21</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE102" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI102" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DJ102" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK102" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL102" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM102" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN102" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DO102" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW102" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="DX102" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="DZ102" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EA102" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EB102" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC102" t="inlineStr"/>
+      <c r="ED102" t="inlineStr"/>
+      <c r="EE102" t="inlineStr"/>
+      <c r="EF102" t="inlineStr"/>
+      <c r="EG102" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EH102" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EI102" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EJ102" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EK102" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL102" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>21</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46060.58333333334</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" t="n">
+        <v>5</v>
+      </c>
+      <c r="L103" t="n">
+        <v>12</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2</v>
+      </c>
+      <c r="N103" t="n">
+        <v>4</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>13</v>
+      </c>
+      <c r="R103" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" t="n">
+        <v>13</v>
+      </c>
+      <c r="T103" t="n">
+        <v>9</v>
+      </c>
+      <c r="U103" t="n">
+        <v>26</v>
+      </c>
+      <c r="V103" t="n">
+        <v>13</v>
+      </c>
+      <c r="W103" t="n">
+        <v>5</v>
+      </c>
+      <c r="X103" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>19790</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>84</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>103</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>169</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>5</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX103" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY103" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>47</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ103" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK103" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL103" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM103" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN103" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DO103" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW103" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="DX103" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="DZ103" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EA103" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC103" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED103" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EE103" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF103" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EG103" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EH103" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EI103" t="inlineStr"/>
+      <c r="EJ103" t="inlineStr"/>
+      <c r="EK103" t="inlineStr"/>
+      <c r="EL103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>21</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46060.67708333334</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" t="n">
+        <v>3</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>4</v>
+      </c>
+      <c r="R104" t="n">
+        <v>5</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="n">
+        <v>8</v>
+      </c>
+      <c r="U104" t="n">
+        <v>9</v>
+      </c>
+      <c r="V104" t="n">
+        <v>13</v>
+      </c>
+      <c r="W104" t="n">
+        <v>16</v>
+      </c>
+      <c r="X104" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>126</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX104" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY104" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>95</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DE104" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DI104" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DJ104" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK104" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL104" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DM104" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN104" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DO104" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW104" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="DX104" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED104" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EK104" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr">
+        <is>
+          <t>1.62</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL104" headerRowCount="1">
-  <autoFilter ref="A1:EL104"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL106" headerRowCount="1">
+  <autoFilter ref="A1:EL106"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL104"/>
+  <dimension ref="A1:EL106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2233,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE4" t="n">
         <v>0.91</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE6" t="n">
         <v>0.9</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -7382,10 +7382,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7846,10 +7846,10 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10654,7 +10654,7 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE21" t="n">
         <v>1.27</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -12046,10 +12046,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12505,7 +12505,7 @@
         <v>1.64</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13902,7 +13902,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE28" t="n">
         <v>1.7</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14374,7 +14374,7 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE29" t="n">
         <v>0.8</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15737,7 +15737,7 @@
         <v>2.09</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF32" t="n">
         <v>2.5</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17137,7 +17137,7 @@
         <v>1.6</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18006,7 +18006,7 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE37" t="n">
         <v>0.18</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18454,7 +18454,7 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE38" t="n">
         <v>1.27</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -19369,7 +19369,7 @@
         <v>1.18</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21225,7 +21225,7 @@
         <v>1.7</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22169,7 +22169,7 @@
         <v>1.64</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF46" t="n">
         <v>1.75</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23521,7 +23521,7 @@
         <v>2.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF49" t="n">
         <v>2.25</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25814,7 +25814,7 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE54" t="n">
         <v>0.91</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26254,10 +26254,10 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26729,7 +26729,7 @@
         <v>1.6</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30441,7 +30441,7 @@
         <v>2.09</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF64" t="n">
         <v>2.17</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30913,7 +30913,7 @@
         <v>1.6</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF65" t="n">
         <v>1.83</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31342,7 +31342,7 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE66" t="n">
         <v>1</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE69" t="n">
         <v>1.7</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34121,7 +34121,7 @@
         <v>1.6</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DF72" t="n">
         <v>1.29</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36009,7 +36009,7 @@
         <v>1.18</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF76" t="n">
         <v>1.25</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37398,7 +37398,7 @@
         <v>79</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE79" t="n">
         <v>0.18</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37846,7 +37846,7 @@
         <v>86</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE80" t="n">
         <v>0.8</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40189,7 +40189,7 @@
         <v>1.7</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF85" t="n">
         <v>2.13</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40650,7 +40650,7 @@
         <v>88</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DE86" t="n">
         <v>1.27</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42494,7 +42494,7 @@
         <v>75</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE90" t="n">
         <v>0.9</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43910,7 +43910,7 @@
         <v>67</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE93" t="n">
         <v>0.91</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44841,7 +44841,7 @@
         <v>1</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DF95" t="n">
         <v>0.89</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49142,6 +49142,926 @@
           <t>1.62</t>
         </is>
       </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>21</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46061.58333333334</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>3</v>
+      </c>
+      <c r="J105" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" t="n">
+        <v>5</v>
+      </c>
+      <c r="L105" t="n">
+        <v>8</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4</v>
+      </c>
+      <c r="N105" t="n">
+        <v>4</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>3</v>
+      </c>
+      <c r="R105" t="n">
+        <v>5</v>
+      </c>
+      <c r="S105" t="n">
+        <v>7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>4</v>
+      </c>
+      <c r="U105" t="n">
+        <v>10</v>
+      </c>
+      <c r="V105" t="n">
+        <v>9</v>
+      </c>
+      <c r="W105" t="n">
+        <v>7</v>
+      </c>
+      <c r="X105" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>1881</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>1447</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>64</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>118</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY105" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ105" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA105" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB105" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC105" t="n">
+        <v>89</v>
+      </c>
+      <c r="DD105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DE105" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF105" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG105" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH105" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DI105" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DJ105" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK105" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL105" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DM105" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DN105" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DO105" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW105" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="DX105" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="DZ105" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EB105" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC105" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED105" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EE105" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EG105" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EH105" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EI105" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EJ105" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EK105" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EL105" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>21</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>46061.69791666666</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>4</v>
+      </c>
+      <c r="K106" t="n">
+        <v>7</v>
+      </c>
+      <c r="L106" t="n">
+        <v>11</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>2</v>
+      </c>
+      <c r="S106" t="n">
+        <v>2</v>
+      </c>
+      <c r="T106" t="n">
+        <v>10</v>
+      </c>
+      <c r="U106" t="n">
+        <v>2</v>
+      </c>
+      <c r="V106" t="n">
+        <v>12</v>
+      </c>
+      <c r="W106" t="n">
+        <v>10</v>
+      </c>
+      <c r="X106" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>7102</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>82</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>124</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX106" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY106" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ106" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA106" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB106" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC106" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD106" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE106" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DF106" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG106" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DH106" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DI106" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DJ106" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK106" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL106" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DM106" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DN106" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="DO106" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW106" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="DX106" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="DY106" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DZ106" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EA106" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EB106" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC106" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="ED106" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EE106" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH106" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EI106" t="inlineStr"/>
+      <c r="EJ106" t="inlineStr"/>
+      <c r="EK106" t="inlineStr"/>
+      <c r="EL106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL106" headerRowCount="1">
-  <autoFilter ref="A1:EL106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL109" headerRowCount="1">
+  <autoFilter ref="A1:EL109"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL106"/>
+  <dimension ref="A1:EL109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE4" t="n">
         <v>0.91</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3177,7 +3177,7 @@
         <v>2.09</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE7" t="n">
         <v>0.18</v>
@@ -4577,7 +4577,7 @@
         <v>1.6</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5510,10 +5510,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6441,7 +6441,7 @@
         <v>1.6</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -7382,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE14" t="n">
         <v>1.82</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -9246,10 +9246,10 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9718,10 +9718,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10654,10 +10654,10 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -13438,10 +13438,10 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14374,10 +14374,10 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF29" t="n">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15286,7 +15286,7 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE31" t="n">
         <v>0.9</v>
@@ -16209,7 +16209,7 @@
         <v>1.64</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF33" t="n">
         <v>1.33</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -18454,10 +18454,10 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18913,7 +18913,7 @@
         <v>2.09</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -19822,7 +19822,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE41" t="n">
         <v>0.91</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20289,7 +20289,7 @@
         <v>1.6</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF42" t="n">
         <v>2.33</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21222,7 +21222,7 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE44" t="n">
         <v>0.6</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22617,7 +22617,7 @@
         <v>1.6</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -23062,7 +23062,7 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE48" t="n">
         <v>1</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23518,7 +23518,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE49" t="n">
         <v>0.6</v>
@@ -24441,7 +24441,7 @@
         <v>1.18</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF51" t="n">
         <v>1</v>
@@ -25369,7 +25369,7 @@
         <v>1.64</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26254,7 +26254,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE55" t="n">
         <v>0.6</v>
@@ -27190,7 +27190,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE57" t="n">
         <v>1</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28094,7 +28094,7 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE59" t="n">
         <v>1.7</v>
@@ -28569,7 +28569,7 @@
         <v>1</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF60" t="n">
         <v>1</v>
@@ -29041,7 +29041,7 @@
         <v>1.18</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF61" t="n">
         <v>0.6</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31806,7 +31806,7 @@
         <v>83</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE67" t="n">
         <v>0.18</v>
@@ -32246,10 +32246,10 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF68" t="n">
         <v>2.5</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE69" t="n">
         <v>1.7</v>
@@ -33177,7 +33177,7 @@
         <v>1</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF70" t="n">
         <v>1</v>
@@ -33649,7 +33649,7 @@
         <v>1.18</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -34593,7 +34593,7 @@
         <v>2.09</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF73" t="n">
         <v>2.29</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36454,7 +36454,7 @@
         <v>77</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE77" t="n">
         <v>0.9</v>
@@ -36926,7 +36926,7 @@
         <v>86</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE78" t="n">
         <v>1.7</v>
@@ -37398,7 +37398,7 @@
         <v>79</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE79" t="n">
         <v>0.18</v>
@@ -37849,7 +37849,7 @@
         <v>1.8</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF80" t="n">
         <v>1.71</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38321,7 +38321,7 @@
         <v>1</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -38793,7 +38793,7 @@
         <v>1.6</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF82" t="n">
         <v>1.25</v>
@@ -40186,7 +40186,7 @@
         <v>82</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE85" t="n">
         <v>1.82</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40653,7 +40653,7 @@
         <v>1.8</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF86" t="n">
         <v>1.88</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41578,10 +41578,10 @@
         <v>88</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF88" t="n">
         <v>2.38</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42494,7 +42494,7 @@
         <v>75</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE90" t="n">
         <v>0.9</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43910,7 +43910,7 @@
         <v>67</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE93" t="n">
         <v>0.91</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44369,7 +44369,7 @@
         <v>2.09</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF94" t="n">
         <v>2.22</v>
@@ -45313,7 +45313,7 @@
         <v>1.18</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF96" t="n">
         <v>1.11</v>
@@ -45769,7 +45769,7 @@
         <v>1.6</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DF97" t="n">
         <v>1.67</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46686,10 +46686,10 @@
         <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF99" t="n">
         <v>1.89</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47630,7 +47630,7 @@
         <v>90</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DE101" t="n">
         <v>0.18</v>
@@ -48553,7 +48553,7 @@
         <v>1.6</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DF103" t="n">
         <v>1.44</v>
@@ -49942,7 +49942,7 @@
         <v>75</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DE106" t="n">
         <v>1.82</v>
@@ -49975,7 +49975,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50062,6 +50062,1390 @@
       <c r="EJ106" t="inlineStr"/>
       <c r="EK106" t="inlineStr"/>
       <c r="EL106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>22</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>46066.70833333334</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" t="n">
+        <v>4</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>5</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>6</v>
+      </c>
+      <c r="T107" t="n">
+        <v>3</v>
+      </c>
+      <c r="U107" t="n">
+        <v>11</v>
+      </c>
+      <c r="V107" t="n">
+        <v>3</v>
+      </c>
+      <c r="W107" t="n">
+        <v>10</v>
+      </c>
+      <c r="X107" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>1861</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>913</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY107" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ107" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>95</v>
+      </c>
+      <c r="DB107" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC107" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD107" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DE107" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DF107" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DG107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH107" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DI107" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DJ107" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK107" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL107" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DM107" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN107" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="DO107" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW107" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="DX107" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="DY107" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="DZ107" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EA107" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EB107" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EF107" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EJ107" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EL107" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>22</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>46067.58333333334</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>4</v>
+      </c>
+      <c r="J108" t="n">
+        <v>9</v>
+      </c>
+      <c r="K108" t="n">
+        <v>3</v>
+      </c>
+      <c r="L108" t="n">
+        <v>12</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>4</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>7</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
+        <v>14</v>
+      </c>
+      <c r="T108" t="n">
+        <v>2</v>
+      </c>
+      <c r="U108" t="n">
+        <v>21</v>
+      </c>
+      <c r="V108" t="n">
+        <v>3</v>
+      </c>
+      <c r="W108" t="n">
+        <v>12</v>
+      </c>
+      <c r="X108" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>62</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY108" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ108" t="n">
+        <v>77</v>
+      </c>
+      <c r="DA108" t="n">
+        <v>91</v>
+      </c>
+      <c r="DB108" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC108" t="n">
+        <v>91</v>
+      </c>
+      <c r="DD108" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>24</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN108" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="DO108" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW108" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="DX108" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="DY108" t="inlineStr">
+        <is>
+          <t>10.74</t>
+        </is>
+      </c>
+      <c r="DZ108" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EC108" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EE108" t="inlineStr"/>
+      <c r="EF108" t="inlineStr"/>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr"/>
+      <c r="EJ108" t="inlineStr"/>
+      <c r="EK108" t="inlineStr"/>
+      <c r="EL108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>22</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>46067.67708333334</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>4</v>
+      </c>
+      <c r="J109" t="n">
+        <v>10</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3</v>
+      </c>
+      <c r="L109" t="n">
+        <v>13</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>9</v>
+      </c>
+      <c r="R109" t="n">
+        <v>5</v>
+      </c>
+      <c r="S109" t="n">
+        <v>17</v>
+      </c>
+      <c r="T109" t="n">
+        <v>13</v>
+      </c>
+      <c r="U109" t="n">
+        <v>26</v>
+      </c>
+      <c r="V109" t="n">
+        <v>18</v>
+      </c>
+      <c r="W109" t="n">
+        <v>13</v>
+      </c>
+      <c r="X109" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>77</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL109" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DM109" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN109" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DO109" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW109" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DX109" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>5.61</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EI109" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EJ109" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EK109" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EL109" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL109" headerRowCount="1">
-  <autoFilter ref="A1:EL109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL111" headerRowCount="1">
+  <autoFilter ref="A1:EL111"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL109"/>
+  <dimension ref="A1:EL111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.64</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE3" t="n">
         <v>1.82</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4113,7 +4113,7 @@
         <v>2.55</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE9" t="n">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10182,10 +10182,10 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13905,7 +13905,7 @@
         <v>1.8</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14830,10 +14830,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16662,7 +16662,7 @@
         <v>17</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE34" t="n">
         <v>0.91</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18009,7 +18009,7 @@
         <v>1.8</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19366,7 +19366,7 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE40" t="n">
         <v>0.6</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20761,7 +20761,7 @@
         <v>1.6</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21694,7 +21694,7 @@
         <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE45" t="n">
         <v>1</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23985,7 +23985,7 @@
         <v>1.6</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24438,7 +24438,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE51" t="n">
         <v>1.17</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24894,10 +24894,10 @@
         <v>88</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27649,7 +27649,7 @@
         <v>1.6</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28097,7 +28097,7 @@
         <v>1.82</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28566,7 +28566,7 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE60" t="n">
         <v>1.17</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -29038,7 +29038,7 @@
         <v>90</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE61" t="n">
         <v>0.73</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29494,10 +29494,10 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31809,7 +31809,7 @@
         <v>1.82</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32713,7 +32713,7 @@
         <v>1.83</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF69" t="n">
         <v>1.33</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33174,7 +33174,7 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE70" t="n">
         <v>0.73</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33646,7 +33646,7 @@
         <v>85</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE71" t="n">
         <v>1.17</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36006,7 +36006,7 @@
         <v>80</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE76" t="n">
         <v>1.82</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36929,7 +36929,7 @@
         <v>2.55</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF78" t="n">
         <v>2.57</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37401,7 +37401,7 @@
         <v>1.83</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF79" t="n">
         <v>1.57</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38318,7 +38318,7 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE81" t="n">
         <v>1.17</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39250,7 +39250,7 @@
         <v>64</v>
       </c>
       <c r="DD83" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE83" t="n">
         <v>0.9</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39725,7 +39725,7 @@
         <v>1.64</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF84" t="n">
         <v>1.5</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41106,7 +41106,7 @@
         <v>69</v>
       </c>
       <c r="DD87" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE87" t="n">
         <v>0.91</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42041,7 +42041,7 @@
         <v>2.09</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF89" t="n">
         <v>2.13</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43441,7 +43441,7 @@
         <v>1.64</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF92" t="n">
         <v>1.33</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44838,7 +44838,7 @@
         <v>67</v>
       </c>
       <c r="DD95" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE95" t="n">
         <v>1.82</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45310,7 +45310,7 @@
         <v>73</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE96" t="n">
         <v>1.17</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46238,10 +46238,10 @@
         <v>79</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="DF98" t="n">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47158,7 +47158,7 @@
         <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE100" t="n">
         <v>1</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47633,7 +47633,7 @@
         <v>2.55</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DF101" t="n">
         <v>2.44</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48127,7 +48127,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48583,7 +48583,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49039,7 +49039,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49503,7 +49503,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -51057,10 +51057,10 @@
         <v>9</v>
       </c>
       <c r="Y109" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z109" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
@@ -51444,6 +51444,950 @@
       <c r="EL109" t="inlineStr">
         <is>
           <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>22</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>46068.58333333334</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>5</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>6</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>2</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" t="n">
+        <v>12</v>
+      </c>
+      <c r="T110" t="n">
+        <v>7</v>
+      </c>
+      <c r="U110" t="n">
+        <v>14</v>
+      </c>
+      <c r="V110" t="n">
+        <v>9</v>
+      </c>
+      <c r="W110" t="n">
+        <v>15</v>
+      </c>
+      <c r="X110" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>ŠRC Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>, Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AC110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>63</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>91</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DN110" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DO110" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW110" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DX110" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="DY110" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EA110" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EB110" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC110" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED110" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EE110" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF110" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EG110" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EH110" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EI110" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EJ110" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EK110" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL110" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>22</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>46068.69791666666</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2</v>
+      </c>
+      <c r="J111" t="n">
+        <v>4</v>
+      </c>
+      <c r="K111" t="n">
+        <v>9</v>
+      </c>
+      <c r="L111" t="n">
+        <v>13</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3</v>
+      </c>
+      <c r="N111" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>4</v>
+      </c>
+      <c r="R111" t="n">
+        <v>5</v>
+      </c>
+      <c r="S111" t="n">
+        <v>3</v>
+      </c>
+      <c r="T111" t="n">
+        <v>9</v>
+      </c>
+      <c r="U111" t="n">
+        <v>7</v>
+      </c>
+      <c r="V111" t="n">
+        <v>14</v>
+      </c>
+      <c r="W111" t="n">
+        <v>13</v>
+      </c>
+      <c r="X111" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>100</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>150</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR111" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS111" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU111" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV111" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX111" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY111" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ111" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA111" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB111" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC111" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD111" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DE111" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DF111" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG111" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DH111" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DI111" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DJ111" t="n">
+        <v>67</v>
+      </c>
+      <c r="DK111" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL111" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM111" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DN111" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="DO111" t="n">
+        <v>22</v>
+      </c>
+      <c r="DP111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV111" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW111" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="DX111" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="DY111" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="DZ111" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EA111" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EB111" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC111" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED111" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EE111" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EF111" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EG111" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EH111" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI111" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EJ111" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EK111" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EL111" t="inlineStr">
+        <is>
+          <t>1.61</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL111" headerRowCount="1">
-  <autoFilter ref="A1:EL111"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL114" headerRowCount="1">
+  <autoFilter ref="A1:EL114"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL111"/>
+  <dimension ref="A1:EL114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE2" t="n">
         <v>0.25</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2705,7 +2705,7 @@
         <v>1.83</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v>1.8</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE8" t="n">
         <v>0.73</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5969,7 +5969,7 @@
         <v>2.09</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6438,7 +6438,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE12" t="n">
         <v>1.17</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6910,10 +6910,10 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7849,7 +7849,7 @@
         <v>1.8</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -8321,7 +8321,7 @@
         <v>2.09</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8790,10 +8790,10 @@
         <v>84</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -11126,10 +11126,10 @@
         <v>88</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF22" t="n">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11598,10 +11598,10 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF23" t="n">
         <v>1</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12502,10 +12502,10 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15289,7 +15289,7 @@
         <v>2.55</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -16206,7 +16206,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE33" t="n">
         <v>1.17</v>
@@ -16665,7 +16665,7 @@
         <v>1.17</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17134,10 +17134,10 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17574,7 +17574,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE36" t="n">
         <v>1</v>
@@ -19369,7 +19369,7 @@
         <v>1.17</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19825,7 +19825,7 @@
         <v>2.55</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -20286,7 +20286,7 @@
         <v>67</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE42" t="n">
         <v>1.17</v>
@@ -20758,7 +20758,7 @@
         <v>100</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE43" t="n">
         <v>1.82</v>
@@ -21225,7 +21225,7 @@
         <v>1.82</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22166,7 +22166,7 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE46" t="n">
         <v>1.82</v>
@@ -22614,7 +22614,7 @@
         <v>90</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE47" t="n">
         <v>0.73</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23521,7 +23521,7 @@
         <v>2.55</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF49" t="n">
         <v>2.25</v>
@@ -23982,7 +23982,7 @@
         <v>59</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE50" t="n">
         <v>1.82</v>
@@ -25366,7 +25366,7 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE53" t="n">
         <v>1.17</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25817,7 +25817,7 @@
         <v>1.8</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF54" t="n">
         <v>1.8</v>
@@ -26257,7 +26257,7 @@
         <v>1.83</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -26726,7 +26726,7 @@
         <v>74</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE56" t="n">
         <v>1.82</v>
@@ -27646,7 +27646,7 @@
         <v>80</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE58" t="n">
         <v>0.25</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29966,10 +29966,10 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF63" t="n">
         <v>1.67</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30441,7 +30441,7 @@
         <v>2.09</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF64" t="n">
         <v>2.17</v>
@@ -30910,7 +30910,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE65" t="n">
         <v>1.82</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34118,10 +34118,10 @@
         <v>73</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF72" t="n">
         <v>1.29</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35062,10 +35062,10 @@
         <v>71</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF74" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35534,7 +35534,7 @@
         <v>86</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE75" t="n">
         <v>1</v>
@@ -36457,7 +36457,7 @@
         <v>1.82</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF77" t="n">
         <v>2</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38790,7 +38790,7 @@
         <v>63</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE82" t="n">
         <v>1.17</v>
@@ -39253,7 +39253,7 @@
         <v>0.92</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF83" t="n">
         <v>0.86</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39722,7 +39722,7 @@
         <v>76</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE84" t="n">
         <v>1.82</v>
@@ -41109,7 +41109,7 @@
         <v>0.92</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF87" t="n">
         <v>0.88</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42497,7 +42497,7 @@
         <v>1.83</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF90" t="n">
         <v>1.75</v>
@@ -42966,7 +42966,7 @@
         <v>82</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE91" t="n">
         <v>1</v>
@@ -43438,7 +43438,7 @@
         <v>89</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE92" t="n">
         <v>0.25</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43913,7 +43913,7 @@
         <v>1.83</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF93" t="n">
         <v>1.89</v>
@@ -45766,7 +45766,7 @@
         <v>84</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DE97" t="n">
         <v>0.73</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -48094,10 +48094,10 @@
         <v>79</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="DF102" t="n">
         <v>1.5</v>
@@ -48127,7 +48127,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48550,7 +48550,7 @@
         <v>73</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DE103" t="n">
         <v>1.17</v>
@@ -48583,7 +48583,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49009,7 +49009,7 @@
         <v>2.09</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -49473,7 +49473,7 @@
         <v>1.8</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DF105" t="n">
         <v>1.67</v>
@@ -50423,7 +50423,7 @@
         <v>3.16</v>
       </c>
       <c r="DO107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -51815,7 +51815,7 @@
         <v>2.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP110" t="b">
         <v>0</v>
@@ -52388,6 +52388,1374 @@
       <c r="EL111" t="inlineStr">
         <is>
           <t>1.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>23</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>46073.70833333334</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" t="n">
+        <v>4</v>
+      </c>
+      <c r="J112" t="n">
+        <v>5</v>
+      </c>
+      <c r="K112" t="n">
+        <v>4</v>
+      </c>
+      <c r="L112" t="n">
+        <v>9</v>
+      </c>
+      <c r="M112" t="n">
+        <v>4</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>3</v>
+      </c>
+      <c r="R112" t="n">
+        <v>3</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="n">
+        <v>4</v>
+      </c>
+      <c r="U112" t="n">
+        <v>8</v>
+      </c>
+      <c r="V112" t="n">
+        <v>7</v>
+      </c>
+      <c r="W112" t="n">
+        <v>17</v>
+      </c>
+      <c r="X112" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>146</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>130</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR112" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS112" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU112" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV112" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX112" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY112" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ112" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA112" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB112" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC112" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD112" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DE112" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DF112" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG112" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DH112" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DI112" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ112" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK112" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL112" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DM112" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DN112" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DO112" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW112" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="DX112" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="DY112" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="DZ112" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EA112" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EB112" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC112" t="inlineStr"/>
+      <c r="ED112" t="inlineStr"/>
+      <c r="EE112" t="inlineStr"/>
+      <c r="EF112" t="inlineStr"/>
+      <c r="EG112" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EH112" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EI112" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EJ112" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EK112" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EL112" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>23</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>46074.58333333334</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" t="n">
+        <v>2</v>
+      </c>
+      <c r="J113" t="n">
+        <v>5</v>
+      </c>
+      <c r="K113" t="n">
+        <v>4</v>
+      </c>
+      <c r="L113" t="n">
+        <v>9</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>3</v>
+      </c>
+      <c r="R113" t="n">
+        <v>4</v>
+      </c>
+      <c r="S113" t="n">
+        <v>3</v>
+      </c>
+      <c r="T113" t="n">
+        <v>11</v>
+      </c>
+      <c r="U113" t="n">
+        <v>6</v>
+      </c>
+      <c r="V113" t="n">
+        <v>15</v>
+      </c>
+      <c r="W113" t="n">
+        <v>15</v>
+      </c>
+      <c r="X113" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>Stadion Aldo Drosina</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>Marsovo polje, Pula</t>
+        </is>
+      </c>
+      <c r="AC113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>1875</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV113" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW113" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX113" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY113" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ113" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR113" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS113" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU113" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV113" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX113" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY113" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ113" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA113" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB113" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC113" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD113" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DE113" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DF113" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG113" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DH113" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI113" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DJ113" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK113" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL113" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM113" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN113" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="DO113" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW113" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="DX113" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="DY113" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="DZ113" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EA113" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="EB113" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EC113" t="inlineStr"/>
+      <c r="ED113" t="inlineStr"/>
+      <c r="EE113" t="inlineStr"/>
+      <c r="EF113" t="inlineStr"/>
+      <c r="EG113" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH113" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EI113" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ113" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EK113" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EL113" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>23</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>46074.67708333334</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>4</v>
+      </c>
+      <c r="J114" t="n">
+        <v>3</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" t="n">
+        <v>6</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>6</v>
+      </c>
+      <c r="R114" t="n">
+        <v>5</v>
+      </c>
+      <c r="S114" t="n">
+        <v>7</v>
+      </c>
+      <c r="T114" t="n">
+        <v>4</v>
+      </c>
+      <c r="U114" t="n">
+        <v>13</v>
+      </c>
+      <c r="V114" t="n">
+        <v>9</v>
+      </c>
+      <c r="W114" t="n">
+        <v>8</v>
+      </c>
+      <c r="X114" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>Stadion Kranjčevićeva</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>Kranjčevićeva 4, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>1859</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR114" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS114" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU114" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX114" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY114" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ114" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA114" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB114" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC114" t="n">
+        <v>91</v>
+      </c>
+      <c r="DD114" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE114" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DF114" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG114" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH114" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI114" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DJ114" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK114" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL114" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM114" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN114" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DO114" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW114" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="DX114" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="DY114" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="DZ114" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EA114" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EB114" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC114" t="inlineStr"/>
+      <c r="ED114" t="inlineStr"/>
+      <c r="EE114" t="inlineStr"/>
+      <c r="EF114" t="inlineStr"/>
+      <c r="EG114" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH114" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EI114" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EJ114" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EK114" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL114" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL114" headerRowCount="1">
-  <autoFilter ref="A1:EL114"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL116" headerRowCount="1">
+  <autoFilter ref="A1:EL116"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL114"/>
+  <dimension ref="A1:EL116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2233,7 +2233,7 @@
         <v>0.92</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE5" t="n">
         <v>1.17</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE6" t="n">
         <v>1.09</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         <v>0.92</v>
       </c>
       <c r="DE9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5966,7 +5966,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE11" t="n">
         <v>1.09</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7385,7 +7385,7 @@
         <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7846,7 +7846,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE15" t="n">
         <v>0.55</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8318,7 +8318,7 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE16" t="n">
         <v>0.92</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -12046,10 +12046,10 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12974,10 +12974,10 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE26" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13902,7 +13902,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE28" t="n">
         <v>1.82</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15734,10 +15734,10 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF32" t="n">
         <v>2.5</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17577,7 +17577,7 @@
         <v>1.55</v>
       </c>
       <c r="DE36" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF36" t="n">
         <v>0.67</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18006,7 +18006,7 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE37" t="n">
         <v>0.25</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18910,7 +18910,7 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE39" t="n">
         <v>0.73</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21697,7 +21697,7 @@
         <v>1.17</v>
       </c>
       <c r="DE45" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22169,7 +22169,7 @@
         <v>1.75</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF46" t="n">
         <v>1.75</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23065,7 +23065,7 @@
         <v>1.82</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF48" t="n">
         <v>2.25</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25814,7 +25814,7 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE54" t="n">
         <v>0.92</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26729,7 +26729,7 @@
         <v>1.55</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27193,7 +27193,7 @@
         <v>2.55</v>
       </c>
       <c r="DE57" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF57" t="n">
         <v>2.4</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30438,7 +30438,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE64" t="n">
         <v>0.55</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30913,7 +30913,7 @@
         <v>1.45</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF65" t="n">
         <v>1.83</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31342,10 +31342,10 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE66" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34590,7 +34590,7 @@
         <v>64</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE73" t="n">
         <v>1.17</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35537,7 +35537,7 @@
         <v>1.75</v>
       </c>
       <c r="DE75" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF75" t="n">
         <v>1.57</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36009,7 +36009,7 @@
         <v>1.17</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF76" t="n">
         <v>1.25</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37846,7 +37846,7 @@
         <v>86</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE80" t="n">
         <v>0.73</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40189,7 +40189,7 @@
         <v>1.82</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF85" t="n">
         <v>2.13</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40650,7 +40650,7 @@
         <v>88</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE86" t="n">
         <v>1.17</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42038,7 +42038,7 @@
         <v>82</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE89" t="n">
         <v>0.25</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42969,7 +42969,7 @@
         <v>1.45</v>
       </c>
       <c r="DE91" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF91" t="n">
         <v>1.88</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44366,7 +44366,7 @@
         <v>84</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE94" t="n">
         <v>1.17</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44841,7 +44841,7 @@
         <v>0.92</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF95" t="n">
         <v>0.89</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47161,7 +47161,7 @@
         <v>0.92</v>
       </c>
       <c r="DE100" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DF100" t="n">
         <v>0.8</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49006,7 +49006,7 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DE104" t="n">
         <v>0.92</v>
@@ -49039,7 +49039,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49470,7 +49470,7 @@
         <v>89</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE105" t="n">
         <v>0.55</v>
@@ -49503,7 +49503,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49945,7 +49945,7 @@
         <v>1.83</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DF106" t="n">
         <v>1.8</v>
@@ -49975,7 +49975,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50895,7 +50895,7 @@
         <v>3.34</v>
       </c>
       <c r="DO108" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51343,7 +51343,7 @@
         <v>2.93</v>
       </c>
       <c r="DO109" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -52287,7 +52287,7 @@
         <v>3.25</v>
       </c>
       <c r="DO111" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -53240,32 +53240,32 @@
       </c>
       <c r="DW113" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="DX113" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="DY113" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="DZ113" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EA113" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="EB113" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EC113" t="inlineStr"/>
@@ -53274,32 +53274,32 @@
       <c r="EF113" t="inlineStr"/>
       <c r="EG113" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EH113" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EI113" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EJ113" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EK113" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EL113" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.56</t>
         </is>
       </c>
     </row>
@@ -53696,68 +53696,988 @@
       </c>
       <c r="DW114" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="DX114" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="DY114" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="DZ114" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EA114" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EB114" t="inlineStr">
         <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EC114" t="inlineStr"/>
-      <c r="ED114" t="inlineStr"/>
-      <c r="EE114" t="inlineStr"/>
-      <c r="EF114" t="inlineStr"/>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC114" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED114" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EE114" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EF114" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
       <c r="EG114" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EH114" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EI114" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EJ114" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EK114" t="inlineStr">
         <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EL114" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>23</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>46075.58333333334</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>4</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>5</v>
+      </c>
+      <c r="L115" t="n">
+        <v>5</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>2</v>
+      </c>
+      <c r="R115" t="n">
+        <v>8</v>
+      </c>
+      <c r="S115" t="n">
+        <v>4</v>
+      </c>
+      <c r="T115" t="n">
+        <v>10</v>
+      </c>
+      <c r="U115" t="n">
+        <v>6</v>
+      </c>
+      <c r="V115" t="n">
+        <v>18</v>
+      </c>
+      <c r="W115" t="n">
+        <v>10</v>
+      </c>
+      <c r="X115" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>75</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>136</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DN115" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="DO115" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW115" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="DX115" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="DY115" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="DZ115" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr"/>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr"/>
+      <c r="EF115" t="inlineStr"/>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EH115" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EI115" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EJ115" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>23</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>46075.69791666666</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>6</v>
+      </c>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
+        <v>8</v>
+      </c>
+      <c r="M116" t="n">
+        <v>2</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>7</v>
+      </c>
+      <c r="R116" t="n">
+        <v>3</v>
+      </c>
+      <c r="S116" t="n">
+        <v>4</v>
+      </c>
+      <c r="T116" t="n">
+        <v>3</v>
+      </c>
+      <c r="U116" t="n">
+        <v>11</v>
+      </c>
+      <c r="V116" t="n">
+        <v>6</v>
+      </c>
+      <c r="W116" t="n">
+        <v>10</v>
+      </c>
+      <c r="X116" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>77</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DN116" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="DO116" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW116" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="DX116" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="DY116" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="DZ116" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="EB116" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC116" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="EL114" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+      <c r="EH116" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr"/>
+      <c r="EJ116" t="inlineStr"/>
+      <c r="EK116" t="inlineStr"/>
+      <c r="EL116" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -54305,10 +54305,10 @@
         <v>14</v>
       </c>
       <c r="Y116" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z116" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL116" headerRowCount="1">
-  <autoFilter ref="A1:EL116"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL119" headerRowCount="1">
+  <autoFilter ref="A1:EL119"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL116"/>
+  <dimension ref="A1:EL119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.75</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE3" t="n">
         <v>1.92</v>
@@ -3177,7 +3177,7 @@
         <v>2.17</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE6" t="n">
         <v>1.09</v>
@@ -4113,7 +4113,7 @@
         <v>2.55</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE9" t="n">
         <v>0.91</v>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE10" t="n">
         <v>1.17</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6441,7 +6441,7 @@
         <v>1.55</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7846,7 +7846,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE15" t="n">
         <v>0.55</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9246,7 +9246,7 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE18" t="n">
         <v>0.73</v>
@@ -9721,7 +9721,7 @@
         <v>2.55</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -10182,10 +10182,10 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12046,7 +12046,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE24" t="n">
         <v>1.92</v>
@@ -13438,10 +13438,10 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13902,10 +13902,10 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14830,10 +14830,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -18006,10 +18006,10 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18457,7 +18457,7 @@
         <v>1.83</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20761,7 +20761,7 @@
         <v>1.55</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21222,7 +21222,7 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE44" t="n">
         <v>0.55</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -23062,7 +23062,7 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE48" t="n">
         <v>0.91</v>
@@ -23985,7 +23985,7 @@
         <v>1.45</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24897,7 +24897,7 @@
         <v>1.17</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -25369,7 +25369,7 @@
         <v>1.75</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -25814,7 +25814,7 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE54" t="n">
         <v>0.92</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27649,7 +27649,7 @@
         <v>1.45</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28094,10 +28094,10 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28566,7 +28566,7 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE60" t="n">
         <v>1.17</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -29497,7 +29497,7 @@
         <v>1.17</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31342,7 +31342,7 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE66" t="n">
         <v>0.91</v>
@@ -31806,10 +31806,10 @@
         <v>83</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32713,7 +32713,7 @@
         <v>1.83</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF69" t="n">
         <v>1.33</v>
@@ -33174,7 +33174,7 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE70" t="n">
         <v>0.73</v>
@@ -33649,7 +33649,7 @@
         <v>1.17</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36454,7 +36454,7 @@
         <v>77</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE77" t="n">
         <v>1.09</v>
@@ -36929,7 +36929,7 @@
         <v>2.55</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF78" t="n">
         <v>2.57</v>
@@ -37401,7 +37401,7 @@
         <v>1.83</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF79" t="n">
         <v>1.57</v>
@@ -37846,7 +37846,7 @@
         <v>86</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE80" t="n">
         <v>0.73</v>
@@ -38318,10 +38318,10 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39250,7 +39250,7 @@
         <v>64</v>
       </c>
       <c r="DD83" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE83" t="n">
         <v>1.09</v>
@@ -39725,7 +39725,7 @@
         <v>1.75</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF84" t="n">
         <v>1.5</v>
@@ -40186,7 +40186,7 @@
         <v>82</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE85" t="n">
         <v>1.92</v>
@@ -40650,10 +40650,10 @@
         <v>88</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF86" t="n">
         <v>1.88</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41106,7 +41106,7 @@
         <v>69</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE87" t="n">
         <v>0.92</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42041,7 +42041,7 @@
         <v>2.17</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF89" t="n">
         <v>2.13</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43441,7 +43441,7 @@
         <v>1.75</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF92" t="n">
         <v>1.33</v>
@@ -44369,7 +44369,7 @@
         <v>2.17</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF94" t="n">
         <v>2.22</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44838,7 +44838,7 @@
         <v>67</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE95" t="n">
         <v>1.92</v>
@@ -46241,7 +46241,7 @@
         <v>1.17</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF98" t="n">
         <v>1</v>
@@ -46686,7 +46686,7 @@
         <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE99" t="n">
         <v>1.17</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47158,7 +47158,7 @@
         <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE100" t="n">
         <v>0.91</v>
@@ -47633,7 +47633,7 @@
         <v>2.55</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF101" t="n">
         <v>2.44</v>
@@ -48553,7 +48553,7 @@
         <v>1.55</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF103" t="n">
         <v>1.44</v>
@@ -48583,7 +48583,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49039,7 +49039,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49470,7 +49470,7 @@
         <v>89</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE105" t="n">
         <v>0.55</v>
@@ -49503,7 +49503,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -50390,7 +50390,7 @@
         <v>90</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DE107" t="n">
         <v>0.73</v>
@@ -50865,7 +50865,7 @@
         <v>2.55</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="DF108" t="n">
         <v>2.5</v>
@@ -51785,7 +51785,7 @@
         <v>1.17</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF110" t="n">
         <v>1.18</v>
@@ -52254,10 +52254,10 @@
         <v>67</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DF111" t="n">
         <v>1</v>
@@ -52287,7 +52287,7 @@
         <v>3.25</v>
       </c>
       <c r="DO111" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52759,7 +52759,7 @@
         <v>2.83</v>
       </c>
       <c r="DO112" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -54102,7 +54102,7 @@
         <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DE115" t="n">
         <v>1.92</v>
@@ -54678,6 +54678,1390 @@
       <c r="EJ116" t="inlineStr"/>
       <c r="EK116" t="inlineStr"/>
       <c r="EL116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>24</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>46080.70833333334</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>7</v>
+      </c>
+      <c r="L117" t="n">
+        <v>12</v>
+      </c>
+      <c r="M117" t="n">
+        <v>3</v>
+      </c>
+      <c r="N117" t="n">
+        <v>3</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>4</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="n">
+        <v>8</v>
+      </c>
+      <c r="U117" t="n">
+        <v>19</v>
+      </c>
+      <c r="V117" t="n">
+        <v>11</v>
+      </c>
+      <c r="W117" t="n">
+        <v>7</v>
+      </c>
+      <c r="X117" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>1861</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>923</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU117" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV117" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX117" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY117" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ117" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA117" t="n">
+        <v>87</v>
+      </c>
+      <c r="DB117" t="n">
+        <v>53</v>
+      </c>
+      <c r="DC117" t="n">
+        <v>92</v>
+      </c>
+      <c r="DD117" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DE117" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DF117" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DG117" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH117" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI117" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ117" t="n">
+        <v>31</v>
+      </c>
+      <c r="DK117" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL117" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DM117" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN117" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO117" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW117" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="DX117" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="DZ117" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EA117" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EB117" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC117" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED117" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EE117" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EG117" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EJ117" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EK117" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EL117" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>24</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>46081.58333333334</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" t="n">
+        <v>7</v>
+      </c>
+      <c r="K118" t="n">
+        <v>3</v>
+      </c>
+      <c r="L118" t="n">
+        <v>10</v>
+      </c>
+      <c r="M118" t="n">
+        <v>4</v>
+      </c>
+      <c r="N118" t="n">
+        <v>2</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>4</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>9</v>
+      </c>
+      <c r="T118" t="n">
+        <v>6</v>
+      </c>
+      <c r="U118" t="n">
+        <v>13</v>
+      </c>
+      <c r="V118" t="n">
+        <v>7</v>
+      </c>
+      <c r="W118" t="n">
+        <v>16</v>
+      </c>
+      <c r="X118" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1864</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>73</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>145</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU118" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV118" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX118" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY118" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ118" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA118" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB118" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC118" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD118" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DE118" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DF118" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DG118" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH118" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DI118" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DJ118" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK118" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL118" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DM118" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DN118" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="DO118" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW118" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="DX118" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="DZ118" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EA118" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EB118" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC118" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="ED118" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EE118" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EF118" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EG118" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EH118" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EI118" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EJ118" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EK118" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL118" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>24</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>46081.69791666666</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="n">
+        <v>14</v>
+      </c>
+      <c r="L119" t="n">
+        <v>15</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>2</v>
+      </c>
+      <c r="R119" t="n">
+        <v>5</v>
+      </c>
+      <c r="S119" t="n">
+        <v>4</v>
+      </c>
+      <c r="T119" t="n">
+        <v>18</v>
+      </c>
+      <c r="U119" t="n">
+        <v>6</v>
+      </c>
+      <c r="V119" t="n">
+        <v>23</v>
+      </c>
+      <c r="W119" t="n">
+        <v>11</v>
+      </c>
+      <c r="X119" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>68</v>
+      </c>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>103</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU119" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV119" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX119" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY119" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ119" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA119" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB119" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC119" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD119" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG119" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DH119" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DI119" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ119" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK119" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL119" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DM119" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DN119" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DO119" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW119" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="DX119" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="DY119" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DZ119" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EA119" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED119" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF119" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EH119" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI119" t="inlineStr"/>
+      <c r="EJ119" t="inlineStr"/>
+      <c r="EK119" t="inlineStr"/>
+      <c r="EL119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL119" headerRowCount="1">
-  <autoFilter ref="A1:EL119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL121" headerRowCount="1">
+  <autoFilter ref="A1:EL121"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL119"/>
+  <dimension ref="A1:EL121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE4" t="n">
         <v>0.92</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3641,7 +3641,7 @@
         <v>1.58</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE7" t="n">
         <v>0.23</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4577,7 +4577,7 @@
         <v>1.45</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5969,7 +5969,7 @@
         <v>2.17</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6913,7 +6913,7 @@
         <v>1.75</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7382,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE14" t="n">
         <v>1.92</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8793,7 +8793,7 @@
         <v>1.55</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9249,7 +9249,7 @@
         <v>1.92</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9718,7 +9718,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE19" t="n">
         <v>1.08</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10654,7 +10654,7 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE21" t="n">
         <v>1.17</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11129,7 +11129,7 @@
         <v>1.45</v>
       </c>
       <c r="DE22" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF22" t="n">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14374,10 +14374,10 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF29" t="n">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15286,10 +15286,10 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE31" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18454,7 +18454,7 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE38" t="n">
         <v>1.08</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18913,7 +18913,7 @@
         <v>2.17</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19822,7 +19822,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE41" t="n">
         <v>0.92</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22617,7 +22617,7 @@
         <v>1.55</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23518,7 +23518,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE49" t="n">
         <v>0.55</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26254,7 +26254,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE55" t="n">
         <v>0.55</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27190,7 +27190,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE57" t="n">
         <v>0.91</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -29041,7 +29041,7 @@
         <v>1.17</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF61" t="n">
         <v>0.6</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32246,7 +32246,7 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE68" t="n">
         <v>1.17</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE69" t="n">
         <v>1.75</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33177,7 +33177,7 @@
         <v>1.08</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF70" t="n">
         <v>1</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36457,7 +36457,7 @@
         <v>1.92</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF77" t="n">
         <v>2</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36926,7 +36926,7 @@
         <v>86</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE78" t="n">
         <v>1.75</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37398,7 +37398,7 @@
         <v>79</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE79" t="n">
         <v>0.23</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37849,7 +37849,7 @@
         <v>1.58</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF80" t="n">
         <v>1.71</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39253,7 +39253,7 @@
         <v>1.08</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF83" t="n">
         <v>0.86</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41578,10 +41578,10 @@
         <v>88</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF88" t="n">
         <v>2.38</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42494,10 +42494,10 @@
         <v>75</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF90" t="n">
         <v>1.75</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43910,7 +43910,7 @@
         <v>67</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE93" t="n">
         <v>0.92</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45769,7 +45769,7 @@
         <v>1.45</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF97" t="n">
         <v>1.67</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47630,7 +47630,7 @@
         <v>90</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE101" t="n">
         <v>0.23</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48097,7 +48097,7 @@
         <v>1.75</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF102" t="n">
         <v>1.5</v>
@@ -48127,7 +48127,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -49942,7 +49942,7 @@
         <v>75</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE106" t="n">
         <v>1.92</v>
@@ -49975,7 +49975,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50393,7 +50393,7 @@
         <v>1.92</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DF107" t="n">
         <v>1.7</v>
@@ -50423,7 +50423,7 @@
         <v>3.16</v>
       </c>
       <c r="DO107" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50862,7 +50862,7 @@
         <v>91</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DE108" t="n">
         <v>1.08</v>
@@ -50895,7 +50895,7 @@
         <v>3.34</v>
       </c>
       <c r="DO108" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51310,7 +51310,7 @@
         <v>64</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DE109" t="n">
         <v>1.17</v>
@@ -51343,7 +51343,7 @@
         <v>2.93</v>
       </c>
       <c r="DO109" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51815,7 +51815,7 @@
         <v>2.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP110" t="b">
         <v>0</v>
@@ -53185,7 +53185,7 @@
         <v>1.45</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DF113" t="n">
         <v>1.6</v>
@@ -53215,7 +53215,7 @@
         <v>2.9</v>
       </c>
       <c r="DO113" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53671,7 +53671,7 @@
         <v>2.83</v>
       </c>
       <c r="DO114" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54135,7 +54135,7 @@
         <v>3.48</v>
       </c>
       <c r="DO115" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54591,7 +54591,7 @@
         <v>3.48</v>
       </c>
       <c r="DO116" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55225,10 +55225,10 @@
         <v>13</v>
       </c>
       <c r="Y118" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z118" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>1</v>
       </c>
       <c r="CR118" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CS118" t="n">
         <v>21</v>
@@ -55463,7 +55463,7 @@
         <v>2</v>
       </c>
       <c r="CY118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ118" t="n">
         <v>46</v>
@@ -56000,27 +56000,27 @@
       </c>
       <c r="DW119" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="DX119" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="DY119" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="DZ119" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EA119" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="EB119" t="inlineStr">
@@ -56030,12 +56030,12 @@
       </c>
       <c r="EC119" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="ED119" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EE119" t="inlineStr">
@@ -56045,23 +56045,951 @@
       </c>
       <c r="EF119" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EG119" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EH119" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EI119" t="inlineStr"/>
-      <c r="EJ119" t="inlineStr"/>
-      <c r="EK119" t="inlineStr"/>
-      <c r="EL119" t="inlineStr"/>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EI119" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EJ119" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EK119" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EL119" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>24</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>46082.58333333334</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="n">
+        <v>4</v>
+      </c>
+      <c r="L120" t="n">
+        <v>5</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4</v>
+      </c>
+      <c r="N120" t="n">
+        <v>2</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>2</v>
+      </c>
+      <c r="R120" t="n">
+        <v>3</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="n">
+        <v>5</v>
+      </c>
+      <c r="U120" t="n">
+        <v>7</v>
+      </c>
+      <c r="V120" t="n">
+        <v>8</v>
+      </c>
+      <c r="W120" t="n">
+        <v>11</v>
+      </c>
+      <c r="X120" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>4986</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>133</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU120" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV120" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX120" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY120" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ120" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA120" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB120" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC120" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD120" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DE120" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF120" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG120" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DH120" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DI120" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DJ120" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK120" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL120" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DM120" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DN120" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="DO120" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP120" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ120" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW120" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DX120" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="DY120" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="DZ120" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EA120" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="EB120" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED120" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF120" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EH120" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EI120" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EJ120" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EK120" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EL120" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>24</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>46082.67708333334</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2</v>
+      </c>
+      <c r="I121" t="n">
+        <v>6</v>
+      </c>
+      <c r="J121" t="n">
+        <v>5</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3</v>
+      </c>
+      <c r="L121" t="n">
+        <v>8</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>2</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>7</v>
+      </c>
+      <c r="R121" t="n">
+        <v>4</v>
+      </c>
+      <c r="S121" t="n">
+        <v>11</v>
+      </c>
+      <c r="T121" t="n">
+        <v>6</v>
+      </c>
+      <c r="U121" t="n">
+        <v>18</v>
+      </c>
+      <c r="V121" t="n">
+        <v>10</v>
+      </c>
+      <c r="W121" t="n">
+        <v>8</v>
+      </c>
+      <c r="X121" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>69</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU121" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV121" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX121" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY121" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ121" t="n">
+        <v>64</v>
+      </c>
+      <c r="DA121" t="n">
+        <v>91</v>
+      </c>
+      <c r="DB121" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC121" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD121" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF121" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DG121" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DH121" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DI121" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ121" t="n">
+        <v>37</v>
+      </c>
+      <c r="DK121" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL121" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DM121" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN121" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="DO121" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW121" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="DX121" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="DY121" t="inlineStr">
+        <is>
+          <t>10.68</t>
+        </is>
+      </c>
+      <c r="DZ121" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EA121" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EB121" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EC121" t="inlineStr"/>
+      <c r="ED121" t="inlineStr"/>
+      <c r="EE121" t="inlineStr"/>
+      <c r="EF121" t="inlineStr"/>
+      <c r="EG121" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH121" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EI121" t="inlineStr"/>
+      <c r="EJ121" t="inlineStr"/>
+      <c r="EK121" t="inlineStr"/>
+      <c r="EL121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -56146,13 +56146,13 @@
         <v>5</v>
       </c>
       <c r="T120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U120" t="n">
         <v>7</v>
       </c>
       <c r="V120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W120" t="n">
         <v>11</v>
@@ -56327,10 +56327,10 @@
         <v>1.02</v>
       </c>
       <c r="CA120" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="CB120" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="CC120" t="n">
         <v>0</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL121" headerRowCount="1">
-  <autoFilter ref="A1:EL121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL123" headerRowCount="1">
+  <autoFilter ref="A1:EL123"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL121"/>
+  <dimension ref="A1:EL123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE8" t="n">
         <v>0.67</v>
@@ -7849,7 +7849,7 @@
         <v>1.58</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -11126,7 +11126,7 @@
         <v>88</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE22" t="n">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12505,7 +12505,7 @@
         <v>1.75</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -16662,7 +16662,7 @@
         <v>17</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE34" t="n">
         <v>0.92</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17134,10 +17134,10 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -19366,10 +19366,10 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20286,7 +20286,7 @@
         <v>67</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE42" t="n">
         <v>1.17</v>
@@ -21225,7 +21225,7 @@
         <v>1.92</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21694,7 +21694,7 @@
         <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE45" t="n">
         <v>0.91</v>
@@ -23521,7 +23521,7 @@
         <v>2.58</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF49" t="n">
         <v>2.25</v>
@@ -23982,7 +23982,7 @@
         <v>59</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE50" t="n">
         <v>1.75</v>
@@ -24438,7 +24438,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE51" t="n">
         <v>1.17</v>
@@ -24894,7 +24894,7 @@
         <v>88</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE52" t="n">
         <v>1.75</v>
@@ -26257,7 +26257,7 @@
         <v>1.92</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -27646,7 +27646,7 @@
         <v>80</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE58" t="n">
         <v>0.23</v>
@@ -29038,7 +29038,7 @@
         <v>90</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE61" t="n">
         <v>0.67</v>
@@ -29494,7 +29494,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE62" t="n">
         <v>0.23</v>
@@ -30441,7 +30441,7 @@
         <v>2.17</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF64" t="n">
         <v>2.17</v>
@@ -30910,7 +30910,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE65" t="n">
         <v>1.92</v>
@@ -33646,7 +33646,7 @@
         <v>85</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE71" t="n">
         <v>1.08</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34121,7 +34121,7 @@
         <v>1.55</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF72" t="n">
         <v>1.29</v>
@@ -35062,7 +35062,7 @@
         <v>71</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE74" t="n">
         <v>0.92</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36006,7 +36006,7 @@
         <v>80</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE76" t="n">
         <v>1.92</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -42966,7 +42966,7 @@
         <v>82</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE91" t="n">
         <v>0.91</v>
@@ -45310,7 +45310,7 @@
         <v>73</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE96" t="n">
         <v>1.17</v>
@@ -45766,7 +45766,7 @@
         <v>84</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE97" t="n">
         <v>0.67</v>
@@ -46238,7 +46238,7 @@
         <v>79</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE98" t="n">
         <v>1.75</v>
@@ -49473,7 +49473,7 @@
         <v>1.58</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF105" t="n">
         <v>1.67</v>
@@ -51782,7 +51782,7 @@
         <v>91</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DE110" t="n">
         <v>0.23</v>
@@ -53182,7 +53182,7 @@
         <v>75</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="DE113" t="n">
         <v>1</v>
@@ -53215,7 +53215,7 @@
         <v>2.9</v>
       </c>
       <c r="DO113" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53641,7 +53641,7 @@
         <v>1.75</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="DF114" t="n">
         <v>1.64</v>
@@ -55039,7 +55039,7 @@
         <v>2.92</v>
       </c>
       <c r="DO117" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -56990,6 +56990,902 @@
       <c r="EJ121" t="inlineStr"/>
       <c r="EK121" t="inlineStr"/>
       <c r="EL121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>25</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>46087.70833333334</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>7</v>
+      </c>
+      <c r="K122" t="n">
+        <v>2</v>
+      </c>
+      <c r="L122" t="n">
+        <v>9</v>
+      </c>
+      <c r="M122" t="n">
+        <v>2</v>
+      </c>
+      <c r="N122" t="n">
+        <v>4</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>2</v>
+      </c>
+      <c r="R122" t="n">
+        <v>3</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="n">
+        <v>6</v>
+      </c>
+      <c r="U122" t="n">
+        <v>12</v>
+      </c>
+      <c r="V122" t="n">
+        <v>9</v>
+      </c>
+      <c r="W122" t="n">
+        <v>15</v>
+      </c>
+      <c r="X122" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Stadion Aldo Drosina</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Marsovo polje, Pula</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>1864</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>87</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW122" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="DX122" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="DZ122" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EA122" t="inlineStr">
+        <is>
+          <t>4.32</t>
+        </is>
+      </c>
+      <c r="EB122" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC122" t="inlineStr"/>
+      <c r="ED122" t="inlineStr"/>
+      <c r="EE122" t="inlineStr"/>
+      <c r="EF122" t="inlineStr"/>
+      <c r="EG122" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EH122" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EI122" t="inlineStr"/>
+      <c r="EJ122" t="inlineStr"/>
+      <c r="EK122" t="inlineStr"/>
+      <c r="EL122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>25</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>46088.58333333334</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>2</v>
+      </c>
+      <c r="K123" t="n">
+        <v>5</v>
+      </c>
+      <c r="L123" t="n">
+        <v>7</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2</v>
+      </c>
+      <c r="N123" t="n">
+        <v>6</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>3</v>
+      </c>
+      <c r="R123" t="n">
+        <v>2</v>
+      </c>
+      <c r="S123" t="n">
+        <v>4</v>
+      </c>
+      <c r="T123" t="n">
+        <v>10</v>
+      </c>
+      <c r="U123" t="n">
+        <v>7</v>
+      </c>
+      <c r="V123" t="n">
+        <v>12</v>
+      </c>
+      <c r="W123" t="n">
+        <v>13</v>
+      </c>
+      <c r="X123" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>ŠRC Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>, Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>35</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV123" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY123" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ123" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC123" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD123" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DE123" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DF123" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG123" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH123" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DI123" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DJ123" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK123" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DM123" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DN123" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DO123" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW123" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="DX123" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="DZ123" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EA123" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr"/>
+      <c r="ED123" t="inlineStr"/>
+      <c r="EE123" t="inlineStr"/>
+      <c r="EF123" t="inlineStr"/>
+      <c r="EG123" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EL123" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL123" headerRowCount="1">
-  <autoFilter ref="A1:EL123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL126" headerRowCount="1">
+  <autoFilter ref="A1:EL126"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL123"/>
+  <dimension ref="A1:EL126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE2" t="n">
         <v>0.23</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2233,7 +2233,7 @@
         <v>1.08</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE5" t="n">
         <v>1.08</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         <v>1.08</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         <v>1.92</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5966,7 +5966,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE11" t="n">
         <v>1</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6438,7 +6438,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE12" t="n">
         <v>1.08</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6910,7 +6910,7 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7385,7 +7385,7 @@
         <v>1.92</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8318,7 +8318,7 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE16" t="n">
         <v>0.92</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         <v>84</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE17" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10657,7 +10657,7 @@
         <v>1.92</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11598,7 +11598,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE23" t="n">
         <v>0.92</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12049,7 +12049,7 @@
         <v>1.58</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12502,7 +12502,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE25" t="n">
         <v>0.75</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12974,10 +12974,10 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15734,10 +15734,10 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF32" t="n">
         <v>2.5</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16206,10 +16206,10 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF33" t="n">
         <v>1.33</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17574,10 +17574,10 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF36" t="n">
         <v>0.67</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18910,7 +18910,7 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE39" t="n">
         <v>0.67</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20289,7 +20289,7 @@
         <v>1.33</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF42" t="n">
         <v>2.33</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20758,7 +20758,7 @@
         <v>100</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE43" t="n">
         <v>1.75</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21697,7 +21697,7 @@
         <v>1.15</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22166,10 +22166,10 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF46" t="n">
         <v>1.75</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22614,7 +22614,7 @@
         <v>90</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE47" t="n">
         <v>0.67</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23065,7 +23065,7 @@
         <v>1.92</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF48" t="n">
         <v>2.25</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24441,7 +24441,7 @@
         <v>1.15</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF51" t="n">
         <v>1</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25366,7 +25366,7 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE53" t="n">
         <v>1.08</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26726,10 +26726,10 @@
         <v>74</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27193,7 +27193,7 @@
         <v>2.58</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF57" t="n">
         <v>2.4</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28569,7 +28569,7 @@
         <v>1.08</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF60" t="n">
         <v>1</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29966,7 +29966,7 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE63" t="n">
         <v>0.92</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30438,7 +30438,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE64" t="n">
         <v>0.75</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30913,7 +30913,7 @@
         <v>1.33</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF65" t="n">
         <v>1.83</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31345,7 +31345,7 @@
         <v>1.58</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32249,7 +32249,7 @@
         <v>2.58</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF68" t="n">
         <v>2.5</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34118,7 +34118,7 @@
         <v>73</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE72" t="n">
         <v>0.75</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34590,10 +34590,10 @@
         <v>64</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF73" t="n">
         <v>2.29</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35534,10 +35534,10 @@
         <v>86</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF75" t="n">
         <v>1.57</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36009,7 +36009,7 @@
         <v>1.15</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF76" t="n">
         <v>1.25</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38790,10 +38790,10 @@
         <v>63</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF82" t="n">
         <v>1.25</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39722,7 +39722,7 @@
         <v>76</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE84" t="n">
         <v>1.75</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40189,7 +40189,7 @@
         <v>1.92</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF85" t="n">
         <v>2.13</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42038,7 +42038,7 @@
         <v>82</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE89" t="n">
         <v>0.23</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42969,7 +42969,7 @@
         <v>1.33</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF91" t="n">
         <v>1.88</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43438,7 +43438,7 @@
         <v>89</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE92" t="n">
         <v>0.23</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44366,7 +44366,7 @@
         <v>84</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE94" t="n">
         <v>1.08</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44841,7 +44841,7 @@
         <v>1.08</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF95" t="n">
         <v>0.89</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45313,7 +45313,7 @@
         <v>1.15</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF96" t="n">
         <v>1.11</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46689,7 +46689,7 @@
         <v>1.92</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF99" t="n">
         <v>1.89</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47161,7 +47161,7 @@
         <v>1.08</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF100" t="n">
         <v>0.8</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48094,7 +48094,7 @@
         <v>79</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE102" t="n">
         <v>1</v>
@@ -48127,7 +48127,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48550,7 +48550,7 @@
         <v>73</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE103" t="n">
         <v>1.08</v>
@@ -48583,7 +48583,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49006,7 +49006,7 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE104" t="n">
         <v>0.92</v>
@@ -49039,7 +49039,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49503,7 +49503,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49945,7 +49945,7 @@
         <v>1.92</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF106" t="n">
         <v>1.8</v>
@@ -49975,7 +49975,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50423,7 +50423,7 @@
         <v>3.16</v>
       </c>
       <c r="DO107" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50895,7 +50895,7 @@
         <v>3.34</v>
       </c>
       <c r="DO108" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51313,7 +51313,7 @@
         <v>1.92</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="DF109" t="n">
         <v>1.73</v>
@@ -51343,7 +51343,7 @@
         <v>2.93</v>
       </c>
       <c r="DO109" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51815,7 +51815,7 @@
         <v>2.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP110" t="b">
         <v>0</v>
@@ -52287,7 +52287,7 @@
         <v>3.25</v>
       </c>
       <c r="DO111" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52726,7 +52726,7 @@
         <v>67</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DE112" t="n">
         <v>0.92</v>
@@ -52759,7 +52759,7 @@
         <v>2.83</v>
       </c>
       <c r="DO112" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53638,7 +53638,7 @@
         <v>91</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DE114" t="n">
         <v>0.75</v>
@@ -53671,7 +53671,7 @@
         <v>2.83</v>
       </c>
       <c r="DO114" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54105,7 +54105,7 @@
         <v>1.58</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DF115" t="n">
         <v>1.8</v>
@@ -54135,7 +54135,7 @@
         <v>3.48</v>
       </c>
       <c r="DO115" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54558,10 +54558,10 @@
         <v>86</v>
       </c>
       <c r="DD116" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DF116" t="n">
         <v>2.09</v>
@@ -54591,7 +54591,7 @@
         <v>3.48</v>
       </c>
       <c r="DO116" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55511,7 +55511,7 @@
         <v>2.73</v>
       </c>
       <c r="DO118" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55975,7 +55975,7 @@
         <v>3.2</v>
       </c>
       <c r="DO119" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56447,7 +56447,7 @@
         <v>3.15</v>
       </c>
       <c r="DO120" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56919,7 +56919,7 @@
         <v>3.58</v>
       </c>
       <c r="DO121" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57468,13 +57468,13 @@
         <v>4</v>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K123" t="n">
         <v>5</v>
       </c>
       <c r="L123" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M123" t="n">
         <v>2</v>
@@ -57507,16 +57507,16 @@
         <v>12</v>
       </c>
       <c r="W123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X123" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y123" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z123" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
@@ -57631,7 +57631,7 @@
         <v>4</v>
       </c>
       <c r="BK123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL123" t="n">
         <v>1</v>
@@ -57640,7 +57640,7 @@
         <v>4</v>
       </c>
       <c r="BN123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO123" t="n">
         <v>0</v>
@@ -57664,10 +57664,10 @@
         <v>1</v>
       </c>
       <c r="BV123" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="BW123" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="BX123" t="n">
         <v>71</v>
@@ -57676,13 +57676,13 @@
         <v>85</v>
       </c>
       <c r="BZ123" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="CA123" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CB123" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="CC123" t="n">
         <v>0</v>
@@ -57739,7 +57739,7 @@
         <v>1</v>
       </c>
       <c r="CU123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CV123" t="n">
         <v>14</v>
@@ -57824,27 +57824,27 @@
       </c>
       <c r="DW123" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="DX123" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DY123" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="DZ123" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EA123" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="EB123" t="inlineStr">
@@ -57858,22 +57858,22 @@
       <c r="EF123" t="inlineStr"/>
       <c r="EG123" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EH123" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EI123" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EJ123" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EK123" t="inlineStr">
@@ -57884,6 +57884,1362 @@
       <c r="EL123" t="inlineStr">
         <is>
           <t>1.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>25</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>46088.67708333334</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>9</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" t="n">
+        <v>10</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1</v>
+      </c>
+      <c r="R124" t="n">
+        <v>2</v>
+      </c>
+      <c r="S124" t="n">
+        <v>17</v>
+      </c>
+      <c r="T124" t="n">
+        <v>6</v>
+      </c>
+      <c r="U124" t="n">
+        <v>18</v>
+      </c>
+      <c r="V124" t="n">
+        <v>8</v>
+      </c>
+      <c r="W124" t="n">
+        <v>14</v>
+      </c>
+      <c r="X124" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Stadion Kranjčevićeva</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Kranjčevićeva 4, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>65</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY124" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ124" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DO124" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW124" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="DX124" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="DZ124" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EA124" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="EB124" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr"/>
+      <c r="ED124" t="inlineStr"/>
+      <c r="EE124" t="inlineStr"/>
+      <c r="EF124" t="inlineStr"/>
+      <c r="EG124" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr"/>
+      <c r="EJ124" t="inlineStr"/>
+      <c r="EK124" t="inlineStr"/>
+      <c r="EL124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>25</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46089.58333333334</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>7</v>
+      </c>
+      <c r="K125" t="n">
+        <v>7</v>
+      </c>
+      <c r="L125" t="n">
+        <v>14</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>3</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="n">
+        <v>11</v>
+      </c>
+      <c r="U125" t="n">
+        <v>13</v>
+      </c>
+      <c r="V125" t="n">
+        <v>18</v>
+      </c>
+      <c r="W125" t="n">
+        <v>10</v>
+      </c>
+      <c r="X125" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW125" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="DX125" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="DZ125" t="inlineStr"/>
+      <c r="EA125" t="inlineStr"/>
+      <c r="EB125" t="inlineStr"/>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED125" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EE125" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF125" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EG125" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EL125" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>25</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46089.69791666666</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>2</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>3</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" t="n">
+        <v>8</v>
+      </c>
+      <c r="T126" t="n">
+        <v>6</v>
+      </c>
+      <c r="U126" t="n">
+        <v>9</v>
+      </c>
+      <c r="V126" t="n">
+        <v>8</v>
+      </c>
+      <c r="W126" t="n">
+        <v>14</v>
+      </c>
+      <c r="X126" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>90</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>91</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>158</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>73</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>25</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW126" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="DX126" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="DY126" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DZ126" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EA126" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EB126" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC126" t="inlineStr"/>
+      <c r="ED126" t="inlineStr"/>
+      <c r="EE126" t="inlineStr"/>
+      <c r="EF126" t="inlineStr"/>
+      <c r="EG126" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EL126" t="inlineStr">
+        <is>
+          <t>1.92</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -58626,7 +58626,7 @@
         <v>1</v>
       </c>
       <c r="CR125" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CS125" t="n">
         <v>27</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL126" headerRowCount="1">
-  <autoFilter ref="A1:EL126"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL127" headerRowCount="1">
+  <autoFilter ref="A1:EL127"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL126"/>
+  <dimension ref="A1:EL127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.69</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE6" t="n">
         <v>1</v>
@@ -4113,7 +4113,7 @@
         <v>2.58</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -7846,7 +7846,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE15" t="n">
         <v>0.75</v>
@@ -12046,7 +12046,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE24" t="n">
         <v>2</v>
@@ -13902,7 +13902,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE28" t="n">
         <v>1.75</v>
@@ -14833,7 +14833,7 @@
         <v>1.08</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -18006,10 +18006,10 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -25814,7 +25814,7 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE54" t="n">
         <v>0.92</v>
@@ -27649,7 +27649,7 @@
         <v>1.33</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -29497,7 +29497,7 @@
         <v>1.15</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -31342,7 +31342,7 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE66" t="n">
         <v>1.08</v>
@@ -31809,7 +31809,7 @@
         <v>1.92</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -37401,7 +37401,7 @@
         <v>1.92</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF79" t="n">
         <v>1.57</v>
@@ -37846,7 +37846,7 @@
         <v>86</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE80" t="n">
         <v>0.67</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40650,7 +40650,7 @@
         <v>88</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE86" t="n">
         <v>1.08</v>
@@ -42041,7 +42041,7 @@
         <v>2</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF89" t="n">
         <v>2.13</v>
@@ -43441,7 +43441,7 @@
         <v>1.69</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF92" t="n">
         <v>1.33</v>
@@ -47633,7 +47633,7 @@
         <v>2.58</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF101" t="n">
         <v>2.44</v>
@@ -49470,7 +49470,7 @@
         <v>89</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE105" t="n">
         <v>0.75</v>
@@ -51785,7 +51785,7 @@
         <v>1.15</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF110" t="n">
         <v>1.18</v>
@@ -54102,7 +54102,7 @@
         <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE115" t="n">
         <v>2</v>
@@ -55481,7 +55481,7 @@
         <v>1.08</v>
       </c>
       <c r="DE118" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF118" t="n">
         <v>0.92</v>
@@ -55942,7 +55942,7 @@
         <v>78</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DE119" t="n">
         <v>1.75</v>
@@ -59240,6 +59240,454 @@
       <c r="EL126" t="inlineStr">
         <is>
           <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>26</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46094.70833333334</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>6</v>
+      </c>
+      <c r="K127" t="n">
+        <v>3</v>
+      </c>
+      <c r="L127" t="n">
+        <v>9</v>
+      </c>
+      <c r="M127" t="n">
+        <v>2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>5</v>
+      </c>
+      <c r="R127" t="n">
+        <v>3</v>
+      </c>
+      <c r="S127" t="n">
+        <v>17</v>
+      </c>
+      <c r="T127" t="n">
+        <v>7</v>
+      </c>
+      <c r="U127" t="n">
+        <v>22</v>
+      </c>
+      <c r="V127" t="n">
+        <v>10</v>
+      </c>
+      <c r="W127" t="n">
+        <v>10</v>
+      </c>
+      <c r="X127" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA127" t="inlineStr"/>
+      <c r="AB127" t="inlineStr"/>
+      <c r="AC127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1881</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>132</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>26</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW127" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DX127" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr"/>
+      <c r="ED127" t="inlineStr"/>
+      <c r="EE127" t="inlineStr"/>
+      <c r="EF127" t="inlineStr"/>
+      <c r="EG127" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EL127" t="inlineStr">
+        <is>
+          <t>1.65</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL127" headerRowCount="1">
-  <autoFilter ref="A1:EL127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL131" headerRowCount="1">
+  <autoFilter ref="A1:EL131"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL127"/>
+  <dimension ref="A1:EL131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE3" t="n">
         <v>2</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3174,10 +3174,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE7" t="n">
         <v>0.21</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4577,7 +4577,7 @@
         <v>1.33</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE9" t="n">
         <v>1.08</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5966,7 +5966,7 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE11" t="n">
         <v>1</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6441,7 +6441,7 @@
         <v>1.42</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7382,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE14" t="n">
         <v>2</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8318,10 +8318,10 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9249,7 +9249,7 @@
         <v>1.92</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9718,10 +9718,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10182,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE20" t="n">
         <v>1.75</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10654,7 +10654,7 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE21" t="n">
         <v>1.15</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11601,7 +11601,7 @@
         <v>1.42</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF23" t="n">
         <v>1</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12974,7 +12974,7 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE26" t="n">
         <v>1.08</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13441,7 +13441,7 @@
         <v>1.92</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14374,10 +14374,10 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF29" t="n">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14830,7 +14830,7 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE30" t="n">
         <v>0.21</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15286,7 +15286,7 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE31" t="n">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15734,7 +15734,7 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE32" t="n">
         <v>2</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16665,7 +16665,7 @@
         <v>1.15</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18454,10 +18454,10 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18910,10 +18910,10 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19822,10 +19822,10 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22617,7 +22617,7 @@
         <v>1.42</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23518,7 +23518,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE49" t="n">
         <v>0.75</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25369,7 +25369,7 @@
         <v>1.69</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25817,7 +25817,7 @@
         <v>1.69</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF54" t="n">
         <v>1.8</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26254,7 +26254,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE55" t="n">
         <v>0.75</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27190,7 +27190,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE57" t="n">
         <v>1.08</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28566,7 +28566,7 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE60" t="n">
         <v>1.15</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -29041,7 +29041,7 @@
         <v>1.15</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF61" t="n">
         <v>0.6</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29969,7 +29969,7 @@
         <v>1.69</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF63" t="n">
         <v>1.67</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30438,7 +30438,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE64" t="n">
         <v>0.75</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32246,7 +32246,7 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE68" t="n">
         <v>1.15</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE69" t="n">
         <v>1.75</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33174,10 +33174,10 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF70" t="n">
         <v>1</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33649,7 +33649,7 @@
         <v>1.15</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34590,7 +34590,7 @@
         <v>64</v>
       </c>
       <c r="DD73" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE73" t="n">
         <v>1.15</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35065,7 +35065,7 @@
         <v>1.33</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF74" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36926,7 +36926,7 @@
         <v>86</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE78" t="n">
         <v>1.75</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37398,7 +37398,7 @@
         <v>79</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE79" t="n">
         <v>0.21</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37849,7 +37849,7 @@
         <v>1.69</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF80" t="n">
         <v>1.71</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38318,10 +38318,10 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39250,7 +39250,7 @@
         <v>64</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE83" t="n">
         <v>1</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40653,7 +40653,7 @@
         <v>1.69</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF86" t="n">
         <v>1.88</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41106,10 +41106,10 @@
         <v>69</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF87" t="n">
         <v>0.88</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -41578,10 +41578,10 @@
         <v>88</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF88" t="n">
         <v>2.38</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42038,7 +42038,7 @@
         <v>82</v>
       </c>
       <c r="DD89" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE89" t="n">
         <v>0.21</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42494,7 +42494,7 @@
         <v>75</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE90" t="n">
         <v>1</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43910,10 +43910,10 @@
         <v>67</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF93" t="n">
         <v>1.89</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44366,10 +44366,10 @@
         <v>84</v>
       </c>
       <c r="DD94" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF94" t="n">
         <v>2.22</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44838,7 +44838,7 @@
         <v>67</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE95" t="n">
         <v>2</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45769,7 +45769,7 @@
         <v>1.33</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF97" t="n">
         <v>1.67</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47158,7 +47158,7 @@
         <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE100" t="n">
         <v>1.08</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47630,7 +47630,7 @@
         <v>90</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE101" t="n">
         <v>0.21</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48127,7 +48127,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48553,7 +48553,7 @@
         <v>1.42</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF103" t="n">
         <v>1.44</v>
@@ -48583,7 +48583,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49006,10 +49006,10 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -49039,7 +49039,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49503,7 +49503,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49942,7 +49942,7 @@
         <v>75</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE106" t="n">
         <v>2</v>
@@ -49975,7 +49975,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50393,7 +50393,7 @@
         <v>1.92</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF107" t="n">
         <v>1.7</v>
@@ -50423,7 +50423,7 @@
         <v>3.16</v>
       </c>
       <c r="DO107" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50862,10 +50862,10 @@
         <v>91</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF108" t="n">
         <v>2.5</v>
@@ -50895,7 +50895,7 @@
         <v>3.34</v>
       </c>
       <c r="DO108" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51310,7 +51310,7 @@
         <v>64</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE109" t="n">
         <v>1.15</v>
@@ -51343,7 +51343,7 @@
         <v>2.93</v>
       </c>
       <c r="DO109" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51815,7 +51815,7 @@
         <v>2.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP110" t="b">
         <v>0</v>
@@ -52254,7 +52254,7 @@
         <v>67</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE111" t="n">
         <v>1.75</v>
@@ -52287,7 +52287,7 @@
         <v>3.25</v>
       </c>
       <c r="DO111" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52729,7 +52729,7 @@
         <v>1.42</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF112" t="n">
         <v>1.6</v>
@@ -52759,7 +52759,7 @@
         <v>2.83</v>
       </c>
       <c r="DO112" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53215,7 +53215,7 @@
         <v>2.9</v>
       </c>
       <c r="DO113" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53671,7 +53671,7 @@
         <v>2.83</v>
       </c>
       <c r="DO114" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54135,7 +54135,7 @@
         <v>3.48</v>
       </c>
       <c r="DO115" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54558,7 +54558,7 @@
         <v>86</v>
       </c>
       <c r="DD116" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE116" t="n">
         <v>1.08</v>
@@ -54591,7 +54591,7 @@
         <v>3.48</v>
       </c>
       <c r="DO116" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55009,7 +55009,7 @@
         <v>1.92</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DF117" t="n">
         <v>1.82</v>
@@ -55039,7 +55039,7 @@
         <v>2.92</v>
       </c>
       <c r="DO117" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55478,7 +55478,7 @@
         <v>75</v>
       </c>
       <c r="DD118" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DE118" t="n">
         <v>0.21</v>
@@ -55511,7 +55511,7 @@
         <v>2.73</v>
       </c>
       <c r="DO118" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55975,7 +55975,7 @@
         <v>3.2</v>
       </c>
       <c r="DO119" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56414,10 +56414,10 @@
         <v>79</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="DE120" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DF120" t="n">
         <v>1.83</v>
@@ -56447,7 +56447,7 @@
         <v>3.15</v>
       </c>
       <c r="DO120" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56886,7 +56886,7 @@
         <v>82</v>
       </c>
       <c r="DD121" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DE121" t="n">
         <v>1</v>
@@ -56919,7 +56919,7 @@
         <v>3.58</v>
       </c>
       <c r="DO121" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57359,7 +57359,7 @@
         <v>2.8</v>
       </c>
       <c r="DO122" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57769,7 +57769,7 @@
         <v>1.15</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DF123" t="n">
         <v>1.17</v>
@@ -57799,7 +57799,7 @@
         <v>2.55</v>
       </c>
       <c r="DO123" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -58255,7 +58255,7 @@
         <v>2.66</v>
       </c>
       <c r="DO124" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58662,7 +58662,7 @@
         <v>71</v>
       </c>
       <c r="DD125" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DE125" t="n">
         <v>2</v>
@@ -58695,7 +58695,7 @@
         <v>3.77</v>
       </c>
       <c r="DO125" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -59155,7 +59155,7 @@
         <v>3.1</v>
       </c>
       <c r="DO126" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59688,6 +59688,1878 @@
       <c r="EL127" t="inlineStr">
         <is>
           <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>26</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46095.58333333334</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" t="n">
+        <v>7</v>
+      </c>
+      <c r="L128" t="n">
+        <v>12</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>2</v>
+      </c>
+      <c r="R128" t="n">
+        <v>4</v>
+      </c>
+      <c r="S128" t="n">
+        <v>17</v>
+      </c>
+      <c r="T128" t="n">
+        <v>9</v>
+      </c>
+      <c r="U128" t="n">
+        <v>19</v>
+      </c>
+      <c r="V128" t="n">
+        <v>13</v>
+      </c>
+      <c r="W128" t="n">
+        <v>13</v>
+      </c>
+      <c r="X128" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>69</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>26</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW128" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="DX128" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EE128" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>26</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46095.67708333334</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4</v>
+      </c>
+      <c r="H129" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" t="n">
+        <v>6</v>
+      </c>
+      <c r="J129" t="n">
+        <v>5</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>10</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2</v>
+      </c>
+      <c r="S129" t="n">
+        <v>9</v>
+      </c>
+      <c r="T129" t="n">
+        <v>3</v>
+      </c>
+      <c r="U129" t="n">
+        <v>19</v>
+      </c>
+      <c r="V129" t="n">
+        <v>5</v>
+      </c>
+      <c r="W129" t="n">
+        <v>8</v>
+      </c>
+      <c r="X129" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>146</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>73</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>96</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>28</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>26</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW129" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="DX129" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="DZ129" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EA129" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EB129" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EC129" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="ED129" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EE129" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EF129" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EG129" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EH129" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EK129" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EL129" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>26</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>46096.58333333334</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>10</v>
+      </c>
+      <c r="L130" t="n">
+        <v>15</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>9</v>
+      </c>
+      <c r="R130" t="n">
+        <v>5</v>
+      </c>
+      <c r="S130" t="n">
+        <v>12</v>
+      </c>
+      <c r="T130" t="n">
+        <v>12</v>
+      </c>
+      <c r="U130" t="n">
+        <v>21</v>
+      </c>
+      <c r="V130" t="n">
+        <v>17</v>
+      </c>
+      <c r="W130" t="n">
+        <v>17</v>
+      </c>
+      <c r="X130" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>96</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>61</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>26</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW130" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="DX130" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="DY130" t="inlineStr">
+        <is>
+          <t>6.32</t>
+        </is>
+      </c>
+      <c r="DZ130" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC130" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED130" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EE130" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EG130" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>26</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>46096.69791666666</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" t="n">
+        <v>11</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>11</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>6</v>
+      </c>
+      <c r="R131" t="n">
+        <v>2</v>
+      </c>
+      <c r="S131" t="n">
+        <v>23</v>
+      </c>
+      <c r="T131" t="n">
+        <v>4</v>
+      </c>
+      <c r="U131" t="n">
+        <v>29</v>
+      </c>
+      <c r="V131" t="n">
+        <v>6</v>
+      </c>
+      <c r="W131" t="n">
+        <v>7</v>
+      </c>
+      <c r="X131" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>1857</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>5897</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>111</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>160</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>23</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>26</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW131" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="DX131" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EB131" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr"/>
+      <c r="ED131" t="inlineStr"/>
+      <c r="EE131" t="inlineStr"/>
+      <c r="EF131" t="inlineStr"/>
+      <c r="EG131" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH131" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI131" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>1.81</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -60937,7 +60937,7 @@
         <v>22</v>
       </c>
       <c r="CS130" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT130" t="n">
         <v>1</v>
@@ -60946,7 +60946,7 @@
         <v>6</v>
       </c>
       <c r="CV130" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW130" t="n">
         <v>1</v>
@@ -61153,7 +61153,7 @@
         <v>11</v>
       </c>
       <c r="M131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N131" t="n">
         <v>2</v>
@@ -61205,7 +61205,7 @@
         </is>
       </c>
       <c r="AC131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD131" t="n">
         <v>2</v>
@@ -61325,7 +61325,7 @@
         <v>0</v>
       </c>
       <c r="BQ131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR131" t="n">
         <v>2</v>
@@ -61334,7 +61334,7 @@
         <v>1</v>
       </c>
       <c r="BT131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU131" t="n">
         <v>1</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL131" headerRowCount="1">
-  <autoFilter ref="A1:EL131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL132" headerRowCount="1">
+  <autoFilter ref="A1:EL132"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL131"/>
+  <dimension ref="A1:EL132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE8" t="n">
         <v>0.62</v>
@@ -5513,7 +5513,7 @@
         <v>1.92</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -10657,7 +10657,7 @@
         <v>1.79</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF21" t="n">
         <v>1.5</v>
@@ -11126,7 +11126,7 @@
         <v>88</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE22" t="n">
         <v>1</v>
@@ -16209,7 +16209,7 @@
         <v>1.69</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF33" t="n">
         <v>1.33</v>
@@ -17134,7 +17134,7 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE35" t="n">
         <v>0.75</v>
@@ -20286,10 +20286,10 @@
         <v>67</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF42" t="n">
         <v>2.33</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -23982,7 +23982,7 @@
         <v>59</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE50" t="n">
         <v>1.75</v>
@@ -24441,7 +24441,7 @@
         <v>1.15</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF51" t="n">
         <v>1</v>
@@ -27646,7 +27646,7 @@
         <v>80</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE58" t="n">
         <v>0.21</v>
@@ -28569,7 +28569,7 @@
         <v>1.07</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF60" t="n">
         <v>1</v>
@@ -30910,7 +30910,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE65" t="n">
         <v>2</v>
@@ -32249,7 +32249,7 @@
         <v>2.62</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF68" t="n">
         <v>2.5</v>
@@ -34593,7 +34593,7 @@
         <v>2.07</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF73" t="n">
         <v>2.29</v>
@@ -35062,7 +35062,7 @@
         <v>71</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE74" t="n">
         <v>0.86</v>
@@ -38793,7 +38793,7 @@
         <v>1.42</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF82" t="n">
         <v>1.25</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42966,7 +42966,7 @@
         <v>82</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE91" t="n">
         <v>1.08</v>
@@ -45313,7 +45313,7 @@
         <v>1.15</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF96" t="n">
         <v>1.11</v>
@@ -45766,7 +45766,7 @@
         <v>84</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE97" t="n">
         <v>0.62</v>
@@ -46689,7 +46689,7 @@
         <v>1.92</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF99" t="n">
         <v>1.89</v>
@@ -51313,7 +51313,7 @@
         <v>1.79</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF109" t="n">
         <v>1.73</v>
@@ -53182,7 +53182,7 @@
         <v>75</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE113" t="n">
         <v>1</v>
@@ -57326,7 +57326,7 @@
         <v>87</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DE122" t="n">
         <v>0.75</v>
@@ -58225,7 +58225,7 @@
         <v>1.69</v>
       </c>
       <c r="DE124" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DF124" t="n">
         <v>1.75</v>
@@ -61560,6 +61560,478 @@
       <c r="EL131" t="inlineStr">
         <is>
           <t>1.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>27</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>46101.70833333334</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" t="n">
+        <v>4</v>
+      </c>
+      <c r="K132" t="n">
+        <v>3</v>
+      </c>
+      <c r="L132" t="n">
+        <v>7</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>5</v>
+      </c>
+      <c r="R132" t="n">
+        <v>4</v>
+      </c>
+      <c r="S132" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" t="n">
+        <v>11</v>
+      </c>
+      <c r="U132" t="n">
+        <v>10</v>
+      </c>
+      <c r="V132" t="n">
+        <v>15</v>
+      </c>
+      <c r="W132" t="n">
+        <v>9</v>
+      </c>
+      <c r="X132" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>Stadion Aldo Drosina</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>Marsovo polje, Pula</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>1857</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>123</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>76</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW132" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="DX132" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="EB132" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC132" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED132" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EE132" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EH132" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EI132" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EJ132" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr">
+        <is>
+          <t>1.64</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL132" headerRowCount="1">
-  <autoFilter ref="A1:EL132"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL136" headerRowCount="1">
+  <autoFilter ref="A1:EL136"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL132"/>
+  <dimension ref="A1:EL136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE2" t="n">
         <v>0.21</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2233,7 +2233,7 @@
         <v>1.07</v>
       </c>
       <c r="DE3" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         <v>1.07</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE10" t="n">
         <v>1.07</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6438,7 +6438,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE12" t="n">
         <v>1.21</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6910,7 +6910,7 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7385,7 +7385,7 @@
         <v>1.79</v>
       </c>
       <c r="DE14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF14" t="n">
         <v>3</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7849,7 +7849,7 @@
         <v>1.69</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         <v>84</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE17" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9246,7 +9246,7 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE18" t="n">
         <v>0.62</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10185,7 +10185,7 @@
         <v>1.07</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11598,7 +11598,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE23" t="n">
         <v>0.86</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12049,7 +12049,7 @@
         <v>1.69</v>
       </c>
       <c r="DE24" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12502,10 +12502,10 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12977,7 +12977,7 @@
         <v>2.07</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13438,7 +13438,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE27" t="n">
         <v>1.21</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13905,7 +13905,7 @@
         <v>1.69</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15737,7 +15737,7 @@
         <v>2.07</v>
       </c>
       <c r="DE32" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF32" t="n">
         <v>2.5</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16206,7 +16206,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE33" t="n">
         <v>1.07</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16662,7 +16662,7 @@
         <v>17</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE34" t="n">
         <v>0.86</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17137,7 +17137,7 @@
         <v>1.46</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17574,10 +17574,10 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF36" t="n">
         <v>0.67</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19366,10 +19366,10 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20758,10 +20758,10 @@
         <v>100</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21222,10 +21222,10 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21694,10 +21694,10 @@
         <v>84</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22166,10 +22166,10 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE46" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF46" t="n">
         <v>1.75</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22614,7 +22614,7 @@
         <v>90</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE47" t="n">
         <v>0.62</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23062,10 +23062,10 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF48" t="n">
         <v>2.25</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23521,7 +23521,7 @@
         <v>2.62</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF49" t="n">
         <v>2.25</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23985,7 +23985,7 @@
         <v>1.46</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24438,7 +24438,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE51" t="n">
         <v>1.07</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24894,10 +24894,10 @@
         <v>88</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25366,7 +25366,7 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE53" t="n">
         <v>1.21</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26257,7 +26257,7 @@
         <v>1.79</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26726,10 +26726,10 @@
         <v>74</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE56" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF56" t="n">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27193,7 +27193,7 @@
         <v>2.62</v>
       </c>
       <c r="DE57" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF57" t="n">
         <v>2.4</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28094,10 +28094,10 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -29038,7 +29038,7 @@
         <v>90</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE61" t="n">
         <v>0.62</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29494,7 +29494,7 @@
         <v>100</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE62" t="n">
         <v>0.21</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29966,7 +29966,7 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE63" t="n">
         <v>0.86</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30441,7 +30441,7 @@
         <v>2.07</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF64" t="n">
         <v>2.17</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30913,7 +30913,7 @@
         <v>1.46</v>
       </c>
       <c r="DE65" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF65" t="n">
         <v>1.83</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31345,7 +31345,7 @@
         <v>1.69</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31806,7 +31806,7 @@
         <v>83</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE67" t="n">
         <v>0.21</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32713,7 +32713,7 @@
         <v>1.79</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF69" t="n">
         <v>1.33</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33646,7 +33646,7 @@
         <v>85</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE71" t="n">
         <v>1.21</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34118,10 +34118,10 @@
         <v>73</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF72" t="n">
         <v>1.29</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35534,10 +35534,10 @@
         <v>86</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF75" t="n">
         <v>1.57</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36006,10 +36006,10 @@
         <v>80</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE76" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF76" t="n">
         <v>1.25</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36454,7 +36454,7 @@
         <v>77</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE77" t="n">
         <v>1</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36929,7 +36929,7 @@
         <v>2.62</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF78" t="n">
         <v>2.57</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38790,7 +38790,7 @@
         <v>63</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE82" t="n">
         <v>1.07</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39722,10 +39722,10 @@
         <v>76</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF84" t="n">
         <v>1.5</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40186,10 +40186,10 @@
         <v>82</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE85" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF85" t="n">
         <v>2.13</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42969,7 +42969,7 @@
         <v>1.46</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF91" t="n">
         <v>1.88</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43438,7 +43438,7 @@
         <v>89</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE92" t="n">
         <v>0.21</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44841,7 +44841,7 @@
         <v>1.07</v>
       </c>
       <c r="DE95" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF95" t="n">
         <v>0.89</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45310,7 +45310,7 @@
         <v>73</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE96" t="n">
         <v>1.07</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46238,10 +46238,10 @@
         <v>79</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF98" t="n">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46686,7 +46686,7 @@
         <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE99" t="n">
         <v>1.07</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47161,7 +47161,7 @@
         <v>1.07</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF100" t="n">
         <v>0.8</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48094,7 +48094,7 @@
         <v>79</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE102" t="n">
         <v>1</v>
@@ -48127,7 +48127,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48550,7 +48550,7 @@
         <v>73</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE103" t="n">
         <v>1.21</v>
@@ -48583,7 +48583,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49039,7 +49039,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49473,7 +49473,7 @@
         <v>1.69</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF105" t="n">
         <v>1.67</v>
@@ -49503,7 +49503,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49945,7 +49945,7 @@
         <v>1.79</v>
       </c>
       <c r="DE106" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF106" t="n">
         <v>1.8</v>
@@ -49975,7 +49975,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50390,7 +50390,7 @@
         <v>90</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE107" t="n">
         <v>0.62</v>
@@ -50423,7 +50423,7 @@
         <v>3.16</v>
       </c>
       <c r="DO107" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50895,7 +50895,7 @@
         <v>3.34</v>
       </c>
       <c r="DO108" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51343,7 +51343,7 @@
         <v>2.93</v>
       </c>
       <c r="DO109" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51782,7 +51782,7 @@
         <v>91</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE110" t="n">
         <v>0.21</v>
@@ -51815,7 +51815,7 @@
         <v>2.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP110" t="b">
         <v>0</v>
@@ -52257,7 +52257,7 @@
         <v>1.07</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF111" t="n">
         <v>1</v>
@@ -52287,7 +52287,7 @@
         <v>3.25</v>
       </c>
       <c r="DO111" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52726,7 +52726,7 @@
         <v>67</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE112" t="n">
         <v>0.86</v>
@@ -52759,7 +52759,7 @@
         <v>2.83</v>
       </c>
       <c r="DO112" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53215,7 +53215,7 @@
         <v>2.9</v>
       </c>
       <c r="DO113" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53638,10 +53638,10 @@
         <v>91</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF114" t="n">
         <v>1.64</v>
@@ -53671,7 +53671,7 @@
         <v>2.83</v>
       </c>
       <c r="DO114" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54105,7 +54105,7 @@
         <v>1.69</v>
       </c>
       <c r="DE115" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF115" t="n">
         <v>1.8</v>
@@ -54135,7 +54135,7 @@
         <v>3.48</v>
       </c>
       <c r="DO115" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54561,7 +54561,7 @@
         <v>2.07</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF116" t="n">
         <v>2.09</v>
@@ -54591,7 +54591,7 @@
         <v>3.48</v>
       </c>
       <c r="DO116" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55006,7 +55006,7 @@
         <v>92</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DE117" t="n">
         <v>1.21</v>
@@ -55039,7 +55039,7 @@
         <v>2.92</v>
       </c>
       <c r="DO117" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55511,7 +55511,7 @@
         <v>2.73</v>
       </c>
       <c r="DO118" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55945,7 +55945,7 @@
         <v>1.69</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DF119" t="n">
         <v>1.64</v>
@@ -55975,7 +55975,7 @@
         <v>3.2</v>
       </c>
       <c r="DO119" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56447,7 +56447,7 @@
         <v>3.15</v>
       </c>
       <c r="DO120" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56919,7 +56919,7 @@
         <v>3.58</v>
       </c>
       <c r="DO121" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57329,7 +57329,7 @@
         <v>1.46</v>
       </c>
       <c r="DE122" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DF122" t="n">
         <v>1.45</v>
@@ -57359,7 +57359,7 @@
         <v>2.8</v>
       </c>
       <c r="DO122" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57766,7 +57766,7 @@
         <v>79</v>
       </c>
       <c r="DD123" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DE123" t="n">
         <v>0.86</v>
@@ -57799,7 +57799,7 @@
         <v>2.55</v>
       </c>
       <c r="DO123" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -58222,7 +58222,7 @@
         <v>80</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DE124" t="n">
         <v>1.07</v>
@@ -58255,7 +58255,7 @@
         <v>2.66</v>
       </c>
       <c r="DO124" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58665,7 +58665,7 @@
         <v>2.07</v>
       </c>
       <c r="DE125" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DF125" t="n">
         <v>2.17</v>
@@ -58695,7 +58695,7 @@
         <v>3.77</v>
       </c>
       <c r="DO125" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -59122,10 +59122,10 @@
         <v>73</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DE126" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DF126" t="n">
         <v>1.55</v>
@@ -59155,7 +59155,7 @@
         <v>3.1</v>
       </c>
       <c r="DO126" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59603,7 +59603,7 @@
         <v>2.62</v>
       </c>
       <c r="DO127" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -60059,7 +60059,7 @@
         <v>3.04</v>
       </c>
       <c r="DO128" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP128" t="b">
         <v>0</v>
@@ -60531,7 +60531,7 @@
         <v>3.31</v>
       </c>
       <c r="DO129" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -61003,7 +61003,7 @@
         <v>3.16</v>
       </c>
       <c r="DO130" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61475,7 +61475,7 @@
         <v>2.97</v>
       </c>
       <c r="DO131" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -62034,6 +62034,1838 @@
           <t>1.64</t>
         </is>
       </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>27</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>46102.58333333334</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>6</v>
+      </c>
+      <c r="I133" t="n">
+        <v>6</v>
+      </c>
+      <c r="J133" t="n">
+        <v>3</v>
+      </c>
+      <c r="K133" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" t="n">
+        <v>5</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>4</v>
+      </c>
+      <c r="R133" t="n">
+        <v>11</v>
+      </c>
+      <c r="S133" t="n">
+        <v>3</v>
+      </c>
+      <c r="T133" t="n">
+        <v>8</v>
+      </c>
+      <c r="U133" t="n">
+        <v>7</v>
+      </c>
+      <c r="V133" t="n">
+        <v>19</v>
+      </c>
+      <c r="W133" t="n">
+        <v>10</v>
+      </c>
+      <c r="X133" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>138</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW133" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="DX133" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="DY133" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DZ133" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EA133" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EB133" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EC133" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="ED133" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EE133" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EF133" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EG133" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EH133" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EI133" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EJ133" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>27</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>46102.67708333334</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>5</v>
+      </c>
+      <c r="J134" t="n">
+        <v>3</v>
+      </c>
+      <c r="K134" t="n">
+        <v>7</v>
+      </c>
+      <c r="L134" t="n">
+        <v>10</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>11</v>
+      </c>
+      <c r="S134" t="n">
+        <v>2</v>
+      </c>
+      <c r="T134" t="n">
+        <v>10</v>
+      </c>
+      <c r="U134" t="n">
+        <v>2</v>
+      </c>
+      <c r="V134" t="n">
+        <v>21</v>
+      </c>
+      <c r="W134" t="n">
+        <v>10</v>
+      </c>
+      <c r="X134" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Stadion Kranjčevićeva</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Kranjčevićeva 4, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>76</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>126</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>54</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>81</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>46</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW134" t="inlineStr">
+        <is>
+          <t>7.85</t>
+        </is>
+      </c>
+      <c r="DX134" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr"/>
+      <c r="EJ134" t="inlineStr"/>
+      <c r="EK134" t="inlineStr"/>
+      <c r="EL134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>27</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>46103.58333333334</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>6</v>
+      </c>
+      <c r="K135" t="n">
+        <v>3</v>
+      </c>
+      <c r="L135" t="n">
+        <v>9</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>2</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2</v>
+      </c>
+      <c r="S135" t="n">
+        <v>6</v>
+      </c>
+      <c r="T135" t="n">
+        <v>9</v>
+      </c>
+      <c r="U135" t="n">
+        <v>8</v>
+      </c>
+      <c r="V135" t="n">
+        <v>11</v>
+      </c>
+      <c r="W135" t="n">
+        <v>12</v>
+      </c>
+      <c r="X135" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>58</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW135" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="DX135" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="DY135" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="DZ135" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED135" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr"/>
+      <c r="EJ135" t="inlineStr"/>
+      <c r="EK135" t="inlineStr"/>
+      <c r="EL135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>27</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>46103.69791666666</v>
+      </c>
+      <c r="G136" t="n">
+        <v>4</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="n">
+        <v>5</v>
+      </c>
+      <c r="L136" t="n">
+        <v>6</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>6</v>
+      </c>
+      <c r="R136" t="n">
+        <v>3</v>
+      </c>
+      <c r="S136" t="n">
+        <v>4</v>
+      </c>
+      <c r="T136" t="n">
+        <v>8</v>
+      </c>
+      <c r="U136" t="n">
+        <v>10</v>
+      </c>
+      <c r="V136" t="n">
+        <v>11</v>
+      </c>
+      <c r="W136" t="n">
+        <v>9</v>
+      </c>
+      <c r="X136" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>ŠRC Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>, Velika Gorica</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>1875</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>1373</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>158</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY136" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ136" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA136" t="n">
+        <v>64</v>
+      </c>
+      <c r="DB136" t="n">
+        <v>28</v>
+      </c>
+      <c r="DC136" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD136" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DE136" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF136" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DG136" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DH136" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DI136" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DJ136" t="n">
+        <v>52</v>
+      </c>
+      <c r="DK136" t="n">
+        <v>37</v>
+      </c>
+      <c r="DL136" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM136" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN136" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DO136" t="n">
+        <v>27</v>
+      </c>
+      <c r="DP136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW136" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="DX136" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="DY136" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="DZ136" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="ED136" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EF136" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EH136" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI136" t="inlineStr"/>
+      <c r="EJ136" t="inlineStr"/>
+      <c r="EK136" t="inlineStr"/>
+      <c r="EL136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -63493,10 +63493,10 @@
         <v>13</v>
       </c>
       <c r="Y136" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z136" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA136" t="inlineStr">
         <is>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -41888,7 +41888,7 @@
         <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>-1</v>
+        <v>21212</v>
       </c>
       <c r="BG89" t="n">
         <v>2</v>
@@ -42344,7 +42344,7 @@
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>-1</v>
+        <v>4731</v>
       </c>
       <c r="BG90" t="n">
         <v>2</v>
@@ -47848,12 +47848,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC102" t="n">
@@ -51493,10 +51493,10 @@
         <v>6</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -51545,10 +51545,10 @@
         </is>
       </c>
       <c r="AC110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE110" t="n">
         <v>1.82</v>
@@ -51665,10 +51665,10 @@
         <v>0</v>
       </c>
       <c r="BQ110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS110" t="n">
         <v>0</v>
@@ -57933,7 +57933,7 @@
         <v>10</v>
       </c>
       <c r="M124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N124" t="n">
         <v>2</v>
@@ -57985,7 +57985,7 @@
         </is>
       </c>
       <c r="AC124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD124" t="n">
         <v>2</v>
@@ -58105,7 +58105,7 @@
         <v>1</v>
       </c>
       <c r="BQ124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR124" t="n">
         <v>1</v>
@@ -58114,7 +58114,7 @@
         <v>1</v>
       </c>
       <c r="BT124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU124" t="n">
         <v>1</v>
@@ -59301,7 +59301,7 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R127" t="n">
         <v>3</v>
@@ -59313,7 +59313,7 @@
         <v>7</v>
       </c>
       <c r="U127" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V127" t="n">
         <v>10</v>
@@ -59325,10 +59325,10 @@
         <v>14</v>
       </c>
       <c r="Y127" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z127" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr"/>
@@ -59480,13 +59480,13 @@
         <v>132</v>
       </c>
       <c r="BZ127" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="CA127" t="n">
         <v>1.35</v>
       </c>
       <c r="CB127" t="n">
-        <v>3.51</v>
+        <v>3.65</v>
       </c>
       <c r="CC127" t="n">
         <v>0</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -1528,12 +1528,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC2" t="n">
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1</v>
+        <v>834</v>
       </c>
       <c r="BG2" t="n">
         <v>2</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1</v>
+        <v>11502</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1</v>
+        <v>5964</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
@@ -3024,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1</v>
+        <v>25501</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-1</v>
+        <v>1880</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
@@ -3960,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-1</v>
+        <v>12721</v>
       </c>
       <c r="BG7" t="n">
         <v>2</v>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-1</v>
+        <v>3483</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
@@ -4896,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1</v>
+        <v>6132</v>
       </c>
       <c r="BG9" t="n">
         <v>2</v>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-1</v>
+        <v>2050</v>
       </c>
       <c r="BG10" t="n">
         <v>2</v>
@@ -5816,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-1</v>
+        <v>25302</v>
       </c>
       <c r="BG11" t="n">
         <v>2</v>
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-1</v>
+        <v>1235</v>
       </c>
       <c r="BG12" t="n">
         <v>2</v>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC13" t="n">
@@ -6760,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-1</v>
+        <v>21702</v>
       </c>
       <c r="BG13" t="n">
         <v>2</v>
@@ -7232,7 +7232,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-1</v>
+        <v>7076</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
@@ -7696,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-1</v>
+        <v>2197</v>
       </c>
       <c r="BG15" t="n">
         <v>2</v>
@@ -8168,7 +8168,7 @@
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-1</v>
+        <v>23635</v>
       </c>
       <c r="BG16" t="n">
         <v>2</v>
@@ -8640,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-1</v>
+        <v>913</v>
       </c>
       <c r="BG17" t="n">
         <v>2</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-1</v>
+        <v>1313</v>
       </c>
       <c r="BG18" t="n">
         <v>2</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-1</v>
+        <v>11461</v>
       </c>
       <c r="BG19" t="n">
         <v>2</v>
@@ -10032,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-1</v>
+        <v>11383</v>
       </c>
       <c r="BG20" t="n">
         <v>2</v>
@@ -10504,7 +10504,7 @@
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>-1</v>
+        <v>4883</v>
       </c>
       <c r="BG21" t="n">
         <v>2</v>
@@ -10976,7 +10976,7 @@
         <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>-1</v>
+        <v>2437</v>
       </c>
       <c r="BG22" t="n">
         <v>-1</v>
@@ -11448,7 +11448,7 @@
         <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>-1</v>
+        <v>697</v>
       </c>
       <c r="BG23" t="n">
         <v>2</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>-1</v>
+        <v>10477</v>
       </c>
       <c r="BG24" t="n">
         <v>2</v>
@@ -12256,12 +12256,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC25" t="n">
@@ -12352,7 +12352,7 @@
         <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>-1</v>
+        <v>561</v>
       </c>
       <c r="BG25" t="n">
         <v>2</v>
@@ -12824,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>-1</v>
+        <v>29112</v>
       </c>
       <c r="BG26" t="n">
         <v>2</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>-1</v>
+        <v>1513</v>
       </c>
       <c r="BG27" t="n">
         <v>2</v>
@@ -13752,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>-1</v>
+        <v>10366</v>
       </c>
       <c r="BG28" t="n">
         <v>2</v>
@@ -14224,7 +14224,7 @@
         <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>-1</v>
+        <v>5497</v>
       </c>
       <c r="BG29" t="n">
         <v>2</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>-1</v>
+        <v>4342</v>
       </c>
       <c r="BG30" t="n">
         <v>2</v>
@@ -15136,7 +15136,7 @@
         <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>-1</v>
+        <v>9670</v>
       </c>
       <c r="BG31" t="n">
         <v>2</v>
@@ -15584,7 +15584,7 @@
         <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>-1</v>
+        <v>32212</v>
       </c>
       <c r="BG32" t="n">
         <v>2</v>
@@ -15960,12 +15960,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC33" t="n">
@@ -16056,7 +16056,7 @@
         <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>-1</v>
+        <v>304</v>
       </c>
       <c r="BG33" t="n">
         <v>2</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>-1</v>
+        <v>1653</v>
       </c>
       <c r="BG34" t="n">
         <v>2</v>
@@ -16984,7 +16984,7 @@
         <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>-1</v>
+        <v>2519</v>
       </c>
       <c r="BG35" t="n">
         <v>2</v>
@@ -17424,7 +17424,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>-1</v>
+        <v>1055</v>
       </c>
       <c r="BG36" t="n">
         <v>2</v>
@@ -17856,7 +17856,7 @@
         <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>-1</v>
+        <v>1209</v>
       </c>
       <c r="BG37" t="n">
         <v>2</v>
@@ -18304,7 +18304,7 @@
         <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>-1</v>
+        <v>5369</v>
       </c>
       <c r="BG38" t="n">
         <v>2</v>
@@ -18760,7 +18760,7 @@
         <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>-1</v>
+        <v>16768</v>
       </c>
       <c r="BG39" t="n">
         <v>2</v>
@@ -19216,7 +19216,7 @@
         <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>-1</v>
+        <v>1427</v>
       </c>
       <c r="BG40" t="n">
         <v>2</v>
@@ -19672,7 +19672,7 @@
         <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>-1</v>
+        <v>9012</v>
       </c>
       <c r="BG41" t="n">
         <v>2</v>
@@ -20136,7 +20136,7 @@
         <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>-1</v>
+        <v>1959</v>
       </c>
       <c r="BG42" t="n">
         <v>2</v>
@@ -20608,7 +20608,7 @@
         <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>-1</v>
+        <v>5961</v>
       </c>
       <c r="BG43" t="n">
         <v>2</v>
@@ -21072,7 +21072,7 @@
         <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>-1</v>
+        <v>1614</v>
       </c>
       <c r="BG44" t="n">
         <v>2</v>
@@ -21544,7 +21544,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>-1</v>
+        <v>735</v>
       </c>
       <c r="BG45" t="n">
         <v>2</v>
@@ -21920,12 +21920,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC46" t="n">
@@ -22016,7 +22016,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-1</v>
+        <v>3354</v>
       </c>
       <c r="BG46" t="n">
         <v>2</v>
@@ -22464,7 +22464,7 @@
         <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>-1</v>
+        <v>532</v>
       </c>
       <c r="BG47" t="n">
         <v>2</v>
@@ -22912,7 +22912,7 @@
         <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>-1</v>
+        <v>1447</v>
       </c>
       <c r="BG48" t="n">
         <v>2</v>
@@ -23368,7 +23368,7 @@
         <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>-1</v>
+        <v>13836</v>
       </c>
       <c r="BG49" t="n">
         <v>2</v>
@@ -23832,7 +23832,7 @@
         <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>-1</v>
+        <v>8124</v>
       </c>
       <c r="BG50" t="n">
         <v>2</v>
@@ -24288,7 +24288,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>-1</v>
+        <v>1163</v>
       </c>
       <c r="BG51" t="n">
         <v>2</v>
@@ -24744,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>-1</v>
+        <v>4707</v>
       </c>
       <c r="BG52" t="n">
         <v>2</v>
@@ -25120,12 +25120,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC53" t="n">
@@ -25216,7 +25216,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>-1</v>
+        <v>305</v>
       </c>
       <c r="BG53" t="n">
         <v>2</v>
@@ -25664,7 +25664,7 @@
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>1346</v>
       </c>
       <c r="BG54" t="n">
         <v>2</v>
@@ -26104,7 +26104,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>-1</v>
+        <v>5096</v>
       </c>
       <c r="BG55" t="n">
         <v>2</v>
@@ -26576,7 +26576,7 @@
         <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>-1</v>
+        <v>6679</v>
       </c>
       <c r="BG56" t="n">
         <v>2</v>
@@ -27040,7 +27040,7 @@
         <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>-1</v>
+        <v>10237</v>
       </c>
       <c r="BG57" t="n">
         <v>2</v>
@@ -27496,7 +27496,7 @@
         <v>0</v>
       </c>
       <c r="BF58" t="n">
-        <v>-1</v>
+        <v>2209</v>
       </c>
       <c r="BG58" t="n">
         <v>2</v>
@@ -27944,7 +27944,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>-1</v>
+        <v>3077</v>
       </c>
       <c r="BG59" t="n">
         <v>2</v>
@@ -28416,7 +28416,7 @@
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>-1</v>
+        <v>4364</v>
       </c>
       <c r="BG60" t="n">
         <v>2</v>
@@ -28888,7 +28888,7 @@
         <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>-1</v>
+        <v>882</v>
       </c>
       <c r="BG61" t="n">
         <v>2</v>
@@ -29344,7 +29344,7 @@
         <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>-1</v>
+        <v>400</v>
       </c>
       <c r="BG62" t="n">
         <v>2</v>
@@ -29720,12 +29720,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC63" t="n">
@@ -29816,7 +29816,7 @@
         <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>-1</v>
+        <v>322</v>
       </c>
       <c r="BG63" t="n">
         <v>2</v>
@@ -30288,7 +30288,7 @@
         <v>0</v>
       </c>
       <c r="BF64" t="n">
-        <v>-1</v>
+        <v>22564</v>
       </c>
       <c r="BG64" t="n">
         <v>2</v>
@@ -30760,7 +30760,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>-1</v>
+        <v>5241</v>
       </c>
       <c r="BG65" t="n">
         <v>2</v>
@@ -31192,7 +31192,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>-1</v>
+        <v>1923</v>
       </c>
       <c r="BG66" t="n">
         <v>2</v>
@@ -31656,7 +31656,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>-1</v>
+        <v>555</v>
       </c>
       <c r="BG67" t="n">
         <v>2</v>
@@ -32096,7 +32096,7 @@
         <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>-1</v>
+        <v>4022</v>
       </c>
       <c r="BG68" t="n">
         <v>2</v>
@@ -32560,7 +32560,7 @@
         <v>0</v>
       </c>
       <c r="BF69" t="n">
-        <v>-1</v>
+        <v>6554</v>
       </c>
       <c r="BG69" t="n">
         <v>2</v>
@@ -33024,7 +33024,7 @@
         <v>0</v>
       </c>
       <c r="BF70" t="n">
-        <v>-1</v>
+        <v>2742</v>
       </c>
       <c r="BG70" t="n">
         <v>2</v>
@@ -33496,7 +33496,7 @@
         <v>0</v>
       </c>
       <c r="BF71" t="n">
-        <v>-1</v>
+        <v>463</v>
       </c>
       <c r="BG71" t="n">
         <v>2</v>
@@ -33968,7 +33968,7 @@
         <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>-1</v>
+        <v>1100</v>
       </c>
       <c r="BG72" t="n">
         <v>2</v>
@@ -34440,7 +34440,7 @@
         <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>-1</v>
+        <v>17202</v>
       </c>
       <c r="BG73" t="n">
         <v>2</v>
@@ -34912,7 +34912,7 @@
         <v>0</v>
       </c>
       <c r="BF74" t="n">
-        <v>-1</v>
+        <v>1574</v>
       </c>
       <c r="BG74" t="n">
         <v>2</v>
@@ -35288,12 +35288,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Stadion Maksimir</t>
+          <t>Stadion Kranjčevićeva</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Maksimirska cesta 128, Zagreb</t>
+          <t>Kranjčevićeva 4, Zagreb</t>
         </is>
       </c>
       <c r="AC75" t="n">
@@ -35384,7 +35384,7 @@
         <v>0</v>
       </c>
       <c r="BF75" t="n">
-        <v>-1</v>
+        <v>513</v>
       </c>
       <c r="BG75" t="n">
         <v>2</v>
@@ -35856,7 +35856,7 @@
         <v>0</v>
       </c>
       <c r="BF76" t="n">
-        <v>-1</v>
+        <v>3391</v>
       </c>
       <c r="BG76" t="n">
         <v>2</v>
@@ -36304,7 +36304,7 @@
         <v>0</v>
       </c>
       <c r="BF77" t="n">
-        <v>-1</v>
+        <v>1130</v>
       </c>
       <c r="BG77" t="n">
         <v>2</v>
@@ -36776,7 +36776,7 @@
         <v>0</v>
       </c>
       <c r="BF78" t="n">
-        <v>-1</v>
+        <v>17028</v>
       </c>
       <c r="BG78" t="n">
         <v>2</v>
@@ -37248,7 +37248,7 @@
         <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>-1</v>
+        <v>4677</v>
       </c>
       <c r="BG79" t="n">
         <v>2</v>
@@ -37696,7 +37696,7 @@
         <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>-1</v>
+        <v>1012</v>
       </c>
       <c r="BG80" t="n">
         <v>2</v>
@@ -38168,7 +38168,7 @@
         <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>-1</v>
+        <v>2734</v>
       </c>
       <c r="BG81" t="n">
         <v>2</v>
@@ -38640,7 +38640,7 @@
         <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>-1</v>
+        <v>493</v>
       </c>
       <c r="BG82" t="n">
         <v>2</v>
@@ -39100,7 +39100,7 @@
         <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>-1</v>
+        <v>2042</v>
       </c>
       <c r="BG83" t="n">
         <v>2</v>
@@ -39572,7 +39572,7 @@
         <v>0</v>
       </c>
       <c r="BF84" t="n">
-        <v>-1</v>
+        <v>2813</v>
       </c>
       <c r="BG84" t="n">
         <v>2</v>
@@ -40036,7 +40036,7 @@
         <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>-1</v>
+        <v>3055</v>
       </c>
       <c r="BG85" t="n">
         <v>2</v>
@@ -40500,7 +40500,7 @@
         <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>-1</v>
+        <v>956</v>
       </c>
       <c r="BG86" t="n">
         <v>2</v>
@@ -40956,7 +40956,7 @@
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>-1</v>
+        <v>2026</v>
       </c>
       <c r="BG87" t="n">
         <v>2</v>
@@ -41428,7 +41428,7 @@
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>-1</v>
+        <v>6270</v>
       </c>
       <c r="BG88" t="n">
         <v>2</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL136" headerRowCount="1">
-  <autoFilter ref="A1:EL136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL139" headerRowCount="1">
+  <autoFilter ref="A1:EL139"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL136"/>
+  <dimension ref="A1:EL139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE6" t="n">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE7" t="n">
         <v>0.21</v>
@@ -5049,7 +5049,7 @@
         <v>1.07</v>
       </c>
       <c r="DE9" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE10" t="n">
         <v>1.07</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -7415,7 +7415,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7846,10 +7846,10 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -7879,7 +7879,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>100</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE18" t="n">
         <v>0.62</v>
@@ -9718,7 +9718,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE19" t="n">
         <v>1.21</v>
@@ -10687,7 +10687,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -12046,7 +12046,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE24" t="n">
         <v>2.07</v>
@@ -12079,7 +12079,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12505,7 +12505,7 @@
         <v>1.57</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF25" t="n">
         <v>1.5</v>
@@ -12977,7 +12977,7 @@
         <v>2.07</v>
       </c>
       <c r="DE26" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13438,7 +13438,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE27" t="n">
         <v>1.21</v>
@@ -13902,7 +13902,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE28" t="n">
         <v>1.85</v>
@@ -15286,7 +15286,7 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE31" t="n">
         <v>1</v>
@@ -15319,7 +15319,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16695,7 +16695,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17137,7 +17137,7 @@
         <v>1.46</v>
       </c>
       <c r="DE35" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -17577,7 +17577,7 @@
         <v>1.31</v>
       </c>
       <c r="DE36" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF36" t="n">
         <v>0.67</v>
@@ -18006,7 +18006,7 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE37" t="n">
         <v>0.21</v>
@@ -19369,7 +19369,7 @@
         <v>1.29</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF40" t="n">
         <v>3</v>
@@ -19399,7 +19399,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19822,7 +19822,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE41" t="n">
         <v>0.86</v>
@@ -19855,7 +19855,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -21222,10 +21222,10 @@
         <v>88</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF44" t="n">
         <v>2</v>
@@ -21255,7 +21255,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21697,7 +21697,7 @@
         <v>1.29</v>
       </c>
       <c r="DE45" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21727,7 +21727,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23062,10 +23062,10 @@
         <v>88</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE48" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF48" t="n">
         <v>2.25</v>
@@ -23095,7 +23095,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23518,10 +23518,10 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF49" t="n">
         <v>2.25</v>
@@ -23551,7 +23551,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24471,7 +24471,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25814,7 +25814,7 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE54" t="n">
         <v>0.86</v>
@@ -25847,7 +25847,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26257,7 +26257,7 @@
         <v>1.79</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -26287,7 +26287,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27190,10 +27190,10 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE57" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF57" t="n">
         <v>2.4</v>
@@ -27223,7 +27223,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28094,7 +28094,7 @@
         <v>90</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE59" t="n">
         <v>1.85</v>
@@ -28599,7 +28599,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -30441,7 +30441,7 @@
         <v>2.07</v>
       </c>
       <c r="DE64" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF64" t="n">
         <v>2.17</v>
@@ -31342,10 +31342,10 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE66" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF66" t="n">
         <v>1.5</v>
@@ -31375,7 +31375,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31806,7 +31806,7 @@
         <v>83</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE67" t="n">
         <v>0.21</v>
@@ -32246,7 +32246,7 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE68" t="n">
         <v>1.07</v>
@@ -32279,7 +32279,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -34121,7 +34121,7 @@
         <v>1.31</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF72" t="n">
         <v>1.29</v>
@@ -35537,7 +35537,7 @@
         <v>1.57</v>
       </c>
       <c r="DE75" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF75" t="n">
         <v>1.57</v>
@@ -36039,7 +36039,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36454,7 +36454,7 @@
         <v>77</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE77" t="n">
         <v>1</v>
@@ -36487,7 +36487,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36926,7 +36926,7 @@
         <v>86</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE78" t="n">
         <v>1.85</v>
@@ -37846,7 +37846,7 @@
         <v>86</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE80" t="n">
         <v>0.62</v>
@@ -39283,7 +39283,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40186,7 +40186,7 @@
         <v>82</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE85" t="n">
         <v>2.07</v>
@@ -40219,7 +40219,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40650,7 +40650,7 @@
         <v>88</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE86" t="n">
         <v>1.21</v>
@@ -41139,7 +41139,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -41578,7 +41578,7 @@
         <v>88</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE88" t="n">
         <v>0.62</v>
@@ -42527,7 +42527,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42969,7 +42969,7 @@
         <v>1.46</v>
       </c>
       <c r="DE91" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF91" t="n">
         <v>1.88</v>
@@ -43943,7 +43943,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44871,7 +44871,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45343,7 +45343,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46686,7 +46686,7 @@
         <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE99" t="n">
         <v>1.07</v>
@@ -46719,7 +46719,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47161,7 +47161,7 @@
         <v>1.07</v>
       </c>
       <c r="DE100" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF100" t="n">
         <v>0.8</v>
@@ -47191,7 +47191,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47630,7 +47630,7 @@
         <v>90</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE101" t="n">
         <v>0.21</v>
@@ -49470,10 +49470,10 @@
         <v>89</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF105" t="n">
         <v>1.67</v>
@@ -49503,7 +49503,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49975,7 +49975,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50390,7 +50390,7 @@
         <v>90</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE107" t="n">
         <v>0.62</v>
@@ -50862,7 +50862,7 @@
         <v>91</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE108" t="n">
         <v>1.21</v>
@@ -51343,7 +51343,7 @@
         <v>2.93</v>
       </c>
       <c r="DO109" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -53641,7 +53641,7 @@
         <v>1.57</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF114" t="n">
         <v>1.64</v>
@@ -54102,7 +54102,7 @@
         <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE115" t="n">
         <v>2.07</v>
@@ -54135,7 +54135,7 @@
         <v>3.48</v>
       </c>
       <c r="DO115" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54561,7 +54561,7 @@
         <v>2.07</v>
       </c>
       <c r="DE116" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF116" t="n">
         <v>2.09</v>
@@ -55006,7 +55006,7 @@
         <v>92</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE117" t="n">
         <v>1.21</v>
@@ -55942,7 +55942,7 @@
         <v>78</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE119" t="n">
         <v>1.85</v>
@@ -56886,7 +56886,7 @@
         <v>82</v>
       </c>
       <c r="DD121" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE121" t="n">
         <v>1</v>
@@ -56919,7 +56919,7 @@
         <v>3.58</v>
       </c>
       <c r="DO121" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57329,7 +57329,7 @@
         <v>1.46</v>
       </c>
       <c r="DE122" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF122" t="n">
         <v>1.45</v>
@@ -57799,7 +57799,7 @@
         <v>2.55</v>
       </c>
       <c r="DO123" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59125,7 +59125,7 @@
         <v>1.31</v>
       </c>
       <c r="DE126" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF126" t="n">
         <v>1.55</v>
@@ -59570,7 +59570,7 @@
         <v>80</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DE127" t="n">
         <v>0.21</v>
@@ -60059,7 +60059,7 @@
         <v>3.04</v>
       </c>
       <c r="DO128" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP128" t="b">
         <v>0</v>
@@ -60498,7 +60498,7 @@
         <v>85</v>
       </c>
       <c r="DD129" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE129" t="n">
         <v>0.86</v>
@@ -60531,7 +60531,7 @@
         <v>3.31</v>
       </c>
       <c r="DO129" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -63290,10 +63290,10 @@
         <v>83</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="DE135" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="DF135" t="n">
         <v>1.92</v>
@@ -63323,7 +63323,7 @@
         <v>3.12</v>
       </c>
       <c r="DO135" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP135" t="b">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1.29</v>
       </c>
       <c r="DE136" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DF136" t="n">
         <v>1.15</v>
@@ -63779,7 +63779,7 @@
         <v>2.81</v>
       </c>
       <c r="DO136" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -63866,6 +63866,1366 @@
       <c r="EJ136" t="inlineStr"/>
       <c r="EK136" t="inlineStr"/>
       <c r="EL136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>28</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>46115.67708333334</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>8</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="n">
+        <v>9</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3</v>
+      </c>
+      <c r="N137" t="n">
+        <v>5</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>5</v>
+      </c>
+      <c r="R137" t="n">
+        <v>2</v>
+      </c>
+      <c r="S137" t="n">
+        <v>11</v>
+      </c>
+      <c r="T137" t="n">
+        <v>3</v>
+      </c>
+      <c r="U137" t="n">
+        <v>16</v>
+      </c>
+      <c r="V137" t="n">
+        <v>5</v>
+      </c>
+      <c r="W137" t="n">
+        <v>19</v>
+      </c>
+      <c r="X137" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA137" t="inlineStr"/>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>1437</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU137" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV137" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW137" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX137" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY137" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ137" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA137" t="n">
+        <v>81</v>
+      </c>
+      <c r="DB137" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC137" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD137" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE137" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF137" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DG137" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH137" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DI137" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DJ137" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK137" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL137" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM137" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN137" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DO137" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU137" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV137" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW137" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="DX137" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="DY137" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="DZ137" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EA137" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EB137" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC137" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="ED137" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EE137" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EF137" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EG137" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH137" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EI137" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ137" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EK137" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EL137" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>28</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>46116.54166666666</v>
+      </c>
+      <c r="G138" t="n">
+        <v>7</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>7</v>
+      </c>
+      <c r="J138" t="n">
+        <v>11</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>11</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>12</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2</v>
+      </c>
+      <c r="S138" t="n">
+        <v>15</v>
+      </c>
+      <c r="T138" t="n">
+        <v>4</v>
+      </c>
+      <c r="U138" t="n">
+        <v>27</v>
+      </c>
+      <c r="V138" t="n">
+        <v>6</v>
+      </c>
+      <c r="W138" t="n">
+        <v>12</v>
+      </c>
+      <c r="X138" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>122</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>9109</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>53</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU138" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV138" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW138" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX138" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY138" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ138" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA138" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB138" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC138" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD138" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DE138" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF138" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DG138" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DH138" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI138" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DJ138" t="n">
+        <v>31</v>
+      </c>
+      <c r="DK138" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL138" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DM138" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN138" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="DO138" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU138" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV138" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW138" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="DX138" t="inlineStr">
+        <is>
+          <t>6.48</t>
+        </is>
+      </c>
+      <c r="DY138" t="inlineStr">
+        <is>
+          <t>12.81</t>
+        </is>
+      </c>
+      <c r="DZ138" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EA138" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EB138" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EC138" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="ED138" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EE138" t="inlineStr"/>
+      <c r="EF138" t="inlineStr"/>
+      <c r="EG138" t="inlineStr"/>
+      <c r="EH138" t="inlineStr"/>
+      <c r="EI138" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EJ138" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EK138" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL138" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>28</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46116.65625</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>2</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>5</v>
+      </c>
+      <c r="K139" t="n">
+        <v>6</v>
+      </c>
+      <c r="L139" t="n">
+        <v>11</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2</v>
+      </c>
+      <c r="R139" t="n">
+        <v>4</v>
+      </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
+      <c r="T139" t="n">
+        <v>7</v>
+      </c>
+      <c r="U139" t="n">
+        <v>17</v>
+      </c>
+      <c r="V139" t="n">
+        <v>11</v>
+      </c>
+      <c r="W139" t="n">
+        <v>12</v>
+      </c>
+      <c r="X139" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA139" t="inlineStr"/>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1337</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>31</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW139" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="DX139" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED139" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EE139" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EF139" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EG139" t="inlineStr"/>
+      <c r="EH139" t="inlineStr"/>
+      <c r="EI139" t="inlineStr"/>
+      <c r="EJ139" t="inlineStr"/>
+      <c r="EK139" t="inlineStr"/>
+      <c r="EL139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL139" headerRowCount="1">
-  <autoFilter ref="A1:EL139"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL141" headerRowCount="1">
+  <autoFilter ref="A1:EL141"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL139"/>
+  <dimension ref="A1:EL141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -4143,7 +4143,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4574,10 +4574,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5999,7 +5999,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6438,7 +6438,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE12" t="n">
         <v>1.21</v>
@@ -6471,7 +6471,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -8351,7 +8351,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         <v>84</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE17" t="n">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9249,7 +9249,7 @@
         <v>1.71</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9279,7 +9279,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10185,7 +10185,7 @@
         <v>1.07</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF20" t="n">
         <v>0.5</v>
@@ -10215,7 +10215,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11126,7 +11126,7 @@
         <v>88</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE22" t="n">
         <v>1</v>
@@ -11159,7 +11159,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11598,7 +11598,7 @@
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE23" t="n">
         <v>0.86</v>
@@ -11631,7 +11631,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12535,7 +12535,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13007,7 +13007,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13471,7 +13471,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13905,7 +13905,7 @@
         <v>1.64</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14377,7 +14377,7 @@
         <v>1.79</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF29" t="n">
         <v>1</v>
@@ -14407,7 +14407,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14863,7 +14863,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15767,7 +15767,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16239,7 +16239,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17134,7 +17134,7 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE35" t="n">
         <v>0.71</v>
@@ -17167,7 +17167,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17574,7 +17574,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE36" t="n">
         <v>1.14</v>
@@ -17607,7 +17607,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18039,7 +18039,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18487,7 +18487,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18913,7 +18913,7 @@
         <v>2.07</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18943,7 +18943,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20286,7 +20286,7 @@
         <v>67</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE42" t="n">
         <v>1.07</v>
@@ -20319,7 +20319,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20758,10 +20758,10 @@
         <v>100</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF43" t="n">
         <v>1.25</v>
@@ -20791,7 +20791,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22199,7 +22199,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22614,10 +22614,10 @@
         <v>90</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -22647,7 +22647,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23982,10 +23982,10 @@
         <v>59</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF50" t="n">
         <v>2.5</v>
@@ -24015,7 +24015,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24897,7 +24897,7 @@
         <v>1.29</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF52" t="n">
         <v>0.75</v>
@@ -24927,7 +24927,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26726,7 +26726,7 @@
         <v>74</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE56" t="n">
         <v>2.07</v>
@@ -26759,7 +26759,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27646,7 +27646,7 @@
         <v>80</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE58" t="n">
         <v>0.21</v>
@@ -27679,7 +27679,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28097,7 +28097,7 @@
         <v>1.71</v>
       </c>
       <c r="DE59" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF59" t="n">
         <v>2</v>
@@ -28127,7 +28127,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -29041,7 +29041,7 @@
         <v>1.29</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF61" t="n">
         <v>0.6</v>
@@ -29071,7 +29071,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29999,7 +29999,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30471,7 +30471,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30910,7 +30910,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE65" t="n">
         <v>2.07</v>
@@ -30943,7 +30943,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31839,7 +31839,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32713,7 +32713,7 @@
         <v>1.79</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF69" t="n">
         <v>1.33</v>
@@ -32743,7 +32743,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33177,7 +33177,7 @@
         <v>1.07</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF70" t="n">
         <v>1</v>
@@ -33207,7 +33207,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33679,7 +33679,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34118,7 +34118,7 @@
         <v>73</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE72" t="n">
         <v>0.71</v>
@@ -34151,7 +34151,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34623,7 +34623,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35062,7 +35062,7 @@
         <v>71</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE74" t="n">
         <v>0.86</v>
@@ -35095,7 +35095,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35567,7 +35567,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36929,7 +36929,7 @@
         <v>2.64</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF78" t="n">
         <v>2.57</v>
@@ -36959,7 +36959,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37431,7 +37431,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37849,7 +37849,7 @@
         <v>1.64</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF80" t="n">
         <v>1.71</v>
@@ -37879,7 +37879,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38351,7 +38351,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38790,7 +38790,7 @@
         <v>63</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE82" t="n">
         <v>1.07</v>
@@ -38823,7 +38823,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39725,7 +39725,7 @@
         <v>1.57</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF84" t="n">
         <v>1.5</v>
@@ -39755,7 +39755,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40683,7 +40683,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41581,7 +41581,7 @@
         <v>2.64</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF88" t="n">
         <v>2.38</v>
@@ -41611,7 +41611,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42071,7 +42071,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42966,7 +42966,7 @@
         <v>82</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE91" t="n">
         <v>1.14</v>
@@ -42999,7 +42999,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43471,7 +43471,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44399,7 +44399,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -45766,10 +45766,10 @@
         <v>84</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF97" t="n">
         <v>1.67</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46241,7 +46241,7 @@
         <v>1.29</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF98" t="n">
         <v>1</v>
@@ -46271,7 +46271,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47663,7 +47663,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48127,7 +48127,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48550,7 +48550,7 @@
         <v>73</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE103" t="n">
         <v>1.21</v>
@@ -48583,7 +48583,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49039,7 +49039,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50393,7 +50393,7 @@
         <v>1.71</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF107" t="n">
         <v>1.7</v>
@@ -50423,7 +50423,7 @@
         <v>3.16</v>
       </c>
       <c r="DO107" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50895,7 +50895,7 @@
         <v>3.34</v>
       </c>
       <c r="DO108" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51815,7 +51815,7 @@
         <v>2.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP110" t="b">
         <v>0</v>
@@ -52257,7 +52257,7 @@
         <v>1.07</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF111" t="n">
         <v>1</v>
@@ -52287,7 +52287,7 @@
         <v>3.25</v>
       </c>
       <c r="DO111" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52726,7 +52726,7 @@
         <v>67</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE112" t="n">
         <v>0.86</v>
@@ -52759,7 +52759,7 @@
         <v>2.83</v>
       </c>
       <c r="DO112" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53182,7 +53182,7 @@
         <v>75</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE113" t="n">
         <v>1</v>
@@ -53215,7 +53215,7 @@
         <v>2.9</v>
       </c>
       <c r="DO113" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53671,7 +53671,7 @@
         <v>2.83</v>
       </c>
       <c r="DO114" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54591,7 +54591,7 @@
         <v>3.48</v>
       </c>
       <c r="DO116" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55039,7 +55039,7 @@
         <v>2.92</v>
       </c>
       <c r="DO117" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55511,7 +55511,7 @@
         <v>2.73</v>
       </c>
       <c r="DO118" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55945,7 +55945,7 @@
         <v>1.64</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF119" t="n">
         <v>1.64</v>
@@ -55975,7 +55975,7 @@
         <v>3.2</v>
       </c>
       <c r="DO119" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56417,7 +56417,7 @@
         <v>1.79</v>
       </c>
       <c r="DE120" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF120" t="n">
         <v>1.83</v>
@@ -56447,7 +56447,7 @@
         <v>3.15</v>
       </c>
       <c r="DO120" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -57326,7 +57326,7 @@
         <v>87</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE122" t="n">
         <v>0.71</v>
@@ -57359,7 +57359,7 @@
         <v>2.8</v>
       </c>
       <c r="DO122" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -58255,7 +58255,7 @@
         <v>2.66</v>
       </c>
       <c r="DO124" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58695,7 +58695,7 @@
         <v>3.77</v>
       </c>
       <c r="DO125" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -59122,7 +59122,7 @@
         <v>73</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE126" t="n">
         <v>1.14</v>
@@ -59155,7 +59155,7 @@
         <v>3.1</v>
       </c>
       <c r="DO126" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59603,7 +59603,7 @@
         <v>2.62</v>
       </c>
       <c r="DO127" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -60973,7 +60973,7 @@
         <v>2.07</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DF130" t="n">
         <v>2</v>
@@ -61003,7 +61003,7 @@
         <v>3.16</v>
       </c>
       <c r="DO130" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61475,7 +61475,7 @@
         <v>2.97</v>
       </c>
       <c r="DO131" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61898,7 +61898,7 @@
         <v>72</v>
       </c>
       <c r="DD132" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="DE132" t="n">
         <v>1.07</v>
@@ -61931,7 +61931,7 @@
         <v>2.63</v>
       </c>
       <c r="DO132" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62370,10 +62370,10 @@
         <v>67</v>
       </c>
       <c r="DD133" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DE133" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DF133" t="n">
         <v>1.42</v>
@@ -62403,7 +62403,7 @@
         <v>3.28</v>
       </c>
       <c r="DO133" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62875,7 +62875,7 @@
         <v>3.33</v>
       </c>
       <c r="DO134" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63949,10 +63949,10 @@
         <v>12</v>
       </c>
       <c r="Y137" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z137" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr"/>
@@ -64395,13 +64395,13 @@
         <v>2</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T138" t="n">
         <v>4</v>
       </c>
       <c r="U138" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V138" t="n">
         <v>6</v>
@@ -64576,13 +64576,13 @@
         <v>53</v>
       </c>
       <c r="BZ138" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="CA138" t="n">
         <v>0.65</v>
       </c>
       <c r="CB138" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="CC138" t="n">
         <v>1</v>
@@ -64869,10 +64869,10 @@
         <v>15</v>
       </c>
       <c r="Y139" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z139" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr"/>
@@ -65226,6 +65226,934 @@
       <c r="EJ139" t="inlineStr"/>
       <c r="EK139" t="inlineStr"/>
       <c r="EL139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>28</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>46119.57291666666</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>4</v>
+      </c>
+      <c r="K140" t="n">
+        <v>4</v>
+      </c>
+      <c r="L140" t="n">
+        <v>8</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>4</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" t="n">
+        <v>5</v>
+      </c>
+      <c r="U140" t="n">
+        <v>5</v>
+      </c>
+      <c r="V140" t="n">
+        <v>6</v>
+      </c>
+      <c r="W140" t="n">
+        <v>18</v>
+      </c>
+      <c r="X140" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>92</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>154</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>46</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>12</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW140" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="DX140" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="DY140" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DZ140" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EB140" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="ED140" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE140" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF140" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EG140" t="inlineStr"/>
+      <c r="EH140" t="inlineStr"/>
+      <c r="EI140" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL140" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>28</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>46119.66666666666</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3</v>
+      </c>
+      <c r="I141" t="n">
+        <v>4</v>
+      </c>
+      <c r="J141" t="n">
+        <v>2</v>
+      </c>
+      <c r="K141" t="n">
+        <v>8</v>
+      </c>
+      <c r="L141" t="n">
+        <v>10</v>
+      </c>
+      <c r="M141" t="n">
+        <v>2</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>2</v>
+      </c>
+      <c r="R141" t="n">
+        <v>8</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="n">
+        <v>11</v>
+      </c>
+      <c r="U141" t="n">
+        <v>7</v>
+      </c>
+      <c r="V141" t="n">
+        <v>19</v>
+      </c>
+      <c r="W141" t="n">
+        <v>18</v>
+      </c>
+      <c r="X141" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>68</v>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>Stadion Aldo Drosina</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>Marsovo polje, Pula</t>
+        </is>
+      </c>
+      <c r="AC141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>65</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU141" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV141" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW141" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX141" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY141" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ141" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA141" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB141" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC141" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD141" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE141" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DF141" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DG141" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DH141" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI141" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DJ141" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK141" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL141" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DN141" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DO141" t="n">
+        <v>28</v>
+      </c>
+      <c r="DP141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU141" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV141" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW141" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="DX141" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="DY141" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="DZ141" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EA141" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EB141" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EC141" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED141" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EE141" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EF141" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EG141" t="inlineStr"/>
+      <c r="EH141" t="inlineStr"/>
+      <c r="EI141" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EJ141" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EK141" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EL141" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -65412,7 +65412,7 @@
         <v>0</v>
       </c>
       <c r="BF140" t="n">
-        <v>-1</v>
+        <v>515</v>
       </c>
       <c r="BG140" t="n">
         <v>2</v>
@@ -65876,7 +65876,7 @@
         <v>0</v>
       </c>
       <c r="BF141" t="n">
-        <v>-1</v>
+        <v>6028</v>
       </c>
       <c r="BG141" t="n">
         <v>2</v>

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL141" headerRowCount="1">
-  <autoFilter ref="A1:EL141"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL142" headerRowCount="1">
+  <autoFilter ref="A1:EL142"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL141"/>
+  <dimension ref="A1:EL142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE2" t="n">
         <v>0.21</v>
@@ -3177,7 +3177,7 @@
         <v>2.07</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -6441,7 +6441,7 @@
         <v>1.29</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
         <v>75</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         <v>2.64</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -12502,7 +12502,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE25" t="n">
         <v>0.71</v>
@@ -13441,7 +13441,7 @@
         <v>1.71</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -16206,7 +16206,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE33" t="n">
         <v>1.07</v>
@@ -18457,7 +18457,7 @@
         <v>1.79</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -22166,7 +22166,7 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE46" t="n">
         <v>2.07</v>
@@ -25366,10 +25366,10 @@
         <v>80</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -25399,7 +25399,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -29966,7 +29966,7 @@
         <v>75</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE63" t="n">
         <v>0.86</v>
@@ -33649,7 +33649,7 @@
         <v>1.29</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -35534,7 +35534,7 @@
         <v>86</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE75" t="n">
         <v>1.14</v>
@@ -38321,7 +38321,7 @@
         <v>1.07</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -39722,7 +39722,7 @@
         <v>76</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE84" t="n">
         <v>1.93</v>
@@ -40653,7 +40653,7 @@
         <v>1.64</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF86" t="n">
         <v>1.88</v>
@@ -43438,7 +43438,7 @@
         <v>89</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE92" t="n">
         <v>0.21</v>
@@ -44369,7 +44369,7 @@
         <v>2.07</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF94" t="n">
         <v>2.22</v>
@@ -45799,7 +45799,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -48094,7 +48094,7 @@
         <v>79</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE102" t="n">
         <v>1</v>
@@ -48553,7 +48553,7 @@
         <v>1.29</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF103" t="n">
         <v>1.44</v>
@@ -50865,7 +50865,7 @@
         <v>2.64</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF108" t="n">
         <v>2.5</v>
@@ -53638,7 +53638,7 @@
         <v>91</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE114" t="n">
         <v>0.71</v>
@@ -55009,7 +55009,7 @@
         <v>1.71</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF117" t="n">
         <v>1.82</v>
@@ -58222,7 +58222,7 @@
         <v>80</v>
       </c>
       <c r="DD124" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE124" t="n">
         <v>1.07</v>
@@ -61445,7 +61445,7 @@
         <v>1.79</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DF131" t="n">
         <v>1.92</v>
@@ -62842,7 +62842,7 @@
         <v>81</v>
       </c>
       <c r="DD134" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DE134" t="n">
         <v>2.07</v>
@@ -66155,6 +66155,454 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>29</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>46123.58333333334</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" t="n">
+        <v>5</v>
+      </c>
+      <c r="K142" t="n">
+        <v>4</v>
+      </c>
+      <c r="L142" t="n">
+        <v>9</v>
+      </c>
+      <c r="M142" t="n">
+        <v>2</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>3</v>
+      </c>
+      <c r="R142" t="n">
+        <v>3</v>
+      </c>
+      <c r="S142" t="n">
+        <v>7</v>
+      </c>
+      <c r="T142" t="n">
+        <v>11</v>
+      </c>
+      <c r="U142" t="n">
+        <v>10</v>
+      </c>
+      <c r="V142" t="n">
+        <v>14</v>
+      </c>
+      <c r="W142" t="n">
+        <v>12</v>
+      </c>
+      <c r="X142" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Stadion Kranjčevićeva</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Kranjčevićeva 4, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1859</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>69</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>105</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU142" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV142" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW142" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX142" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY142" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ142" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA142" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB142" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC142" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD142" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE142" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG142" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DH142" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DI142" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ142" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK142" t="n">
+        <v>18</v>
+      </c>
+      <c r="DL142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM142" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DN142" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DO142" t="n">
+        <v>29</v>
+      </c>
+      <c r="DP142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ142" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV142" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW142" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="DX142" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="DY142" t="inlineStr">
+        <is>
+          <t>4.92</t>
+        </is>
+      </c>
+      <c r="DZ142" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EA142" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EB142" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EC142" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="ED142" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE142" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EF142" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EG142" t="inlineStr"/>
+      <c r="EH142" t="inlineStr"/>
+      <c r="EI142" t="inlineStr"/>
+      <c r="EJ142" t="inlineStr"/>
+      <c r="EK142" t="inlineStr"/>
+      <c r="EL142" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
+++ b/data/matches/leagues/Croatia_HNL_2025-2026.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL176" headerRowCount="1">
-  <autoFilter ref="A1:EL176"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL181" headerRowCount="1">
+  <autoFilter ref="A1:EL181"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL176"/>
+  <dimension ref="A1:EL181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.6" customWidth="1" min="1" max="1"/>
@@ -1765,7 +1765,7 @@
         <v>1.61</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2218,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE3" t="n">
         <v>2.28</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2690,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3162,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4098,10 +4098,10 @@
         <v>50</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
         <v>1.07</v>
       </c>
       <c r="DO7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4565,7 +4565,7 @@
         <v>1.28</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5034,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE9" t="n">
         <v>1.17</v>
@@ -5067,7 +5067,7 @@
         <v>1.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP9" t="b">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5954,10 +5954,10 @@
         <v>100</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -5987,7 +5987,7 @@
         <v>3.2</v>
       </c>
       <c r="DO11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6429,7 +6429,7 @@
         <v>1.17</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.02</v>
       </c>
       <c r="DO12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6901,7 +6901,7 @@
         <v>1.61</v>
       </c>
       <c r="DE13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF13" t="n">
         <v>3</v>
@@ -6931,7 +6931,7 @@
         <v>2.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7370,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE14" t="n">
         <v>2.28</v>
@@ -7403,7 +7403,7 @@
         <v>4.19</v>
       </c>
       <c r="DO14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7834,7 +7834,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE15" t="n">
         <v>0.89</v>
@@ -7867,7 +7867,7 @@
         <v>2.01</v>
       </c>
       <c r="DO15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP15" t="b">
         <v>0</v>
@@ -8306,10 +8306,10 @@
         <v>25</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8339,7 +8339,7 @@
         <v>3.11</v>
       </c>
       <c r="DO16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8781,7 +8781,7 @@
         <v>1.17</v>
       </c>
       <c r="DE17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -8811,7 +8811,7 @@
         <v>2.49</v>
       </c>
       <c r="DO17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9237,7 +9237,7 @@
         <v>1.61</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF18" t="n">
         <v>3</v>
@@ -9267,7 +9267,7 @@
         <v>3.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9706,10 +9706,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9739,7 +9739,7 @@
         <v>4.33</v>
       </c>
       <c r="DO19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10170,7 +10170,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE20" t="n">
         <v>1.67</v>
@@ -10203,7 +10203,7 @@
         <v>1.83</v>
       </c>
       <c r="DO20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10642,7 +10642,7 @@
         <v>75</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE21" t="n">
         <v>1.17</v>
@@ -10675,7 +10675,7 @@
         <v>2.57</v>
       </c>
       <c r="DO21" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11117,7 +11117,7 @@
         <v>1.28</v>
       </c>
       <c r="DE22" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF22" t="n">
         <v>1</v>
@@ -11147,7 +11147,7 @@
         <v>3.47</v>
       </c>
       <c r="DO22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11589,7 +11589,7 @@
         <v>1.17</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF23" t="n">
         <v>1</v>
@@ -11619,7 +11619,7 @@
         <v>2.02</v>
       </c>
       <c r="DO23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12034,7 +12034,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE24" t="n">
         <v>2.28</v>
@@ -12067,7 +12067,7 @@
         <v>3.25</v>
       </c>
       <c r="DO24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12523,7 +12523,7 @@
         <v>2.51</v>
       </c>
       <c r="DO25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12962,7 +12962,7 @@
         <v>17</v>
       </c>
       <c r="DD26" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE26" t="n">
         <v>1.17</v>
@@ -12995,7 +12995,7 @@
         <v>3.47</v>
       </c>
       <c r="DO26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13429,7 +13429,7 @@
         <v>1.61</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF27" t="n">
         <v>1.5</v>
@@ -13459,7 +13459,7 @@
         <v>3</v>
       </c>
       <c r="DO27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13890,7 +13890,7 @@
         <v>84</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE28" t="n">
         <v>1.67</v>
@@ -13923,7 +13923,7 @@
         <v>3.5</v>
       </c>
       <c r="DO28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14362,10 +14362,10 @@
         <v>84</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF29" t="n">
         <v>1</v>
@@ -14395,7 +14395,7 @@
         <v>2.97</v>
       </c>
       <c r="DO29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14818,10 +14818,10 @@
         <v>67</v>
       </c>
       <c r="DD30" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF30" t="n">
         <v>0.33</v>
@@ -14851,7 +14851,7 @@
         <v>2.82</v>
       </c>
       <c r="DO30" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15274,10 +15274,10 @@
         <v>80</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15307,7 +15307,7 @@
         <v>4.65</v>
       </c>
       <c r="DO31" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15722,7 +15722,7 @@
         <v>59</v>
       </c>
       <c r="DD32" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE32" t="n">
         <v>2.28</v>
@@ -15755,7 +15755,7 @@
         <v>3.86</v>
       </c>
       <c r="DO32" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16227,7 +16227,7 @@
         <v>2.52</v>
       </c>
       <c r="DO33" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16653,7 +16653,7 @@
         <v>1.33</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -16683,7 +16683,7 @@
         <v>0.91</v>
       </c>
       <c r="DO34" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17155,7 +17155,7 @@
         <v>3.31</v>
       </c>
       <c r="DO35" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17595,7 +17595,7 @@
         <v>2.52</v>
       </c>
       <c r="DO36" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17994,10 +17994,10 @@
         <v>88</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE37" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF37" t="n">
         <v>1.5</v>
@@ -18027,7 +18027,7 @@
         <v>2.75</v>
       </c>
       <c r="DO37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18442,10 +18442,10 @@
         <v>88</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18475,7 +18475,7 @@
         <v>2.62</v>
       </c>
       <c r="DO38" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP38" t="b">
         <v>0</v>
@@ -18898,10 +18898,10 @@
         <v>80</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF39" t="n">
         <v>2</v>
@@ -18931,7 +18931,7 @@
         <v>3.26</v>
       </c>
       <c r="DO39" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19387,7 +19387,7 @@
         <v>3.09</v>
       </c>
       <c r="DO40" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19810,10 +19810,10 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE41" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -19843,7 +19843,7 @@
         <v>3.48</v>
       </c>
       <c r="DO41" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20307,7 +20307,7 @@
         <v>2.6</v>
       </c>
       <c r="DO42" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20779,7 +20779,7 @@
         <v>3.33</v>
       </c>
       <c r="DO43" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21243,7 +21243,7 @@
         <v>3.5</v>
       </c>
       <c r="DO44" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21715,7 +21715,7 @@
         <v>2.84</v>
       </c>
       <c r="DO45" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22187,7 +22187,7 @@
         <v>3.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22605,7 +22605,7 @@
         <v>1.17</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -22635,7 +22635,7 @@
         <v>2.64</v>
       </c>
       <c r="DO47" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23083,7 +23083,7 @@
         <v>3.27</v>
       </c>
       <c r="DO48" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23506,7 +23506,7 @@
         <v>90</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE49" t="n">
         <v>0.89</v>
@@ -23539,7 +23539,7 @@
         <v>4.08</v>
       </c>
       <c r="DO49" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24003,7 +24003,7 @@
         <v>3.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24459,7 +24459,7 @@
         <v>2.57</v>
       </c>
       <c r="DO51" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24915,7 +24915,7 @@
         <v>3.22</v>
       </c>
       <c r="DO52" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25357,7 +25357,7 @@
         <v>1.61</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF53" t="n">
         <v>2</v>
@@ -25387,7 +25387,7 @@
         <v>2.3</v>
       </c>
       <c r="DO53" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25802,10 +25802,10 @@
         <v>70</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF54" t="n">
         <v>1.8</v>
@@ -25835,7 +25835,7 @@
         <v>2.58</v>
       </c>
       <c r="DO54" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26242,7 +26242,7 @@
         <v>72</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE55" t="n">
         <v>0.89</v>
@@ -26275,7 +26275,7 @@
         <v>3.12</v>
       </c>
       <c r="DO55" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26747,7 +26747,7 @@
         <v>3.07</v>
       </c>
       <c r="DO56" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27178,7 +27178,7 @@
         <v>90</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE57" t="n">
         <v>1.17</v>
@@ -27211,7 +27211,7 @@
         <v>3.71</v>
       </c>
       <c r="DO57" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27637,7 +27637,7 @@
         <v>1.28</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF58" t="n">
         <v>2</v>
@@ -27667,7 +27667,7 @@
         <v>2.87</v>
       </c>
       <c r="DO58" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28115,7 +28115,7 @@
         <v>3.51</v>
       </c>
       <c r="DO59" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP59" t="b">
         <v>0</v>
@@ -28554,7 +28554,7 @@
         <v>55</v>
       </c>
       <c r="DD60" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE60" t="n">
         <v>1.17</v>
@@ -28587,7 +28587,7 @@
         <v>3</v>
       </c>
       <c r="DO60" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP60" t="b">
         <v>0</v>
@@ -29029,7 +29029,7 @@
         <v>1.33</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF61" t="n">
         <v>0.6</v>
@@ -29059,7 +29059,7 @@
         <v>2.72</v>
       </c>
       <c r="DO61" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29485,7 +29485,7 @@
         <v>1.33</v>
       </c>
       <c r="DE62" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF62" t="n">
         <v>1</v>
@@ -29515,7 +29515,7 @@
         <v>2.71</v>
       </c>
       <c r="DO62" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29957,7 +29957,7 @@
         <v>1.61</v>
       </c>
       <c r="DE63" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF63" t="n">
         <v>1.67</v>
@@ -29987,7 +29987,7 @@
         <v>2.41</v>
       </c>
       <c r="DO63" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30426,7 +30426,7 @@
         <v>77</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE64" t="n">
         <v>0.89</v>
@@ -30459,7 +30459,7 @@
         <v>3.21</v>
       </c>
       <c r="DO64" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30931,7 +30931,7 @@
         <v>3.32</v>
       </c>
       <c r="DO65" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31330,7 +31330,7 @@
         <v>83</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE66" t="n">
         <v>1.17</v>
@@ -31363,7 +31363,7 @@
         <v>3.18</v>
       </c>
       <c r="DO66" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31797,7 +31797,7 @@
         <v>1.61</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF67" t="n">
         <v>1.83</v>
@@ -31827,7 +31827,7 @@
         <v>3.01</v>
       </c>
       <c r="DO67" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32234,7 +32234,7 @@
         <v>75</v>
       </c>
       <c r="DD68" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE68" t="n">
         <v>1.17</v>
@@ -32267,7 +32267,7 @@
         <v>3.28</v>
       </c>
       <c r="DO68" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32698,7 +32698,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE69" t="n">
         <v>1.67</v>
@@ -32731,7 +32731,7 @@
         <v>3.52</v>
       </c>
       <c r="DO69" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33162,10 +33162,10 @@
         <v>62</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF70" t="n">
         <v>1</v>
@@ -33195,7 +33195,7 @@
         <v>3.13</v>
       </c>
       <c r="DO70" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33637,7 +33637,7 @@
         <v>1.33</v>
       </c>
       <c r="DE71" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF71" t="n">
         <v>1</v>
@@ -33667,7 +33667,7 @@
         <v>2.38</v>
       </c>
       <c r="DO71" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34139,7 +34139,7 @@
         <v>2.69</v>
       </c>
       <c r="DO72" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34578,7 +34578,7 @@
         <v>64</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE73" t="n">
         <v>1.17</v>
@@ -34611,7 +34611,7 @@
         <v>3.12</v>
       </c>
       <c r="DO73" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35053,7 +35053,7 @@
         <v>1.28</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF74" t="n">
         <v>2</v>
@@ -35083,7 +35083,7 @@
         <v>2.53</v>
       </c>
       <c r="DO74" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35555,7 +35555,7 @@
         <v>3.16</v>
       </c>
       <c r="DO75" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36027,7 +36027,7 @@
         <v>3.37</v>
       </c>
       <c r="DO76" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36445,7 +36445,7 @@
         <v>1.61</v>
       </c>
       <c r="DE77" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF77" t="n">
         <v>2</v>
@@ -36475,7 +36475,7 @@
         <v>3.23</v>
       </c>
       <c r="DO77" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
@@ -36914,7 +36914,7 @@
         <v>86</v>
       </c>
       <c r="DD78" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE78" t="n">
         <v>1.67</v>
@@ -36947,7 +36947,7 @@
         <v>3.65</v>
       </c>
       <c r="DO78" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37386,10 +37386,10 @@
         <v>79</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF79" t="n">
         <v>1.57</v>
@@ -37419,7 +37419,7 @@
         <v>3.15</v>
       </c>
       <c r="DO79" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37834,10 +37834,10 @@
         <v>86</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF80" t="n">
         <v>1.71</v>
@@ -37867,7 +37867,7 @@
         <v>3.15</v>
       </c>
       <c r="DO80" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38306,10 +38306,10 @@
         <v>68</v>
       </c>
       <c r="DD81" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -38339,7 +38339,7 @@
         <v>2.72</v>
       </c>
       <c r="DO81" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38811,7 +38811,7 @@
         <v>2.56</v>
       </c>
       <c r="DO82" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39238,10 +39238,10 @@
         <v>64</v>
       </c>
       <c r="DD83" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DE83" t="n">
         <v>0.9399999999999999</v>
-      </c>
-      <c r="DE83" t="n">
-        <v>1</v>
       </c>
       <c r="DF83" t="n">
         <v>0.86</v>
@@ -39271,7 +39271,7 @@
         <v>3.24</v>
       </c>
       <c r="DO83" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39743,7 +39743,7 @@
         <v>2.99</v>
       </c>
       <c r="DO84" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40207,7 +40207,7 @@
         <v>3.56</v>
       </c>
       <c r="DO85" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40638,10 +40638,10 @@
         <v>88</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF86" t="n">
         <v>1.88</v>
@@ -40671,7 +40671,7 @@
         <v>2.72</v>
       </c>
       <c r="DO86" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41094,10 +41094,10 @@
         <v>69</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE87" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF87" t="n">
         <v>0.88</v>
@@ -41127,7 +41127,7 @@
         <v>2.86</v>
       </c>
       <c r="DO87" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP87" t="b">
         <v>0</v>
@@ -41566,10 +41566,10 @@
         <v>88</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE88" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF88" t="n">
         <v>2.38</v>
@@ -41599,7 +41599,7 @@
         <v>3.52</v>
       </c>
       <c r="DO88" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42026,10 +42026,10 @@
         <v>82</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF89" t="n">
         <v>2.13</v>
@@ -42059,7 +42059,7 @@
         <v>3.16</v>
       </c>
       <c r="DO89" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42482,10 +42482,10 @@
         <v>75</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE90" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF90" t="n">
         <v>1.75</v>
@@ -42515,7 +42515,7 @@
         <v>3.33</v>
       </c>
       <c r="DO90" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42987,7 +42987,7 @@
         <v>3.09</v>
       </c>
       <c r="DO91" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43429,7 +43429,7 @@
         <v>1.61</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF92" t="n">
         <v>1.33</v>
@@ -43459,7 +43459,7 @@
         <v>2.63</v>
       </c>
       <c r="DO92" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43898,10 +43898,10 @@
         <v>67</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF93" t="n">
         <v>1.89</v>
@@ -43931,7 +43931,7 @@
         <v>2.98</v>
       </c>
       <c r="DO93" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44354,10 +44354,10 @@
         <v>84</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF94" t="n">
         <v>2.22</v>
@@ -44387,7 +44387,7 @@
         <v>3.12</v>
       </c>
       <c r="DO94" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44826,7 +44826,7 @@
         <v>67</v>
       </c>
       <c r="DD95" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE95" t="n">
         <v>2.28</v>
@@ -44859,7 +44859,7 @@
         <v>3.63</v>
       </c>
       <c r="DO95" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45331,7 +45331,7 @@
         <v>2.54</v>
       </c>
       <c r="DO96" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45757,7 +45757,7 @@
         <v>1.28</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF97" t="n">
         <v>1.67</v>
@@ -45787,7 +45787,7 @@
         <v>2.89</v>
       </c>
       <c r="DO97" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46259,7 +46259,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46707,7 +46707,7 @@
         <v>2.84</v>
       </c>
       <c r="DO99" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47146,7 +47146,7 @@
         <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE100" t="n">
         <v>1.17</v>
@@ -47179,7 +47179,7 @@
         <v>3.25</v>
       </c>
       <c r="DO100" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47618,10 +47618,10 @@
         <v>90</v>
       </c>
       <c r="DD101" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF101" t="n">
         <v>2.44</v>
@@ -47651,7 +47651,7 @@
         <v>3.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48085,7 +48085,7 @@
         <v>1.61</v>
       </c>
       <c r="DE102" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF102" t="n">
         <v>1.5</v>
@@ -48115,7 +48115,7 @@
         <v>2.81</v>
       </c>
       <c r="DO102" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48541,7 +48541,7 @@
         <v>1.17</v>
       </c>
       <c r="DE103" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF103" t="n">
         <v>1.44</v>
@@ -48571,7 +48571,7 @@
         <v>2.64</v>
       </c>
       <c r="DO103" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48994,10 +48994,10 @@
         <v>75</v>
       </c>
       <c r="DD104" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -49027,7 +49027,7 @@
         <v>3.14</v>
       </c>
       <c r="DO104" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49458,7 +49458,7 @@
         <v>89</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE105" t="n">
         <v>0.89</v>
@@ -49491,7 +49491,7 @@
         <v>3.1</v>
       </c>
       <c r="DO105" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49930,7 +49930,7 @@
         <v>75</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE106" t="n">
         <v>2.28</v>
@@ -49963,7 +49963,7 @@
         <v>3.75</v>
       </c>
       <c r="DO106" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP106" t="b">
         <v>0</v>
@@ -50381,7 +50381,7 @@
         <v>1.61</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF107" t="n">
         <v>1.7</v>
@@ -50411,7 +50411,7 @@
         <v>3.16</v>
       </c>
       <c r="DO107" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50850,10 +50850,10 @@
         <v>91</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF108" t="n">
         <v>2.5</v>
@@ -50883,7 +50883,7 @@
         <v>3.34</v>
       </c>
       <c r="DO108" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51298,7 +51298,7 @@
         <v>64</v>
       </c>
       <c r="DD109" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE109" t="n">
         <v>1.17</v>
@@ -51331,7 +51331,7 @@
         <v>2.93</v>
       </c>
       <c r="DO109" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51773,7 +51773,7 @@
         <v>1.33</v>
       </c>
       <c r="DE110" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF110" t="n">
         <v>1.18</v>
@@ -51803,7 +51803,7 @@
         <v>2.47</v>
       </c>
       <c r="DO110" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP110" t="b">
         <v>0</v>
@@ -52242,7 +52242,7 @@
         <v>67</v>
       </c>
       <c r="DD111" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE111" t="n">
         <v>1.67</v>
@@ -52275,7 +52275,7 @@
         <v>3.25</v>
       </c>
       <c r="DO111" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52717,7 +52717,7 @@
         <v>1.17</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF112" t="n">
         <v>1.6</v>
@@ -52747,7 +52747,7 @@
         <v>2.83</v>
       </c>
       <c r="DO112" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53173,7 +53173,7 @@
         <v>1.28</v>
       </c>
       <c r="DE113" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF113" t="n">
         <v>1.6</v>
@@ -53203,7 +53203,7 @@
         <v>2.9</v>
       </c>
       <c r="DO113" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53659,7 +53659,7 @@
         <v>2.83</v>
       </c>
       <c r="DO114" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54090,7 +54090,7 @@
         <v>82</v>
       </c>
       <c r="DD115" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE115" t="n">
         <v>2.28</v>
@@ -54123,7 +54123,7 @@
         <v>3.48</v>
       </c>
       <c r="DO115" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54546,7 +54546,7 @@
         <v>86</v>
       </c>
       <c r="DD116" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE116" t="n">
         <v>1.17</v>
@@ -54579,7 +54579,7 @@
         <v>3.48</v>
       </c>
       <c r="DO116" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -54997,7 +54997,7 @@
         <v>1.61</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF117" t="n">
         <v>1.82</v>
@@ -55027,7 +55027,7 @@
         <v>2.92</v>
       </c>
       <c r="DO117" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55466,10 +55466,10 @@
         <v>75</v>
       </c>
       <c r="DD118" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE118" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF118" t="n">
         <v>0.92</v>
@@ -55499,7 +55499,7 @@
         <v>2.73</v>
       </c>
       <c r="DO118" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55930,7 +55930,7 @@
         <v>78</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE119" t="n">
         <v>1.67</v>
@@ -55963,7 +55963,7 @@
         <v>3.2</v>
       </c>
       <c r="DO119" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56402,10 +56402,10 @@
         <v>79</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE120" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF120" t="n">
         <v>1.83</v>
@@ -56435,7 +56435,7 @@
         <v>3.15</v>
       </c>
       <c r="DO120" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56874,10 +56874,10 @@
         <v>82</v>
       </c>
       <c r="DD121" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE121" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF121" t="n">
         <v>2.55</v>
@@ -56907,7 +56907,7 @@
         <v>3.58</v>
       </c>
       <c r="DO121" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57347,7 +57347,7 @@
         <v>2.8</v>
       </c>
       <c r="DO122" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57757,7 +57757,7 @@
         <v>1.33</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF123" t="n">
         <v>1.17</v>
@@ -57787,7 +57787,7 @@
         <v>2.55</v>
       </c>
       <c r="DO123" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -58243,7 +58243,7 @@
         <v>2.66</v>
       </c>
       <c r="DO124" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -58650,7 +58650,7 @@
         <v>71</v>
       </c>
       <c r="DD125" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE125" t="n">
         <v>2.28</v>
@@ -58683,7 +58683,7 @@
         <v>3.77</v>
       </c>
       <c r="DO125" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -59143,7 +59143,7 @@
         <v>3.1</v>
       </c>
       <c r="DO126" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59558,10 +59558,10 @@
         <v>80</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE127" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF127" t="n">
         <v>1.58</v>
@@ -59591,7 +59591,7 @@
         <v>2.62</v>
       </c>
       <c r="DO127" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -60014,10 +60014,10 @@
         <v>69</v>
       </c>
       <c r="DD128" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DE128" t="n">
         <v>0.9399999999999999</v>
-      </c>
-      <c r="DE128" t="n">
-        <v>1</v>
       </c>
       <c r="DF128" t="n">
         <v>1.08</v>
@@ -60047,7 +60047,7 @@
         <v>3.04</v>
       </c>
       <c r="DO128" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP128" t="b">
         <v>0</v>
@@ -60486,10 +60486,10 @@
         <v>85</v>
       </c>
       <c r="DD129" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE129" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF129" t="n">
         <v>2.58</v>
@@ -60519,7 +60519,7 @@
         <v>3.31</v>
       </c>
       <c r="DO129" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -60958,10 +60958,10 @@
         <v>85</v>
       </c>
       <c r="DD130" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF130" t="n">
         <v>2</v>
@@ -60991,7 +60991,7 @@
         <v>3.16</v>
       </c>
       <c r="DO130" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61430,10 +61430,10 @@
         <v>77</v>
       </c>
       <c r="DD131" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE131" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF131" t="n">
         <v>1.92</v>
@@ -61463,7 +61463,7 @@
         <v>2.97</v>
       </c>
       <c r="DO131" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -61919,7 +61919,7 @@
         <v>2.63</v>
       </c>
       <c r="DO132" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP132" t="b">
         <v>1</v>
@@ -62391,7 +62391,7 @@
         <v>3.28</v>
       </c>
       <c r="DO133" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -62863,7 +62863,7 @@
         <v>3.33</v>
       </c>
       <c r="DO134" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63311,7 +63311,7 @@
         <v>3.12</v>
       </c>
       <c r="DO135" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP135" t="b">
         <v>0</v>
@@ -63767,7 +63767,7 @@
         <v>2.81</v>
       </c>
       <c r="DO136" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP136" t="b">
         <v>1</v>
@@ -64182,10 +64182,10 @@
         <v>77</v>
       </c>
       <c r="DD137" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE137" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF137" t="n">
         <v>1.69</v>
@@ -64215,7 +64215,7 @@
         <v>3.01</v>
       </c>
       <c r="DO137" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP137" t="b">
         <v>1</v>
@@ -64654,7 +64654,7 @@
         <v>85</v>
       </c>
       <c r="DD138" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE138" t="n">
         <v>0.89</v>
@@ -64687,7 +64687,7 @@
         <v>3.48</v>
       </c>
       <c r="DO138" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP138" t="b">
         <v>1</v>
@@ -65135,7 +65135,7 @@
         <v>3.18</v>
       </c>
       <c r="DO139" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP139" t="b">
         <v>1</v>
@@ -65553,7 +65553,7 @@
         <v>1.17</v>
       </c>
       <c r="DE140" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF140" t="n">
         <v>1.31</v>
@@ -65583,7 +65583,7 @@
         <v>2.86</v>
       </c>
       <c r="DO140" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -66047,7 +66047,7 @@
         <v>3.2</v>
       </c>
       <c r="DO141" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -66481,7 +66481,7 @@
         <v>1.61</v>
       </c>
       <c r="DE142" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF142" t="n">
         <v>1.57</v>
@@ -66511,7 +66511,7 @@
         <v>2.53</v>
       </c>
       <c r="DO142" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66607,176 +66607,168 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F143" s="1" t="n">
         <v>46124.58333333334</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J143" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143" t="n">
+        <v>5</v>
+      </c>
+      <c r="L143" t="n">
+        <v>8</v>
+      </c>
+      <c r="M143" t="n">
+        <v>2</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
         <v>6</v>
       </c>
-      <c r="K143" t="n">
+      <c r="R143" t="n">
+        <v>6</v>
+      </c>
+      <c r="S143" t="n">
+        <v>8</v>
+      </c>
+      <c r="T143" t="n">
+        <v>8</v>
+      </c>
+      <c r="U143" t="n">
+        <v>14</v>
+      </c>
+      <c r="V143" t="n">
+        <v>14</v>
+      </c>
+      <c r="W143" t="n">
+        <v>12</v>
+      </c>
+      <c r="X143" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG143" t="n">
         <v>3</v>
-      </c>
-      <c r="L143" t="n">
-        <v>9</v>
-      </c>
-      <c r="M143" t="n">
-        <v>4</v>
-      </c>
-      <c r="N143" t="n">
-        <v>1</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>4</v>
-      </c>
-      <c r="R143" t="n">
-        <v>2</v>
-      </c>
-      <c r="S143" t="n">
-        <v>16</v>
-      </c>
-      <c r="T143" t="n">
-        <v>4</v>
-      </c>
-      <c r="U143" t="n">
-        <v>20</v>
-      </c>
-      <c r="V143" t="n">
-        <v>6</v>
-      </c>
-      <c r="W143" t="n">
-        <v>11</v>
-      </c>
-      <c r="X143" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>Stadion HNK Rijeka</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>Rujevica ulica 6B, Rijeka</t>
-        </is>
-      </c>
-      <c r="AC143" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE143" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF143" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>5.25</v>
       </c>
       <c r="AH143" t="n">
         <v>1.32</v>
       </c>
       <c r="AI143" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AJ143" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AK143" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AL143" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AM143" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AN143" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AO143" t="n">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AR143" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU143" t="n">
         <v>3</v>
       </c>
-      <c r="AS143" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AT143" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AU143" t="n">
-        <v>2</v>
-      </c>
       <c r="AV143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW143" t="n">
         <v>1</v>
       </c>
       <c r="AX143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ143" t="n">
         <v>1</v>
       </c>
       <c r="BA143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB143" t="n">
-        <v>1864</v>
+        <v>1881</v>
       </c>
       <c r="BC143" t="n">
         <v>0</v>
       </c>
       <c r="BD143" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="BE143" t="n">
         <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>4919</v>
+        <v>1696</v>
       </c>
       <c r="BG143" t="n">
         <v>2</v>
@@ -66785,73 +66777,73 @@
         <v>1</v>
       </c>
       <c r="BI143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM143" t="n">
         <v>5</v>
-      </c>
-      <c r="BJ143" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK143" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL143" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM143" t="n">
-        <v>6</v>
       </c>
       <c r="BN143" t="n">
         <v>3</v>
       </c>
       <c r="BO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT143" t="n">
         <v>4</v>
       </c>
-      <c r="BP143" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS143" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT143" t="n">
-        <v>0</v>
-      </c>
       <c r="BU143" t="n">
         <v>1</v>
       </c>
       <c r="BV143" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="BW143" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="BX143" t="n">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="BY143" t="n">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="BZ143" t="n">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="CA143" t="n">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="CB143" t="n">
-        <v>3.08</v>
+        <v>3.47</v>
       </c>
       <c r="CC143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD143" t="n">
         <v>0</v>
       </c>
       <c r="CE143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF143" t="n">
         <v>0</v>
@@ -66872,7 +66864,7 @@
         <v>0</v>
       </c>
       <c r="CL143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM143" t="n">
         <v>0</v>
@@ -66890,77 +66882,77 @@
         <v>1</v>
       </c>
       <c r="CR143" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="CS143" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="CT143" t="n">
         <v>1</v>
       </c>
       <c r="CU143" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CV143" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY143" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ143" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA143" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB143" t="n">
+        <v>47</v>
+      </c>
+      <c r="DC143" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD143" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE143" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF143" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DG143" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DI143" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ143" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK143" t="n">
         <v>11</v>
       </c>
-      <c r="CW143" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX143" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY143" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ143" t="n">
-        <v>50</v>
-      </c>
-      <c r="DA143" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB143" t="n">
+      <c r="DL143" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM143" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DO143" t="n">
         <v>36</v>
       </c>
-      <c r="DC143" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD143" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DE143" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DF143" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DG143" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DH143" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="DI143" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DJ143" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK143" t="n">
-        <v>25</v>
-      </c>
-      <c r="DL143" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DM143" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DN143" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="DO143" t="n">
-        <v>35</v>
-      </c>
       <c r="DP143" t="b">
         <v>1</v>
       </c>
@@ -66968,7 +66960,7 @@
         <v>1</v>
       </c>
       <c r="DR143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS143" t="b">
         <v>0</v>
@@ -66980,31 +66972,31 @@
         <v>0</v>
       </c>
       <c r="DV143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW143" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="DX143" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="DY143" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="DZ143" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EA143" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EB143" t="inlineStr">
@@ -67014,44 +67006,44 @@
       </c>
       <c r="EC143" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED143" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EE143" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EF143" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EG143" t="inlineStr"/>
       <c r="EH143" t="inlineStr"/>
       <c r="EI143" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EJ143" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EK143" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EL143" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.54</t>
         </is>
       </c>
     </row>
@@ -67071,40 +67063,40 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F144" s="1" t="n">
         <v>46124.58333333334</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I144" t="n">
+        <v>2</v>
+      </c>
+      <c r="J144" t="n">
+        <v>6</v>
+      </c>
+      <c r="K144" t="n">
         <v>3</v>
       </c>
-      <c r="J144" t="n">
-        <v>3</v>
-      </c>
-      <c r="K144" t="n">
-        <v>5</v>
-      </c>
       <c r="L144" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -67113,126 +67105,134 @@
         <v>0</v>
       </c>
       <c r="Q144" t="n">
+        <v>4</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2</v>
+      </c>
+      <c r="S144" t="n">
+        <v>16</v>
+      </c>
+      <c r="T144" t="n">
+        <v>4</v>
+      </c>
+      <c r="U144" t="n">
+        <v>20</v>
+      </c>
+      <c r="V144" t="n">
         <v>6</v>
       </c>
-      <c r="R144" t="n">
-        <v>6</v>
-      </c>
-      <c r="S144" t="n">
-        <v>8</v>
-      </c>
-      <c r="T144" t="n">
-        <v>8</v>
-      </c>
-      <c r="U144" t="n">
-        <v>14</v>
-      </c>
-      <c r="V144" t="n">
-        <v>14</v>
-      </c>
       <c r="W144" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X144" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y144" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="Z144" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA144" t="inlineStr"/>
-      <c r="AB144" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
       <c r="AC144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE144" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AF144" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AG144" t="n">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="AH144" t="n">
         <v>1.32</v>
       </c>
       <c r="AI144" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AJ144" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AK144" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AL144" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AM144" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AN144" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AO144" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AR144" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AS144" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AT144" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AU144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW144" t="n">
         <v>1</v>
       </c>
       <c r="AX144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ144" t="n">
         <v>1</v>
       </c>
       <c r="BA144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB144" t="n">
-        <v>1881</v>
+        <v>1864</v>
       </c>
       <c r="BC144" t="n">
         <v>0</v>
       </c>
       <c r="BD144" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="BE144" t="n">
         <v>0</v>
       </c>
       <c r="BF144" t="n">
-        <v>1696</v>
+        <v>4919</v>
       </c>
       <c r="BG144" t="n">
         <v>2</v>
@@ -67241,10 +67241,10 @@
         <v>1</v>
       </c>
       <c r="BI144" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BJ144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK144" t="n">
         <v>1</v>
@@ -67253,61 +67253,61 @@
         <v>2</v>
       </c>
       <c r="BM144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN144" t="n">
         <v>3</v>
       </c>
       <c r="BO144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BT144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BU144" t="n">
         <v>1</v>
       </c>
       <c r="BV144" t="n">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="BW144" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="BX144" t="n">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="BY144" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="BZ144" t="n">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="CA144" t="n">
-        <v>1.71</v>
+        <v>0.75</v>
       </c>
       <c r="CB144" t="n">
-        <v>3.47</v>
+        <v>3.08</v>
       </c>
       <c r="CC144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD144" t="n">
         <v>0</v>
       </c>
       <c r="CE144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF144" t="n">
         <v>0</v>
@@ -67328,7 +67328,7 @@
         <v>0</v>
       </c>
       <c r="CL144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM144" t="n">
         <v>0</v>
@@ -67346,76 +67346,76 @@
         <v>1</v>
       </c>
       <c r="CR144" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="CS144" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU144" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV144" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX144" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY144" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ144" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA144" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB144" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC144" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD144" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE144" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF144" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DG144" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH144" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DI144" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DJ144" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK144" t="n">
         <v>25</v>
       </c>
-      <c r="CT144" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU144" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV144" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW144" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX144" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY144" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ144" t="n">
-        <v>57</v>
-      </c>
-      <c r="DA144" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB144" t="n">
-        <v>47</v>
-      </c>
-      <c r="DC144" t="n">
-        <v>83</v>
-      </c>
-      <c r="DD144" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="DE144" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DF144" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="DG144" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="DH144" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DI144" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="DJ144" t="n">
-        <v>43</v>
-      </c>
-      <c r="DK144" t="n">
-        <v>11</v>
-      </c>
       <c r="DL144" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="DM144" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="DN144" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="DO144" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -67424,7 +67424,7 @@
         <v>1</v>
       </c>
       <c r="DR144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS144" t="b">
         <v>0</v>
@@ -67436,31 +67436,31 @@
         <v>0</v>
       </c>
       <c r="DV144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW144" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX144" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="DY144" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="DZ144" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EA144" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EB144" t="inlineStr">
@@ -67470,44 +67470,44 @@
       </c>
       <c r="EC144" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="ED144" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EE144" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EF144" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="EG144" t="inlineStr"/>
       <c r="EH144" t="inlineStr"/>
       <c r="EI144" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EJ144" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EK144" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EL144" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -67846,10 +67846,10 @@
         <v>75</v>
       </c>
       <c r="DD145" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE145" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF145" t="n">
         <v>2.07</v>
@@ -67879,7 +67879,7 @@
         <v>3.3</v>
       </c>
       <c r="DO145" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -68343,7 +68343,7 @@
         <v>3.45</v>
       </c>
       <c r="DO146" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -68761,7 +68761,7 @@
         <v>1.33</v>
       </c>
       <c r="DE147" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF147" t="n">
         <v>1.29</v>
@@ -68791,7 +68791,7 @@
         <v>2.64</v>
       </c>
       <c r="DO147" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP147" t="b">
         <v>1</v>
@@ -69231,7 +69231,7 @@
         <v>3.5</v>
       </c>
       <c r="DO148" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -69662,7 +69662,7 @@
         <v>64</v>
       </c>
       <c r="DD149" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE149" t="n">
         <v>1.17</v>
@@ -69695,7 +69695,7 @@
         <v>2.87</v>
       </c>
       <c r="DO149" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP149" t="b">
         <v>1</v>
@@ -70110,7 +70110,7 @@
         <v>86</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE150" t="n">
         <v>1.17</v>
@@ -70143,7 +70143,7 @@
         <v>3.67</v>
       </c>
       <c r="DO150" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP150" t="b">
         <v>1</v>
@@ -70569,7 +70569,7 @@
         <v>1.28</v>
       </c>
       <c r="DE151" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF151" t="n">
         <v>1.36</v>
@@ -70599,7 +70599,7 @@
         <v>2.52</v>
       </c>
       <c r="DO151" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP151" t="b">
         <v>1</v>
@@ -71017,7 +71017,7 @@
         <v>1.61</v>
       </c>
       <c r="DE152" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF152" t="n">
         <v>1.67</v>
@@ -71047,7 +71047,7 @@
         <v>2.58</v>
       </c>
       <c r="DO152" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -71462,7 +71462,7 @@
         <v>80</v>
       </c>
       <c r="DD153" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE153" t="n">
         <v>0.89</v>
@@ -71495,7 +71495,7 @@
         <v>3.18</v>
       </c>
       <c r="DO153" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP153" t="b">
         <v>1</v>
@@ -71929,7 +71929,7 @@
         <v>1.17</v>
       </c>
       <c r="DE154" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF154" t="n">
         <v>1.2</v>
@@ -71959,7 +71959,7 @@
         <v>2.84</v>
       </c>
       <c r="DO154" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP154" t="b">
         <v>1</v>
@@ -72366,7 +72366,7 @@
         <v>84</v>
       </c>
       <c r="DD155" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE155" t="n">
         <v>1.17</v>
@@ -72399,7 +72399,7 @@
         <v>3.05</v>
       </c>
       <c r="DO155" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP155" t="b">
         <v>1</v>
@@ -72847,7 +72847,7 @@
         <v>3.37</v>
       </c>
       <c r="DO156" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP156" t="b">
         <v>1</v>
@@ -73265,7 +73265,7 @@
         <v>1.61</v>
       </c>
       <c r="DE157" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF157" t="n">
         <v>1.67</v>
@@ -73295,7 +73295,7 @@
         <v>2.82</v>
       </c>
       <c r="DO157" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP157" t="b">
         <v>1</v>
@@ -73726,10 +73726,10 @@
         <v>74</v>
       </c>
       <c r="DD158" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE158" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF158" t="n">
         <v>1</v>
@@ -73759,7 +73759,7 @@
         <v>2.99</v>
       </c>
       <c r="DO158" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP158" t="b">
         <v>0</v>
@@ -74190,7 +74190,7 @@
         <v>77</v>
       </c>
       <c r="DD159" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE159" t="n">
         <v>1.67</v>
@@ -74223,7 +74223,7 @@
         <v>3.68</v>
       </c>
       <c r="DO159" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP159" t="b">
         <v>0</v>
@@ -74654,7 +74654,7 @@
         <v>83</v>
       </c>
       <c r="DD160" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE160" t="n">
         <v>1.17</v>
@@ -74687,7 +74687,7 @@
         <v>3.4</v>
       </c>
       <c r="DO160" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75113,7 +75113,7 @@
         <v>1.33</v>
       </c>
       <c r="DE161" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF161" t="n">
         <v>1.2</v>
@@ -75143,7 +75143,7 @@
         <v>2.5</v>
       </c>
       <c r="DO161" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP161" t="b">
         <v>1</v>
@@ -75591,7 +75591,7 @@
         <v>3.3</v>
       </c>
       <c r="DO162" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP162" t="b">
         <v>1</v>
@@ -76023,7 +76023,7 @@
         <v>2.75</v>
       </c>
       <c r="DO163" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP163" t="b">
         <v>1</v>
@@ -76471,7 +76471,7 @@
         <v>2.88</v>
       </c>
       <c r="DO164" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP164" t="b">
         <v>1</v>
@@ -76902,7 +76902,7 @@
         <v>72</v>
       </c>
       <c r="DD165" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DE165" t="n">
         <v>1.17</v>
@@ -76935,7 +76935,7 @@
         <v>3.11</v>
       </c>
       <c r="DO165" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP165" t="b">
         <v>1</v>
@@ -77369,7 +77369,7 @@
         <v>1.28</v>
       </c>
       <c r="DE166" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DF166" t="n">
         <v>1.19</v>
@@ -77399,7 +77399,7 @@
         <v>2.54</v>
       </c>
       <c r="DO166" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP166" t="b">
         <v>1</v>
@@ -77814,10 +77814,10 @@
         <v>75</v>
       </c>
       <c r="DD167" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DE167" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DF167" t="n">
         <v>1.63</v>
@@ -77847,7 +77847,7 @@
         <v>3.02</v>
       </c>
       <c r="DO167" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP167" t="b">
         <v>1</v>
@@ -78262,7 +78262,7 @@
         <v>82</v>
       </c>
       <c r="DD168" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DE168" t="n">
         <v>1.67</v>
@@ -78295,7 +78295,7 @@
         <v>3.8</v>
       </c>
       <c r="DO168" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP168" t="b">
         <v>1</v>
@@ -78710,10 +78710,10 @@
         <v>81</v>
       </c>
       <c r="DD169" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DE169" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DF169" t="n">
         <v>1.81</v>
@@ -78743,7 +78743,7 @@
         <v>2.78</v>
       </c>
       <c r="DO169" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP169" t="b">
         <v>1</v>
@@ -79174,10 +79174,10 @@
         <v>72</v>
       </c>
       <c r="DD170" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DE170" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DF170" t="n">
         <v>1</v>
@@ -79207,7 +79207,7 @@
         <v>2.87</v>
       </c>
       <c r="DO170" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP170" t="b">
         <v>1</v>
@@ -79617,7 +79617,7 @@
         <v>1.61</v>
       </c>
       <c r="DE171" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DF171" t="n">
         <v>1.63</v>
@@ -79647,7 +79647,7 @@
         <v>3.08</v>
       </c>
       <c r="DO171" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -80095,7 +80095,7 @@
         <v>2.72</v>
       </c>
       <c r="DO172" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP172" t="b">
         <v>1</v>
@@ -80527,7 +80527,7 @@
         <v>2.59</v>
       </c>
       <c r="DO173" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP173" t="b">
         <v>1</v>
@@ -80999,7 +80999,7 @@
         <v>2.98</v>
       </c>
       <c r="DO174" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP174" t="b">
         <v>1</v>
@@ -81455,7 +81455,7 @@
         <v>3.59</v>
       </c>
       <c r="DO175" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP175" t="b">
         <v>1</v>
@@ -81887,7 +81887,7 @@
         <v>2.83</v>
       </c>
       <c r="DO176" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="DP176" t="b">
         <v>0</v>
@@ -81966,6 +81966,2254 @@
       <c r="EJ176" t="inlineStr"/>
       <c r="EK176" t="inlineStr"/>
       <c r="EL176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>36</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Slaven Koprivnica</t>
+        </is>
+      </c>
+      <c r="F177" s="1" t="n">
+        <v>46164.58333333334</v>
+      </c>
+      <c r="G177" t="n">
+        <v>2</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2</v>
+      </c>
+      <c r="J177" t="n">
+        <v>16</v>
+      </c>
+      <c r="K177" t="n">
+        <v>2</v>
+      </c>
+      <c r="L177" t="n">
+        <v>18</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>9</v>
+      </c>
+      <c r="R177" t="n">
+        <v>2</v>
+      </c>
+      <c r="S177" t="n">
+        <v>15</v>
+      </c>
+      <c r="T177" t="n">
+        <v>8</v>
+      </c>
+      <c r="U177" t="n">
+        <v>24</v>
+      </c>
+      <c r="V177" t="n">
+        <v>10</v>
+      </c>
+      <c r="W177" t="n">
+        <v>19</v>
+      </c>
+      <c r="X177" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>Stadion Gradski vrt</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>Delnička bb, Osijek</t>
+        </is>
+      </c>
+      <c r="AC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>1864</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>1572</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU177" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV177" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW177" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX177" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY177" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ177" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CA177" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB177" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="CC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM177" t="n">
+        <v>3</v>
+      </c>
+      <c r="CN177" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR177" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS177" t="n">
+        <v>7</v>
+      </c>
+      <c r="CT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU177" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV177" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW177" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX177" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY177" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ177" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA177" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB177" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC177" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD177" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DE177" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF177" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DG177" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DH177" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DI177" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ177" t="n">
+        <v>56</v>
+      </c>
+      <c r="DK177" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL177" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DM177" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN177" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO177" t="n">
+        <v>36</v>
+      </c>
+      <c r="DP177" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ177" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV177" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW177" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="DX177" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="DY177" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="DZ177" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA177" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EB177" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EC177" t="inlineStr"/>
+      <c r="ED177" t="inlineStr"/>
+      <c r="EE177" t="inlineStr"/>
+      <c r="EF177" t="inlineStr"/>
+      <c r="EG177" t="inlineStr"/>
+      <c r="EH177" t="inlineStr"/>
+      <c r="EI177" t="inlineStr"/>
+      <c r="EJ177" t="inlineStr"/>
+      <c r="EK177" t="inlineStr"/>
+      <c r="EL177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>36</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Hajduk Split</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>HNK Vukovar 1991</t>
+        </is>
+      </c>
+      <c r="F178" s="1" t="n">
+        <v>46164.67708333334</v>
+      </c>
+      <c r="G178" t="n">
+        <v>6</v>
+      </c>
+      <c r="H178" t="n">
+        <v>3</v>
+      </c>
+      <c r="I178" t="n">
+        <v>9</v>
+      </c>
+      <c r="J178" t="n">
+        <v>8</v>
+      </c>
+      <c r="K178" t="n">
+        <v>3</v>
+      </c>
+      <c r="L178" t="n">
+        <v>11</v>
+      </c>
+      <c r="M178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>9</v>
+      </c>
+      <c r="R178" t="n">
+        <v>3</v>
+      </c>
+      <c r="S178" t="n">
+        <v>3</v>
+      </c>
+      <c r="T178" t="n">
+        <v>5</v>
+      </c>
+      <c r="U178" t="n">
+        <v>12</v>
+      </c>
+      <c r="V178" t="n">
+        <v>8</v>
+      </c>
+      <c r="W178" t="n">
+        <v>15</v>
+      </c>
+      <c r="X178" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Stadion Poljud</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>8. Mediteranskih igara 2, Split</t>
+        </is>
+      </c>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>1863</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>11355</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU178" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV178" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW178" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX178" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY178" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ178" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA178" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CB178" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP178" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR178" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS178" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU178" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV178" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW178" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX178" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY178" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ178" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA178" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB178" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC178" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD178" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE178" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="DF178" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DG178" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DH178" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DI178" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ178" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK178" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL178" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM178" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN178" t="n">
+        <v>3</v>
+      </c>
+      <c r="DO178" t="n">
+        <v>36</v>
+      </c>
+      <c r="DP178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV178" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW178" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="DX178" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="DY178" t="inlineStr">
+        <is>
+          <t>8.74</t>
+        </is>
+      </c>
+      <c r="DZ178" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EA178" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EB178" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EC178" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="ED178" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE178" t="inlineStr"/>
+      <c r="EF178" t="inlineStr"/>
+      <c r="EG178" t="inlineStr"/>
+      <c r="EH178" t="inlineStr"/>
+      <c r="EI178" t="inlineStr"/>
+      <c r="EJ178" t="inlineStr"/>
+      <c r="EK178" t="inlineStr"/>
+      <c r="EL178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>36</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Istra 1961</t>
+        </is>
+      </c>
+      <c r="F179" s="1" t="n">
+        <v>46165.58333333334</v>
+      </c>
+      <c r="G179" t="n">
+        <v>2</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>2</v>
+      </c>
+      <c r="J179" t="n">
+        <v>2</v>
+      </c>
+      <c r="K179" t="n">
+        <v>3</v>
+      </c>
+      <c r="L179" t="n">
+        <v>5</v>
+      </c>
+      <c r="M179" t="n">
+        <v>2</v>
+      </c>
+      <c r="N179" t="n">
+        <v>3</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>8</v>
+      </c>
+      <c r="R179" t="n">
+        <v>4</v>
+      </c>
+      <c r="S179" t="n">
+        <v>4</v>
+      </c>
+      <c r="T179" t="n">
+        <v>7</v>
+      </c>
+      <c r="U179" t="n">
+        <v>12</v>
+      </c>
+      <c r="V179" t="n">
+        <v>11</v>
+      </c>
+      <c r="W179" t="n">
+        <v>18</v>
+      </c>
+      <c r="X179" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA179" t="inlineStr"/>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>1881</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>2420</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS179" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT179" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV179" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW179" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX179" t="n">
+        <v>62</v>
+      </c>
+      <c r="BY179" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ179" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CA179" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CC179" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE179" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP179" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR179" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS179" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU179" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV179" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW179" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX179" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY179" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ179" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA179" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB179" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC179" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD179" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DE179" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DF179" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DG179" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DH179" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DI179" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DJ179" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK179" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL179" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM179" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN179" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DO179" t="n">
+        <v>36</v>
+      </c>
+      <c r="DP179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ179" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV179" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW179" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX179" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="DY179" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="DZ179" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EA179" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EB179" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC179" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="ED179" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EE179" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF179" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EG179" t="inlineStr"/>
+      <c r="EH179" t="inlineStr"/>
+      <c r="EI179" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EJ179" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EK179" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EL179" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>36</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Gorica</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="n">
+        <v>46165.58333333334</v>
+      </c>
+      <c r="G180" t="n">
+        <v>2</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>2</v>
+      </c>
+      <c r="J180" t="n">
+        <v>7</v>
+      </c>
+      <c r="K180" t="n">
+        <v>3</v>
+      </c>
+      <c r="L180" t="n">
+        <v>10</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>3</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>7</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2</v>
+      </c>
+      <c r="S180" t="n">
+        <v>14</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1</v>
+      </c>
+      <c r="U180" t="n">
+        <v>21</v>
+      </c>
+      <c r="V180" t="n">
+        <v>3</v>
+      </c>
+      <c r="W180" t="n">
+        <v>11</v>
+      </c>
+      <c r="X180" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>Stadion HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>Rujevica ulica 6B, Rijeka</t>
+        </is>
+      </c>
+      <c r="AC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>1215</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>4208</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU180" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV180" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW180" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX180" t="n">
+        <v>132</v>
+      </c>
+      <c r="BY180" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ180" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CA180" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="CB180" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP180" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR180" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS180" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU180" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV180" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW180" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX180" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY180" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ180" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA180" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB180" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC180" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD180" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE180" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DF180" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG180" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH180" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI180" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ180" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK180" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL180" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DM180" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN180" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DO180" t="n">
+        <v>36</v>
+      </c>
+      <c r="DP180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ180" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV180" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW180" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="DX180" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="DY180" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="DZ180" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EA180" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EB180" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EC180" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="ED180" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EE180" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EF180" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EG180" t="inlineStr"/>
+      <c r="EH180" t="inlineStr"/>
+      <c r="EI180" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EJ180" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EK180" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EL180" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Croatia_HNL_2025-2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>36</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb</t>
+        </is>
+      </c>
+      <c r="F181" s="1" t="n">
+        <v>46165.69791666666</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>4</v>
+      </c>
+      <c r="K181" t="n">
+        <v>2</v>
+      </c>
+      <c r="L181" t="n">
+        <v>6</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1</v>
+      </c>
+      <c r="R181" t="n">
+        <v>5</v>
+      </c>
+      <c r="S181" t="n">
+        <v>12</v>
+      </c>
+      <c r="T181" t="n">
+        <v>3</v>
+      </c>
+      <c r="U181" t="n">
+        <v>13</v>
+      </c>
+      <c r="V181" t="n">
+        <v>8</v>
+      </c>
+      <c r="W181" t="n">
+        <v>10</v>
+      </c>
+      <c r="X181" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>Stadion Maksimir</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>Maksimirska cesta 128, Zagreb</t>
+        </is>
+      </c>
+      <c r="AC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>24735</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV181" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW181" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX181" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY181" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ181" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB181" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR181" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS181" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU181" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV181" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX181" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY181" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ181" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA181" t="n">
+        <v>97</v>
+      </c>
+      <c r="DB181" t="n">
+        <v>27</v>
+      </c>
+      <c r="DC181" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE181" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF181" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DG181" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DH181" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DI181" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DJ181" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK181" t="n">
+        <v>3</v>
+      </c>
+      <c r="DL181" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DM181" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN181" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DO181" t="n">
+        <v>36</v>
+      </c>
+      <c r="DP181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW181" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="DX181" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="DY181" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="DZ181" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EA181" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EB181" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EC181" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="ED181" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EE181" t="inlineStr"/>
+      <c r="EF181" t="inlineStr"/>
+      <c r="EG181" t="inlineStr"/>
+      <c r="EH181" t="inlineStr"/>
+      <c r="EI181" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ181" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EK181" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EL181" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
